--- a/BD Cobre.xlsx
+++ b/BD Cobre.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julip\GitHub\Cobre\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534E204F-2FE7-4665-93E8-8CE91BE81CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="58">
   <si>
     <t>id</t>
   </si>
@@ -106,12 +100,105 @@
   </si>
   <si>
     <t>CuVastago</t>
+  </si>
+  <si>
+    <t>pf raiz</t>
+  </si>
+  <si>
+    <t>p seco raiz</t>
+  </si>
+  <si>
+    <t>largo vasta</t>
+  </si>
+  <si>
+    <t>pf aer</t>
+  </si>
+  <si>
+    <t>p s aereo</t>
+  </si>
+  <si>
+    <t>RAIZ+TIERRA</t>
+  </si>
+  <si>
+    <t>adherido</t>
+  </si>
+  <si>
+    <t>506,21</t>
+  </si>
+  <si>
+    <t>166,65</t>
+  </si>
+  <si>
+    <t>330,50</t>
+  </si>
+  <si>
+    <t>317,26</t>
+  </si>
+  <si>
+    <t>151,55</t>
+  </si>
+  <si>
+    <t>202,84</t>
+  </si>
+  <si>
+    <t>553,50</t>
+  </si>
+  <si>
+    <t>510,23</t>
+  </si>
+  <si>
+    <t>499,54</t>
+  </si>
+  <si>
+    <t>602,80</t>
+  </si>
+  <si>
+    <t>451,20</t>
+  </si>
+  <si>
+    <t>646,10</t>
+  </si>
+  <si>
+    <t>283,64</t>
+  </si>
+  <si>
+    <t>512,02</t>
+  </si>
+  <si>
+    <t>232,64</t>
+  </si>
+  <si>
+    <t>298,00</t>
+  </si>
+  <si>
+    <t>219,90</t>
+  </si>
+  <si>
+    <t>495,33</t>
+  </si>
+  <si>
+    <t>748,86</t>
+  </si>
+  <si>
+    <t>426,74</t>
+  </si>
+  <si>
+    <t>569,88</t>
+  </si>
+  <si>
+    <t>342,04</t>
+  </si>
+  <si>
+    <t>198,64</t>
+  </si>
+  <si>
+    <t>366,62</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -239,7 +326,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -574,12 +661,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="166">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1074,10 +1185,13 @@
     <xf numFmtId="2" fontId="4" fillId="14" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{D6A77139-65C8-49F1-9AB5-DA957D2A9824}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1135,7 +1249,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1170,7 +1284,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1347,21 +1461,21 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X43"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AE43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1434,8 +1548,29 @@
       <c r="X1" s="6" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" s="166" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="166" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA1" s="166" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB1" s="166" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC1" s="166" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD1" s="167" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE1" s="168" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1491,7 +1626,7 @@
       <c r="W2" s="9"/>
       <c r="X2" s="11"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1533,7 +1668,7 @@
       <c r="W3" s="14"/>
       <c r="X3" s="15"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1575,7 +1710,7 @@
       <c r="W4" s="14"/>
       <c r="X4" s="15"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1631,7 +1766,7 @@
       <c r="W5" s="18"/>
       <c r="X5" s="20"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1687,7 +1822,7 @@
       <c r="W6" s="18"/>
       <c r="X6" s="20"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1743,7 +1878,7 @@
       <c r="W7" s="18"/>
       <c r="X7" s="20"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1799,7 +1934,7 @@
       <c r="W8" s="25"/>
       <c r="X8" s="26"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1855,7 +1990,7 @@
       <c r="W9" s="25"/>
       <c r="X9" s="26"/>
     </row>
-    <row r="10" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1911,7 +2046,7 @@
       <c r="W10" s="29"/>
       <c r="X10" s="30"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1971,7 +2106,7 @@
       <c r="W11" s="34"/>
       <c r="X11" s="36"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -2031,7 +2166,7 @@
       <c r="W12" s="40"/>
       <c r="X12" s="42"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2073,7 +2208,7 @@
       <c r="W13" s="40"/>
       <c r="X13" s="42"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2133,7 +2268,7 @@
       <c r="W14" s="46"/>
       <c r="X14" s="48"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2193,7 +2328,7 @@
       <c r="W15" s="46"/>
       <c r="X15" s="48"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -2251,7 +2386,7 @@
       <c r="W16" s="46"/>
       <c r="X16" s="48"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -2311,7 +2446,7 @@
       <c r="W17" s="53"/>
       <c r="X17" s="55"/>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2371,7 +2506,7 @@
       <c r="W18" s="53"/>
       <c r="X18" s="55"/>
     </row>
-    <row r="19" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -2431,7 +2566,7 @@
       <c r="W19" s="60"/>
       <c r="X19" s="62"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -2490,8 +2625,30 @@
       <c r="X20" s="69">
         <v>100</v>
       </c>
+      <c r="Y20" s="69">
+        <v>5.5</v>
+      </c>
+      <c r="Z20" s="69">
+        <v>1.1176999999999999</v>
+      </c>
+      <c r="AA20" s="69">
+        <v>134</v>
+      </c>
+      <c r="AB20" s="69">
+        <f>66.01+0.26</f>
+        <v>66.27000000000001</v>
+      </c>
+      <c r="AC20" s="69">
+        <v>12.5967</v>
+      </c>
+      <c r="AD20" s="69">
+        <v>1565.5</v>
+      </c>
+      <c r="AE20" s="69" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -2550,8 +2707,29 @@
       <c r="X21" s="77">
         <v>110</v>
       </c>
+      <c r="Y21" s="77">
+        <v>3.84</v>
+      </c>
+      <c r="Z21" s="77">
+        <v>1.0099</v>
+      </c>
+      <c r="AA21" s="77">
+        <v>137</v>
+      </c>
+      <c r="AB21" s="77">
+        <v>63.34</v>
+      </c>
+      <c r="AC21" s="77">
+        <v>12.082800000000001</v>
+      </c>
+      <c r="AD21" s="77">
+        <v>1970</v>
+      </c>
+      <c r="AE21" s="77" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -2610,8 +2788,30 @@
       <c r="X22" s="77">
         <v>191</v>
       </c>
+      <c r="Y22" s="77">
+        <v>4.18</v>
+      </c>
+      <c r="Z22" s="77">
+        <v>0.87560000000000004</v>
+      </c>
+      <c r="AA22" s="77">
+        <v>135</v>
+      </c>
+      <c r="AB22" s="77">
+        <f>60.98+0.62</f>
+        <v>61.599999999999994</v>
+      </c>
+      <c r="AC22" s="77">
+        <v>9.5932999999999993</v>
+      </c>
+      <c r="AD22" s="77">
+        <v>976.6</v>
+      </c>
+      <c r="AE22" s="77" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -2662,8 +2862,29 @@
       <c r="X23" s="77">
         <v>566</v>
       </c>
+      <c r="Y23" s="77">
+        <v>4.7</v>
+      </c>
+      <c r="Z23" s="77">
+        <v>0.9617</v>
+      </c>
+      <c r="AA23" s="77">
+        <v>117</v>
+      </c>
+      <c r="AB23" s="77">
+        <v>56.13</v>
+      </c>
+      <c r="AC23" s="77">
+        <v>10.324999999999999</v>
+      </c>
+      <c r="AD23" s="77">
+        <v>1405.3</v>
+      </c>
+      <c r="AE23" s="77" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -2704,8 +2925,30 @@
       <c r="V24" s="80"/>
       <c r="W24" s="80"/>
       <c r="X24" s="84"/>
+      <c r="Y24" s="84">
+        <v>6.1</v>
+      </c>
+      <c r="Z24" s="84">
+        <v>0.83899999999999997</v>
+      </c>
+      <c r="AA24" s="84">
+        <v>121</v>
+      </c>
+      <c r="AB24" s="84">
+        <f>46.77+0.83</f>
+        <v>47.6</v>
+      </c>
+      <c r="AC24" s="84">
+        <v>9.7091999999999992</v>
+      </c>
+      <c r="AD24" s="84">
+        <v>1347.49</v>
+      </c>
+      <c r="AE24" s="84" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -2746,8 +2989,29 @@
       <c r="V25" s="80"/>
       <c r="W25" s="80"/>
       <c r="X25" s="84"/>
+      <c r="Y25" s="84">
+        <v>2.7</v>
+      </c>
+      <c r="Z25" s="84">
+        <v>0.55459999999999998</v>
+      </c>
+      <c r="AA25" s="84">
+        <v>158</v>
+      </c>
+      <c r="AB25" s="84">
+        <v>69.430000000000007</v>
+      </c>
+      <c r="AC25" s="84">
+        <v>12.512700000000001</v>
+      </c>
+      <c r="AD25" s="84">
+        <v>1340.09</v>
+      </c>
+      <c r="AE25" s="84" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -2788,8 +3052,29 @@
       <c r="V26" s="80"/>
       <c r="W26" s="80"/>
       <c r="X26" s="84"/>
+      <c r="Y26" s="84">
+        <v>1.64</v>
+      </c>
+      <c r="Z26" s="84">
+        <v>0.4622</v>
+      </c>
+      <c r="AA26" s="84">
+        <v>120</v>
+      </c>
+      <c r="AB26" s="84">
+        <v>45.52</v>
+      </c>
+      <c r="AC26" s="84">
+        <v>7.8204000000000002</v>
+      </c>
+      <c r="AD26" s="84">
+        <v>1229.77</v>
+      </c>
+      <c r="AE26" s="84" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -2830,8 +3115,29 @@
       <c r="V27" s="80"/>
       <c r="W27" s="80"/>
       <c r="X27" s="84"/>
+      <c r="Y27" s="84">
+        <v>3.3</v>
+      </c>
+      <c r="Z27" s="84">
+        <v>0.39300000000000002</v>
+      </c>
+      <c r="AA27" s="84">
+        <v>69</v>
+      </c>
+      <c r="AB27" s="84">
+        <v>43.58</v>
+      </c>
+      <c r="AC27" s="84">
+        <v>5.5315000000000003</v>
+      </c>
+      <c r="AD27" s="84">
+        <v>1411.55</v>
+      </c>
+      <c r="AE27" s="84" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -2890,8 +3196,29 @@
       <c r="X28" s="93">
         <v>808</v>
       </c>
+      <c r="Y28" s="93">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Z28" s="93">
+        <v>0.60680000000000001</v>
+      </c>
+      <c r="AA28" s="93">
+        <v>116</v>
+      </c>
+      <c r="AB28" s="93">
+        <v>59.53</v>
+      </c>
+      <c r="AC28" s="93">
+        <v>10.5433</v>
+      </c>
+      <c r="AD28" s="93">
+        <v>1313.02</v>
+      </c>
+      <c r="AE28" s="93" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -2950,8 +3277,29 @@
       <c r="X29" s="93">
         <v>668</v>
       </c>
+      <c r="Y29" s="93">
+        <v>3.97</v>
+      </c>
+      <c r="Z29" s="93">
+        <v>1.089</v>
+      </c>
+      <c r="AA29" s="93">
+        <v>142</v>
+      </c>
+      <c r="AB29" s="93">
+        <v>60.27</v>
+      </c>
+      <c r="AC29" s="93">
+        <v>13.506399999999999</v>
+      </c>
+      <c r="AD29" s="93">
+        <v>1361.88</v>
+      </c>
+      <c r="AE29" s="93" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -3010,8 +3358,29 @@
       <c r="X30" s="93">
         <v>920</v>
       </c>
+      <c r="Y30" s="93">
+        <v>6.33</v>
+      </c>
+      <c r="Z30" s="93">
+        <v>1.0049999999999999</v>
+      </c>
+      <c r="AA30" s="93">
+        <v>85</v>
+      </c>
+      <c r="AB30" s="93">
+        <v>39.89</v>
+      </c>
+      <c r="AC30" s="93">
+        <v>11.229100000000001</v>
+      </c>
+      <c r="AD30" s="93">
+        <v>1263.72</v>
+      </c>
+      <c r="AE30" s="93" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="31" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -3070,8 +3439,29 @@
       <c r="X31" s="103">
         <v>130</v>
       </c>
+      <c r="Y31" s="103">
+        <v>3.41</v>
+      </c>
+      <c r="Z31" s="103">
+        <v>0.50919999999999999</v>
+      </c>
+      <c r="AA31" s="103">
+        <v>71</v>
+      </c>
+      <c r="AB31" s="103">
+        <v>53.12</v>
+      </c>
+      <c r="AC31" s="103">
+        <v>6.9410999999999996</v>
+      </c>
+      <c r="AD31" s="103">
+        <v>1253.58</v>
+      </c>
+      <c r="AE31" s="103" t="s">
+        <v>57</v>
+      </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -3132,8 +3522,29 @@
       <c r="X32" s="111">
         <v>150</v>
       </c>
+      <c r="Y32" s="111">
+        <v>2.38</v>
+      </c>
+      <c r="Z32" s="111">
+        <v>0.74480000000000002</v>
+      </c>
+      <c r="AA32" s="111">
+        <v>145</v>
+      </c>
+      <c r="AB32" s="111">
+        <v>55.63</v>
+      </c>
+      <c r="AC32" s="111">
+        <v>11.422000000000001</v>
+      </c>
+      <c r="AD32" s="111">
+        <v>1207.1500000000001</v>
+      </c>
+      <c r="AE32" s="111" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -3194,8 +3605,29 @@
       <c r="X33" s="119">
         <v>120</v>
       </c>
+      <c r="Y33" s="119">
+        <v>7.29</v>
+      </c>
+      <c r="Z33" s="119">
+        <v>0.81930000000000003</v>
+      </c>
+      <c r="AA33" s="119">
+        <v>109</v>
+      </c>
+      <c r="AB33" s="119">
+        <v>56.17</v>
+      </c>
+      <c r="AC33" s="119">
+        <v>9.0335999999999999</v>
+      </c>
+      <c r="AD33" s="119">
+        <v>1222.1400000000001</v>
+      </c>
+      <c r="AE33" s="119" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -3256,8 +3688,29 @@
       <c r="X34" s="119">
         <v>170</v>
       </c>
+      <c r="Y34" s="119">
+        <v>3.3</v>
+      </c>
+      <c r="Z34" s="119">
+        <v>0.89429999999999998</v>
+      </c>
+      <c r="AA34" s="119">
+        <v>117</v>
+      </c>
+      <c r="AB34" s="119">
+        <v>56.04</v>
+      </c>
+      <c r="AC34" s="119">
+        <v>10.404500000000001</v>
+      </c>
+      <c r="AD34" s="119">
+        <v>1093.95</v>
+      </c>
+      <c r="AE34" s="119" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -3310,8 +3763,29 @@
         <v>105</v>
       </c>
       <c r="X35" s="121"/>
+      <c r="Y35" s="121">
+        <v>4.22</v>
+      </c>
+      <c r="Z35" s="121">
+        <v>0.54300000000000004</v>
+      </c>
+      <c r="AA35" s="121">
+        <v>76</v>
+      </c>
+      <c r="AB35" s="121">
+        <v>40.119999999999997</v>
+      </c>
+      <c r="AC35" s="121">
+        <v>6.6025</v>
+      </c>
+      <c r="AD35" s="121">
+        <v>1343.07</v>
+      </c>
+      <c r="AE35" s="121" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -3354,8 +3828,29 @@
       <c r="V36" s="124"/>
       <c r="W36" s="123"/>
       <c r="X36" s="127"/>
+      <c r="Y36" s="127">
+        <v>8.61</v>
+      </c>
+      <c r="Z36" s="127">
+        <v>1.0141</v>
+      </c>
+      <c r="AA36" s="127">
+        <v>128</v>
+      </c>
+      <c r="AB36" s="127">
+        <v>69.31</v>
+      </c>
+      <c r="AC36" s="127">
+        <v>11.479200000000001</v>
+      </c>
+      <c r="AD36" s="127">
+        <v>1313.44</v>
+      </c>
+      <c r="AE36" s="127" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -3398,8 +3893,29 @@
       <c r="V37" s="124"/>
       <c r="W37" s="123"/>
       <c r="X37" s="127"/>
+      <c r="Y37" s="127">
+        <v>6.73</v>
+      </c>
+      <c r="Z37" s="127">
+        <v>0.90800000000000003</v>
+      </c>
+      <c r="AA37" s="127">
+        <v>112</v>
+      </c>
+      <c r="AB37" s="127">
+        <v>58.19</v>
+      </c>
+      <c r="AC37" s="127">
+        <v>9.5004000000000008</v>
+      </c>
+      <c r="AD37" s="127">
+        <v>1371.83</v>
+      </c>
+      <c r="AE37" s="127" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -3442,8 +3958,29 @@
       <c r="V38" s="124"/>
       <c r="W38" s="123"/>
       <c r="X38" s="127"/>
+      <c r="Y38" s="127">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="Z38" s="127">
+        <v>0.51919999999999999</v>
+      </c>
+      <c r="AA38" s="127">
+        <v>127</v>
+      </c>
+      <c r="AB38" s="127">
+        <v>58.88</v>
+      </c>
+      <c r="AC38" s="127">
+        <v>11.9574</v>
+      </c>
+      <c r="AD38" s="127">
+        <v>1347.44</v>
+      </c>
+      <c r="AE38" s="127" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -3486,8 +4023,29 @@
       <c r="V39" s="124"/>
       <c r="W39" s="123"/>
       <c r="X39" s="127"/>
+      <c r="Y39" s="127">
+        <v>2.21</v>
+      </c>
+      <c r="Z39" s="127">
+        <v>0.59340000000000004</v>
+      </c>
+      <c r="AA39" s="127">
+        <v>110</v>
+      </c>
+      <c r="AB39" s="127">
+        <v>54.48</v>
+      </c>
+      <c r="AC39" s="127">
+        <v>9.8055000000000003</v>
+      </c>
+      <c r="AD39" s="127">
+        <v>1129.82</v>
+      </c>
+      <c r="AE39" s="127" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -3548,8 +4106,29 @@
       <c r="X40" s="139">
         <v>574</v>
       </c>
+      <c r="Y40" s="139">
+        <v>2.4</v>
+      </c>
+      <c r="Z40" s="139">
+        <v>0.61670000000000003</v>
+      </c>
+      <c r="AA40" s="139">
+        <v>138</v>
+      </c>
+      <c r="AB40" s="139">
+        <v>52.21</v>
+      </c>
+      <c r="AC40" s="139">
+        <v>11.1843</v>
+      </c>
+      <c r="AD40" s="139">
+        <v>1201.3</v>
+      </c>
+      <c r="AE40" s="139" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -3610,8 +4189,29 @@
       <c r="X41" s="139">
         <v>817</v>
       </c>
+      <c r="Y41" s="139">
+        <v>2.12</v>
+      </c>
+      <c r="Z41" s="139">
+        <v>0.60489999999999999</v>
+      </c>
+      <c r="AA41" s="139">
+        <v>134</v>
+      </c>
+      <c r="AB41" s="139">
+        <v>63.87</v>
+      </c>
+      <c r="AC41" s="139">
+        <v>12.145300000000001</v>
+      </c>
+      <c r="AD41" s="139">
+        <v>1280.06</v>
+      </c>
+      <c r="AE41" s="139" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -3672,8 +4272,29 @@
       <c r="X42" s="139">
         <v>751</v>
       </c>
+      <c r="Y42" s="139">
+        <v>2.8</v>
+      </c>
+      <c r="Z42" s="139">
+        <v>0.76349999999999996</v>
+      </c>
+      <c r="AA42" s="139">
+        <v>129</v>
+      </c>
+      <c r="AB42" s="139">
+        <v>62.27</v>
+      </c>
+      <c r="AC42" s="139">
+        <v>11.507</v>
+      </c>
+      <c r="AD42" s="139">
+        <v>1266.1500000000001</v>
+      </c>
+      <c r="AE42" s="139" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="43" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -3716,8 +4337,30 @@
       <c r="V43" s="147"/>
       <c r="W43" s="147"/>
       <c r="X43" s="148"/>
+      <c r="Y43" s="148">
+        <v>1.97</v>
+      </c>
+      <c r="Z43" s="148">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="AA43" s="148">
+        <v>125</v>
+      </c>
+      <c r="AB43" s="148">
+        <v>53.07</v>
+      </c>
+      <c r="AC43" s="148">
+        <v>10.924200000000001</v>
+      </c>
+      <c r="AD43" s="148">
+        <v>1274.79</v>
+      </c>
+      <c r="AE43" s="148" t="s">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/BD Cobre.xlsx
+++ b/BD Cobre.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="35">
   <si>
     <t>id</t>
   </si>
@@ -123,76 +123,7 @@
     <t>adherido</t>
   </si>
   <si>
-    <t>506,21</t>
-  </si>
-  <si>
-    <t>166,65</t>
-  </si>
-  <si>
-    <t>330,50</t>
-  </si>
-  <si>
-    <t>317,26</t>
-  </si>
-  <si>
-    <t>151,55</t>
-  </si>
-  <si>
-    <t>202,84</t>
-  </si>
-  <si>
-    <t>553,50</t>
-  </si>
-  <si>
-    <t>510,23</t>
-  </si>
-  <si>
-    <t>499,54</t>
-  </si>
-  <si>
-    <t>602,80</t>
-  </si>
-  <si>
-    <t>451,20</t>
-  </si>
-  <si>
-    <t>646,10</t>
-  </si>
-  <si>
-    <t>283,64</t>
-  </si>
-  <si>
-    <t>512,02</t>
-  </si>
-  <si>
-    <t>232,64</t>
-  </si>
-  <si>
-    <t>298,00</t>
-  </si>
-  <si>
-    <t>219,90</t>
-  </si>
-  <si>
-    <t>495,33</t>
-  </si>
-  <si>
-    <t>748,86</t>
-  </si>
-  <si>
-    <t>426,74</t>
-  </si>
-  <si>
-    <t>569,88</t>
-  </si>
-  <si>
-    <t>342,04</t>
-  </si>
-  <si>
-    <t>198,64</t>
-  </si>
-  <si>
-    <t>366,62</t>
+    <t>EE</t>
   </si>
 </sst>
 </file>
@@ -1469,13 +1400,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE43"/>
+  <dimension ref="A1:AF43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1569,8 +1500,11 @@
       <c r="AE1" s="168" t="s">
         <v>33</v>
       </c>
+      <c r="AF1" s="168" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1626,7 +1560,7 @@
       <c r="W2" s="9"/>
       <c r="X2" s="11"/>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1668,7 +1602,7 @@
       <c r="W3" s="14"/>
       <c r="X3" s="15"/>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1710,7 +1644,7 @@
       <c r="W4" s="14"/>
       <c r="X4" s="15"/>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1766,7 +1700,7 @@
       <c r="W5" s="18"/>
       <c r="X5" s="20"/>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1822,7 +1756,7 @@
       <c r="W6" s="18"/>
       <c r="X6" s="20"/>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1878,7 +1812,7 @@
       <c r="W7" s="18"/>
       <c r="X7" s="20"/>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1934,7 +1868,7 @@
       <c r="W8" s="25"/>
       <c r="X8" s="26"/>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1990,7 +1924,7 @@
       <c r="W9" s="25"/>
       <c r="X9" s="26"/>
     </row>
-    <row r="10" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -2046,7 +1980,7 @@
       <c r="W10" s="29"/>
       <c r="X10" s="30"/>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2106,7 +2040,7 @@
       <c r="W11" s="34"/>
       <c r="X11" s="36"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -2166,7 +2100,7 @@
       <c r="W12" s="40"/>
       <c r="X12" s="42"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2208,7 +2142,7 @@
       <c r="W13" s="40"/>
       <c r="X13" s="42"/>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2268,7 +2202,7 @@
       <c r="W14" s="46"/>
       <c r="X14" s="48"/>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2328,7 +2262,7 @@
       <c r="W15" s="46"/>
       <c r="X15" s="48"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -2386,7 +2320,7 @@
       <c r="W16" s="46"/>
       <c r="X16" s="48"/>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -2446,7 +2380,7 @@
       <c r="W17" s="53"/>
       <c r="X17" s="55"/>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2506,7 +2440,7 @@
       <c r="W18" s="53"/>
       <c r="X18" s="55"/>
     </row>
-    <row r="19" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -2566,7 +2500,7 @@
       <c r="W19" s="60"/>
       <c r="X19" s="62"/>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -2592,7 +2526,9 @@
         <v>37.5</v>
       </c>
       <c r="I20" s="64"/>
-      <c r="J20" s="67"/>
+      <c r="J20" s="67">
+        <v>0</v>
+      </c>
       <c r="K20" s="64"/>
       <c r="L20" s="64"/>
       <c r="M20" s="64"/>
@@ -2644,11 +2580,15 @@
       <c r="AD20" s="69">
         <v>1565.5</v>
       </c>
-      <c r="AE20" s="69" t="s">
-        <v>46</v>
+      <c r="AE20" s="69">
+        <v>283.64</v>
+      </c>
+      <c r="AF20">
+        <f>T20/Y20</f>
+        <v>3.3454545454545452</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -2674,7 +2614,9 @@
         <v>48.863636399999997</v>
       </c>
       <c r="I21" s="71"/>
-      <c r="J21" s="74"/>
+      <c r="J21" s="74">
+        <v>0</v>
+      </c>
       <c r="K21" s="71"/>
       <c r="L21" s="71"/>
       <c r="M21" s="71"/>
@@ -2725,11 +2667,15 @@
       <c r="AD21" s="77">
         <v>1970</v>
       </c>
-      <c r="AE21" s="77" t="s">
-        <v>47</v>
+      <c r="AE21" s="77">
+        <v>512.02</v>
+      </c>
+      <c r="AF21">
+        <f t="shared" ref="AF21:AF43" si="0">T21/Y21</f>
+        <v>4.661458333333333</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -2755,7 +2701,9 @@
         <v>20.454545499999998</v>
       </c>
       <c r="I22" s="71"/>
-      <c r="J22" s="74"/>
+      <c r="J22" s="74">
+        <v>0</v>
+      </c>
       <c r="K22" s="71"/>
       <c r="L22" s="71"/>
       <c r="M22" s="71"/>
@@ -2807,11 +2755,15 @@
       <c r="AD22" s="77">
         <v>976.6</v>
       </c>
-      <c r="AE22" s="77" t="s">
-        <v>48</v>
+      <c r="AE22" s="77">
+        <v>232.64</v>
+      </c>
+      <c r="AF22">
+        <f t="shared" si="0"/>
+        <v>12.129186602870815</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -2837,7 +2789,9 @@
         <v>37.5</v>
       </c>
       <c r="I23" s="71"/>
-      <c r="J23" s="74"/>
+      <c r="J23" s="74">
+        <v>0</v>
+      </c>
       <c r="K23" s="71"/>
       <c r="L23" s="71"/>
       <c r="M23" s="71"/>
@@ -2880,11 +2834,11 @@
       <c r="AD23" s="77">
         <v>1405.3</v>
       </c>
-      <c r="AE23" s="77" t="s">
-        <v>49</v>
+      <c r="AE23" s="77">
+        <v>298</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -2910,7 +2864,9 @@
         <v>42.045454599999999</v>
       </c>
       <c r="I24" s="80"/>
-      <c r="J24" s="83"/>
+      <c r="J24" s="83">
+        <v>0</v>
+      </c>
       <c r="K24" s="80"/>
       <c r="L24" s="80"/>
       <c r="M24" s="80"/>
@@ -2944,11 +2900,11 @@
       <c r="AD24" s="84">
         <v>1347.49</v>
       </c>
-      <c r="AE24" s="84" t="s">
-        <v>50</v>
+      <c r="AE24" s="84">
+        <v>219.9</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -2974,7 +2930,9 @@
         <v>51.136363699999997</v>
       </c>
       <c r="I25" s="80"/>
-      <c r="J25" s="83"/>
+      <c r="J25" s="83">
+        <v>0</v>
+      </c>
       <c r="K25" s="80"/>
       <c r="L25" s="80"/>
       <c r="M25" s="80"/>
@@ -3007,11 +2965,11 @@
       <c r="AD25" s="84">
         <v>1340.09</v>
       </c>
-      <c r="AE25" s="84" t="s">
-        <v>51</v>
+      <c r="AE25" s="84">
+        <v>495.33</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -3037,7 +2995,9 @@
         <v>40.340909099999998</v>
       </c>
       <c r="I26" s="80"/>
-      <c r="J26" s="83"/>
+      <c r="J26" s="83">
+        <v>0</v>
+      </c>
       <c r="K26" s="80"/>
       <c r="L26" s="80"/>
       <c r="M26" s="80"/>
@@ -3070,11 +3030,11 @@
       <c r="AD26" s="84">
         <v>1229.77</v>
       </c>
-      <c r="AE26" s="84" t="s">
-        <v>52</v>
+      <c r="AE26" s="84">
+        <v>748.86</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -3100,7 +3060,9 @@
         <v>40.340909099999998</v>
       </c>
       <c r="I27" s="80"/>
-      <c r="J27" s="83"/>
+      <c r="J27" s="83">
+        <v>0</v>
+      </c>
       <c r="K27" s="80"/>
       <c r="L27" s="80"/>
       <c r="M27" s="80"/>
@@ -3133,11 +3095,11 @@
       <c r="AD27" s="84">
         <v>1411.55</v>
       </c>
-      <c r="AE27" s="84" t="s">
-        <v>53</v>
+      <c r="AE27" s="84">
+        <v>426.74</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -3163,7 +3125,9 @@
         <v>40.909090900000002</v>
       </c>
       <c r="I28" s="87"/>
-      <c r="J28" s="90"/>
+      <c r="J28" s="90">
+        <v>0</v>
+      </c>
       <c r="K28" s="87"/>
       <c r="L28" s="87"/>
       <c r="M28" s="87"/>
@@ -3214,11 +3178,15 @@
       <c r="AD28" s="93">
         <v>1313.02</v>
       </c>
-      <c r="AE28" s="93" t="s">
-        <v>54</v>
+      <c r="AE28" s="93">
+        <v>569.88</v>
+      </c>
+      <c r="AF28">
+        <f t="shared" si="0"/>
+        <v>13.391304347826088</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -3244,7 +3212,9 @@
         <v>33.5227273</v>
       </c>
       <c r="I29" s="87"/>
-      <c r="J29" s="90"/>
+      <c r="J29" s="90">
+        <v>0</v>
+      </c>
       <c r="K29" s="87"/>
       <c r="L29" s="87"/>
       <c r="M29" s="87"/>
@@ -3295,11 +3265,15 @@
       <c r="AD29" s="93">
         <v>1361.88</v>
       </c>
-      <c r="AE29" s="93" t="s">
-        <v>55</v>
+      <c r="AE29" s="93">
+        <v>342.04</v>
+      </c>
+      <c r="AF29">
+        <f t="shared" si="0"/>
+        <v>9.7732997481108299</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -3325,7 +3299,9 @@
         <v>39.7727273</v>
       </c>
       <c r="I30" s="87"/>
-      <c r="J30" s="90"/>
+      <c r="J30" s="90">
+        <v>0</v>
+      </c>
       <c r="K30" s="87"/>
       <c r="L30" s="87"/>
       <c r="M30" s="87"/>
@@ -3376,11 +3352,15 @@
       <c r="AD30" s="93">
         <v>1263.72</v>
       </c>
-      <c r="AE30" s="93" t="s">
-        <v>56</v>
+      <c r="AE30" s="93">
+        <v>198.64</v>
+      </c>
+      <c r="AF30">
+        <f t="shared" si="0"/>
+        <v>2.8120063191153237</v>
       </c>
     </row>
-    <row r="31" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -3406,7 +3386,9 @@
         <v>39.7727273</v>
       </c>
       <c r="I31" s="99"/>
-      <c r="J31" s="100"/>
+      <c r="J31" s="100">
+        <v>0</v>
+      </c>
       <c r="K31" s="96"/>
       <c r="L31" s="96"/>
       <c r="M31" s="96"/>
@@ -3457,11 +3439,15 @@
       <c r="AD31" s="103">
         <v>1253.58</v>
       </c>
-      <c r="AE31" s="103" t="s">
-        <v>57</v>
+      <c r="AE31" s="103">
+        <v>366.62</v>
+      </c>
+      <c r="AF31">
+        <f t="shared" si="0"/>
+        <v>10.293255131964809</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -3540,11 +3526,15 @@
       <c r="AD32" s="111">
         <v>1207.1500000000001</v>
       </c>
-      <c r="AE32" s="111" t="s">
-        <v>34</v>
+      <c r="AE32" s="111">
+        <v>506.21</v>
+      </c>
+      <c r="AF32">
+        <f t="shared" si="0"/>
+        <v>6.6386554621848743</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -3623,11 +3613,15 @@
       <c r="AD33" s="119">
         <v>1222.1400000000001</v>
       </c>
-      <c r="AE33" s="119" t="s">
-        <v>35</v>
+      <c r="AE33" s="119">
+        <v>166.65</v>
+      </c>
+      <c r="AF33">
+        <f t="shared" si="0"/>
+        <v>3.4156378600823043</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -3706,11 +3700,15 @@
       <c r="AD34" s="119">
         <v>1093.95</v>
       </c>
-      <c r="AE34" s="119" t="s">
-        <v>36</v>
+      <c r="AE34" s="119">
+        <v>330.5</v>
+      </c>
+      <c r="AF34">
+        <f t="shared" si="0"/>
+        <v>4.1515151515151514</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -3781,11 +3779,15 @@
       <c r="AD35" s="121">
         <v>1343.07</v>
       </c>
-      <c r="AE35" s="121" t="s">
-        <v>37</v>
+      <c r="AE35" s="121">
+        <v>317.26</v>
+      </c>
+      <c r="AF35">
+        <f t="shared" si="0"/>
+        <v>7.890995260663507</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -3846,11 +3848,11 @@
       <c r="AD36" s="127">
         <v>1313.44</v>
       </c>
-      <c r="AE36" s="127" t="s">
-        <v>38</v>
+      <c r="AE36" s="127">
+        <v>151.55000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -3911,11 +3913,11 @@
       <c r="AD37" s="127">
         <v>1371.83</v>
       </c>
-      <c r="AE37" s="127" t="s">
-        <v>39</v>
+      <c r="AE37" s="127">
+        <v>202.84</v>
       </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -3976,11 +3978,11 @@
       <c r="AD38" s="127">
         <v>1347.44</v>
       </c>
-      <c r="AE38" s="127" t="s">
-        <v>40</v>
+      <c r="AE38" s="127">
+        <v>553.5</v>
       </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -4041,11 +4043,11 @@
       <c r="AD39" s="127">
         <v>1129.82</v>
       </c>
-      <c r="AE39" s="127" t="s">
-        <v>41</v>
+      <c r="AE39" s="127">
+        <v>510.23</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -4124,11 +4126,15 @@
       <c r="AD40" s="139">
         <v>1201.3</v>
       </c>
-      <c r="AE40" s="139" t="s">
-        <v>42</v>
+      <c r="AE40" s="139">
+        <v>499.54</v>
+      </c>
+      <c r="AF40">
+        <f t="shared" si="0"/>
+        <v>11.666666666666668</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -4207,11 +4213,15 @@
       <c r="AD41" s="139">
         <v>1280.06</v>
       </c>
-      <c r="AE41" s="139" t="s">
-        <v>43</v>
+      <c r="AE41" s="139">
+        <v>602.79999999999995</v>
+      </c>
+      <c r="AF41">
+        <f t="shared" si="0"/>
+        <v>17.40566037735849</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -4290,11 +4300,15 @@
       <c r="AD42" s="139">
         <v>1266.1500000000001</v>
       </c>
-      <c r="AE42" s="139" t="s">
-        <v>44</v>
+      <c r="AE42" s="139">
+        <v>451.2</v>
+      </c>
+      <c r="AF42">
+        <f t="shared" si="0"/>
+        <v>10.571428571428573</v>
       </c>
     </row>
-    <row r="43" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -4355,8 +4369,8 @@
       <c r="AD43" s="148">
         <v>1274.79</v>
       </c>
-      <c r="AE43" s="148" t="s">
-        <v>45</v>
+      <c r="AE43" s="148">
+        <v>646.1</v>
       </c>
     </row>
   </sheetData>

--- a/BD Cobre.xlsx
+++ b/BD Cobre.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="236"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="37">
   <si>
     <t>id</t>
   </si>
@@ -87,9 +87,6 @@
     <t>PSuelo</t>
   </si>
   <si>
-    <t>Pvastago</t>
-  </si>
-  <si>
     <t>PRaiz</t>
   </si>
   <si>
@@ -124,6 +121,15 @@
   </si>
   <si>
     <t>EE</t>
+  </si>
+  <si>
+    <t>PStotal</t>
+  </si>
+  <si>
+    <t>PVastago</t>
+  </si>
+  <si>
+    <t>in vitro</t>
   </si>
 </sst>
 </file>
@@ -621,7 +627,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="169">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -711,9 +717,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -729,9 +732,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -747,9 +747,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -768,9 +765,6 @@
     <xf numFmtId="2" fontId="3" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -784,9 +778,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1119,6 +1110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1392,7 +1384,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1400,13 +1392,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AF43"/>
+  <dimension ref="A1:AG43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1420,10 +1412,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>4</v>
@@ -1465,7 +1457,7 @@
         <v>19</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U1" s="5" t="s">
         <v>20</v>
@@ -1474,37 +1466,40 @@
         <v>21</v>
       </c>
       <c r="W1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="X1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="166" t="s">
+      <c r="Y1" s="161" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z1" s="161" t="s">
         <v>27</v>
       </c>
-      <c r="Z1" s="166" t="s">
+      <c r="AA1" s="161" t="s">
         <v>28</v>
       </c>
-      <c r="AA1" s="166" t="s">
+      <c r="AB1" s="161" t="s">
         <v>29</v>
       </c>
-      <c r="AB1" s="166" t="s">
+      <c r="AC1" s="161" t="s">
         <v>30</v>
       </c>
-      <c r="AC1" s="166" t="s">
+      <c r="AD1" s="162" t="s">
         <v>31</v>
       </c>
-      <c r="AD1" s="167" t="s">
+      <c r="AE1" s="163" t="s">
         <v>32</v>
       </c>
-      <c r="AE1" s="168" t="s">
+      <c r="AF1" s="163" t="s">
         <v>33</v>
       </c>
-      <c r="AF1" s="168" t="s">
+      <c r="AG1" s="163" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1560,7 +1555,7 @@
       <c r="W2" s="9"/>
       <c r="X2" s="11"/>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1602,12 +1597,12 @@
       <c r="W3" s="14"/>
       <c r="X3" s="15"/>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C4" s="12">
         <v>0</v>
@@ -1644,12 +1639,12 @@
       <c r="W4" s="14"/>
       <c r="X4" s="15"/>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C5" s="16">
         <v>0</v>
@@ -1700,12 +1695,12 @@
       <c r="W5" s="18"/>
       <c r="X5" s="20"/>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C6" s="16">
         <v>0</v>
@@ -1756,12 +1751,12 @@
       <c r="W6" s="18"/>
       <c r="X6" s="20"/>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C7" s="16">
         <v>0</v>
@@ -1812,12 +1807,12 @@
       <c r="W7" s="18"/>
       <c r="X7" s="20"/>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C8" s="21">
         <v>0</v>
@@ -1868,12 +1863,12 @@
       <c r="W8" s="25"/>
       <c r="X8" s="26"/>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C9" s="21">
         <v>0</v>
@@ -1924,12 +1919,12 @@
       <c r="W9" s="25"/>
       <c r="X9" s="26"/>
     </row>
-    <row r="10" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C10" s="23">
         <v>0</v>
@@ -1980,2397 +1975,2493 @@
       <c r="W10" s="29"/>
       <c r="X10" s="30"/>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="32">
+        <v>36</v>
+      </c>
+      <c r="C11" s="31">
         <v>1</v>
       </c>
-      <c r="D11" s="32">
-        <v>0</v>
-      </c>
-      <c r="E11" s="33">
+      <c r="D11" s="31">
+        <v>0</v>
+      </c>
+      <c r="E11" s="32">
         <v>95.35</v>
       </c>
-      <c r="F11" s="33">
+      <c r="F11" s="32">
         <v>42.68</v>
       </c>
-      <c r="G11" s="33">
+      <c r="G11" s="32">
         <v>4.2946708463949852</v>
       </c>
-      <c r="H11" s="33">
+      <c r="H11" s="32">
         <v>20.956521739130434</v>
       </c>
-      <c r="I11" s="34">
+      <c r="I11" s="33">
         <v>100</v>
       </c>
-      <c r="J11" s="34">
+      <c r="J11" s="33">
         <v>62.7</v>
       </c>
-      <c r="K11" s="35">
+      <c r="K11" s="34">
         <v>2.6</v>
       </c>
-      <c r="L11" s="35">
+      <c r="L11" s="34">
         <v>53</v>
       </c>
-      <c r="M11" s="35">
+      <c r="M11" s="34">
         <v>48</v>
       </c>
-      <c r="N11" s="35">
+      <c r="N11" s="34">
         <v>29</v>
       </c>
-      <c r="O11" s="35">
+      <c r="O11" s="34">
         <v>30</v>
       </c>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="32"/>
-      <c r="R11" s="32"/>
-      <c r="S11" s="35">
+      <c r="P11" s="31"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="34">
         <v>99</v>
       </c>
-      <c r="T11" s="150"/>
-      <c r="U11" s="160"/>
-      <c r="V11" s="155">
+      <c r="T11" s="145"/>
+      <c r="U11" s="155"/>
+      <c r="V11" s="150">
         <v>410</v>
       </c>
-      <c r="W11" s="34"/>
-      <c r="X11" s="36"/>
+      <c r="W11" s="33"/>
+      <c r="X11" s="35"/>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="38">
+      <c r="B12" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="36">
         <v>1</v>
       </c>
-      <c r="D12" s="38">
-        <v>0</v>
-      </c>
-      <c r="E12" s="39">
+      <c r="D12" s="36">
+        <v>0</v>
+      </c>
+      <c r="E12" s="37">
         <v>87.8</v>
       </c>
-      <c r="F12" s="39">
+      <c r="F12" s="37">
         <v>58.59</v>
       </c>
-      <c r="G12" s="39">
+      <c r="G12" s="37">
         <v>4.0125391849529786</v>
       </c>
-      <c r="H12" s="39">
+      <c r="H12" s="37">
         <v>23.043478260869566</v>
       </c>
-      <c r="I12" s="40">
+      <c r="I12" s="38">
         <v>168</v>
       </c>
-      <c r="J12" s="40">
+      <c r="J12" s="38">
         <v>101</v>
       </c>
-      <c r="K12" s="41">
+      <c r="K12" s="39">
         <v>2.7</v>
       </c>
-      <c r="L12" s="41">
+      <c r="L12" s="39">
         <v>45</v>
       </c>
-      <c r="M12" s="41">
+      <c r="M12" s="39">
         <v>42</v>
       </c>
-      <c r="N12" s="41">
+      <c r="N12" s="39">
         <v>27</v>
       </c>
-      <c r="O12" s="41">
+      <c r="O12" s="39">
         <v>30</v>
       </c>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="41">
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
+      <c r="S12" s="39">
         <v>101</v>
       </c>
-      <c r="T12" s="151"/>
-      <c r="U12" s="161"/>
-      <c r="V12" s="156">
+      <c r="T12" s="146"/>
+      <c r="U12" s="156"/>
+      <c r="V12" s="151">
         <v>450</v>
       </c>
-      <c r="W12" s="40"/>
-      <c r="X12" s="42"/>
+      <c r="W12" s="38"/>
+      <c r="X12" s="40"/>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="38">
+      <c r="B13" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="36">
         <v>1</v>
       </c>
-      <c r="D13" s="38">
-        <v>0</v>
-      </c>
-      <c r="E13" s="39">
+      <c r="D13" s="36">
+        <v>0</v>
+      </c>
+      <c r="E13" s="37">
         <v>90.25</v>
       </c>
-      <c r="F13" s="39">
+      <c r="F13" s="37">
         <v>47.6</v>
       </c>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="40">
+      <c r="G13" s="37"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="38">
         <v>154</v>
       </c>
-      <c r="J13" s="40">
+      <c r="J13" s="38">
         <v>88.5</v>
       </c>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="38"/>
-      <c r="P13" s="38"/>
-      <c r="Q13" s="38"/>
-      <c r="R13" s="38"/>
-      <c r="S13" s="38"/>
-      <c r="T13" s="151"/>
-      <c r="U13" s="161"/>
-      <c r="V13" s="156"/>
-      <c r="W13" s="40"/>
-      <c r="X13" s="42"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
+      <c r="S13" s="36"/>
+      <c r="T13" s="146"/>
+      <c r="U13" s="156"/>
+      <c r="V13" s="151"/>
+      <c r="W13" s="38"/>
+      <c r="X13" s="40"/>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="44">
+      <c r="B14" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="41">
         <v>1</v>
       </c>
-      <c r="D14" s="44">
+      <c r="D14" s="41">
         <v>1</v>
       </c>
-      <c r="E14" s="45">
+      <c r="E14" s="42">
         <v>82.93</v>
       </c>
-      <c r="F14" s="45">
+      <c r="F14" s="42">
         <v>29.41</v>
       </c>
-      <c r="G14" s="165">
+      <c r="G14" s="160">
         <v>10.501567398119123</v>
       </c>
-      <c r="H14" s="45">
+      <c r="H14" s="42">
         <v>19.434782608695652</v>
       </c>
-      <c r="I14" s="46">
+      <c r="I14" s="43">
         <v>184</v>
       </c>
-      <c r="J14" s="46">
+      <c r="J14" s="43">
         <v>124.6</v>
       </c>
-      <c r="K14" s="47">
+      <c r="K14" s="44">
         <v>2.4</v>
       </c>
-      <c r="L14" s="47">
+      <c r="L14" s="44">
         <v>89</v>
       </c>
-      <c r="M14" s="47">
+      <c r="M14" s="44">
         <v>63</v>
       </c>
-      <c r="N14" s="47">
+      <c r="N14" s="44">
         <v>30</v>
       </c>
-      <c r="O14" s="47">
+      <c r="O14" s="44">
         <v>15</v>
       </c>
-      <c r="P14" s="44"/>
-      <c r="Q14" s="44"/>
-      <c r="R14" s="44"/>
-      <c r="S14" s="47">
+      <c r="P14" s="41"/>
+      <c r="Q14" s="41"/>
+      <c r="R14" s="41"/>
+      <c r="S14" s="44">
         <v>171</v>
       </c>
-      <c r="T14" s="152"/>
-      <c r="U14" s="162"/>
-      <c r="V14" s="157">
+      <c r="T14" s="147"/>
+      <c r="U14" s="157"/>
+      <c r="V14" s="152">
         <v>400</v>
       </c>
-      <c r="W14" s="46"/>
-      <c r="X14" s="48"/>
+      <c r="W14" s="43"/>
+      <c r="X14" s="45"/>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="44">
+      <c r="B15" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="41">
         <v>1</v>
       </c>
-      <c r="D15" s="44">
+      <c r="D15" s="41">
         <v>1</v>
       </c>
-      <c r="E15" s="45">
+      <c r="E15" s="42">
         <v>86.84</v>
       </c>
-      <c r="F15" s="45">
+      <c r="F15" s="42">
         <v>49.39</v>
       </c>
-      <c r="G15" s="45">
+      <c r="G15" s="42">
         <v>3.949843260188088</v>
       </c>
-      <c r="H15" s="45">
+      <c r="H15" s="42">
         <v>20.521739130434781</v>
       </c>
-      <c r="I15" s="46">
+      <c r="I15" s="43">
         <v>468</v>
       </c>
-      <c r="J15" s="46">
+      <c r="J15" s="43">
         <v>202</v>
       </c>
-      <c r="K15" s="47">
+      <c r="K15" s="44">
         <v>2.5</v>
       </c>
-      <c r="L15" s="47">
+      <c r="L15" s="44">
         <v>94</v>
       </c>
-      <c r="M15" s="47">
+      <c r="M15" s="44">
         <v>61</v>
       </c>
-      <c r="N15" s="47">
+      <c r="N15" s="44">
         <v>24</v>
       </c>
-      <c r="O15" s="47">
+      <c r="O15" s="44">
         <v>30</v>
       </c>
-      <c r="P15" s="44"/>
-      <c r="Q15" s="44"/>
-      <c r="R15" s="44"/>
-      <c r="S15" s="47">
+      <c r="P15" s="41"/>
+      <c r="Q15" s="41"/>
+      <c r="R15" s="41"/>
+      <c r="S15" s="44">
         <v>208</v>
       </c>
-      <c r="T15" s="152"/>
-      <c r="U15" s="162"/>
-      <c r="V15" s="157">
+      <c r="T15" s="147"/>
+      <c r="U15" s="157"/>
+      <c r="V15" s="152">
         <v>410</v>
       </c>
-      <c r="W15" s="46"/>
-      <c r="X15" s="48"/>
+      <c r="W15" s="43"/>
+      <c r="X15" s="45"/>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="44">
+      <c r="B16" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="41">
         <v>1</v>
       </c>
-      <c r="D16" s="44">
+      <c r="D16" s="41">
         <v>1</v>
       </c>
-      <c r="E16" s="45">
+      <c r="E16" s="42">
         <v>81.39</v>
       </c>
-      <c r="F16" s="45">
+      <c r="F16" s="42">
         <v>44.29</v>
       </c>
-      <c r="G16" s="45">
+      <c r="G16" s="42">
         <v>2.7586206896551726</v>
       </c>
-      <c r="H16" s="49"/>
-      <c r="I16" s="46">
+      <c r="H16" s="46"/>
+      <c r="I16" s="43">
         <v>683</v>
       </c>
-      <c r="J16" s="46">
+      <c r="J16" s="43">
         <v>133.4</v>
       </c>
-      <c r="K16" s="47">
+      <c r="K16" s="44">
         <v>2.6</v>
       </c>
-      <c r="L16" s="47">
+      <c r="L16" s="44">
         <v>58</v>
       </c>
-      <c r="M16" s="47">
+      <c r="M16" s="44">
         <v>51</v>
       </c>
-      <c r="N16" s="47">
+      <c r="N16" s="44">
         <v>38</v>
       </c>
-      <c r="O16" s="47">
+      <c r="O16" s="44">
         <v>15</v>
       </c>
-      <c r="P16" s="44"/>
-      <c r="Q16" s="44"/>
-      <c r="R16" s="44"/>
-      <c r="S16" s="47">
+      <c r="P16" s="41"/>
+      <c r="Q16" s="41"/>
+      <c r="R16" s="41"/>
+      <c r="S16" s="44">
         <v>94</v>
       </c>
-      <c r="T16" s="152"/>
-      <c r="U16" s="162"/>
-      <c r="V16" s="157">
+      <c r="T16" s="147"/>
+      <c r="U16" s="157"/>
+      <c r="V16" s="152">
         <v>400</v>
       </c>
-      <c r="W16" s="46"/>
-      <c r="X16" s="48"/>
+      <c r="W16" s="43"/>
+      <c r="X16" s="45"/>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="51">
+      <c r="B17" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="47">
         <v>1</v>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="47">
         <v>2</v>
       </c>
-      <c r="E17" s="52">
+      <c r="E17" s="48">
         <v>85</v>
       </c>
-      <c r="F17" s="52">
+      <c r="F17" s="48">
         <v>35</v>
       </c>
-      <c r="G17" s="52">
+      <c r="G17" s="48">
         <v>3.0094043887147337</v>
       </c>
-      <c r="H17" s="52">
+      <c r="H17" s="48">
         <v>20.695652173913043</v>
       </c>
-      <c r="I17" s="53">
+      <c r="I17" s="49">
         <v>12</v>
       </c>
-      <c r="J17" s="53">
+      <c r="J17" s="49">
         <v>55.3</v>
       </c>
-      <c r="K17" s="54">
+      <c r="K17" s="50">
         <v>2.4</v>
       </c>
-      <c r="L17" s="54">
+      <c r="L17" s="50">
         <v>94</v>
       </c>
-      <c r="M17" s="54">
+      <c r="M17" s="50">
         <v>57</v>
       </c>
-      <c r="N17" s="54">
+      <c r="N17" s="50">
         <v>32</v>
       </c>
-      <c r="O17" s="54">
+      <c r="O17" s="50">
         <v>30</v>
       </c>
-      <c r="P17" s="51"/>
-      <c r="Q17" s="51"/>
-      <c r="R17" s="51"/>
-      <c r="S17" s="54">
+      <c r="P17" s="47"/>
+      <c r="Q17" s="47"/>
+      <c r="R17" s="47"/>
+      <c r="S17" s="50">
         <v>342</v>
       </c>
-      <c r="T17" s="153"/>
-      <c r="U17" s="163"/>
-      <c r="V17" s="158">
+      <c r="T17" s="148"/>
+      <c r="U17" s="158"/>
+      <c r="V17" s="153">
         <v>390</v>
       </c>
-      <c r="W17" s="53"/>
-      <c r="X17" s="55"/>
+      <c r="W17" s="49"/>
+      <c r="X17" s="51"/>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="51">
+      <c r="B18" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="47">
         <v>1</v>
       </c>
-      <c r="D18" s="51">
+      <c r="D18" s="47">
         <v>2</v>
       </c>
-      <c r="E18" s="52">
+      <c r="E18" s="48">
         <v>92.86</v>
       </c>
-      <c r="F18" s="52">
+      <c r="F18" s="48">
         <v>37.72</v>
       </c>
-      <c r="G18" s="52">
+      <c r="G18" s="48">
         <v>3.6677115987460818</v>
       </c>
-      <c r="H18" s="52">
+      <c r="H18" s="48">
         <v>22.826086956521742</v>
       </c>
-      <c r="I18" s="53">
+      <c r="I18" s="49">
         <v>6</v>
       </c>
-      <c r="J18" s="53">
+      <c r="J18" s="49">
         <v>61.9</v>
       </c>
-      <c r="K18" s="54">
+      <c r="K18" s="50">
         <v>2.5</v>
       </c>
-      <c r="L18" s="54">
+      <c r="L18" s="50">
         <v>91</v>
       </c>
-      <c r="M18" s="54">
+      <c r="M18" s="50">
         <v>68</v>
       </c>
-      <c r="N18" s="54">
+      <c r="N18" s="50">
         <v>30</v>
       </c>
-      <c r="O18" s="54">
+      <c r="O18" s="50">
         <v>30</v>
       </c>
-      <c r="P18" s="51"/>
-      <c r="Q18" s="51"/>
-      <c r="R18" s="51"/>
-      <c r="S18" s="54">
+      <c r="P18" s="47"/>
+      <c r="Q18" s="47"/>
+      <c r="R18" s="47"/>
+      <c r="S18" s="50">
         <v>248</v>
       </c>
-      <c r="T18" s="153"/>
-      <c r="U18" s="163"/>
-      <c r="V18" s="158">
+      <c r="T18" s="148"/>
+      <c r="U18" s="158"/>
+      <c r="V18" s="153">
         <v>390</v>
       </c>
-      <c r="W18" s="53"/>
-      <c r="X18" s="55"/>
+      <c r="W18" s="49"/>
+      <c r="X18" s="51"/>
     </row>
-    <row r="19" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="57">
+      <c r="B19" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="52">
         <v>1</v>
       </c>
-      <c r="D19" s="57">
+      <c r="D19" s="52">
         <v>2</v>
       </c>
-      <c r="E19" s="58">
+      <c r="E19" s="53">
         <v>92.31</v>
       </c>
-      <c r="F19" s="58">
+      <c r="F19" s="53">
         <v>48.67</v>
       </c>
-      <c r="G19" s="58">
+      <c r="G19" s="53">
         <v>4.5454545454545459</v>
       </c>
-      <c r="H19" s="58">
+      <c r="H19" s="53">
         <v>20.913043478260871</v>
       </c>
-      <c r="I19" s="59">
+      <c r="I19" s="54">
         <v>8</v>
       </c>
-      <c r="J19" s="60">
+      <c r="J19" s="55">
         <v>92.9</v>
       </c>
-      <c r="K19" s="61">
+      <c r="K19" s="56">
         <v>2.2999999999999998</v>
       </c>
-      <c r="L19" s="61">
+      <c r="L19" s="56">
         <v>91</v>
       </c>
-      <c r="M19" s="61">
+      <c r="M19" s="56">
         <v>30</v>
       </c>
-      <c r="N19" s="61">
+      <c r="N19" s="56">
         <v>25</v>
       </c>
-      <c r="O19" s="61">
+      <c r="O19" s="56">
         <v>40</v>
       </c>
-      <c r="P19" s="57"/>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="57"/>
-      <c r="S19" s="61">
+      <c r="P19" s="52"/>
+      <c r="Q19" s="52"/>
+      <c r="R19" s="52"/>
+      <c r="S19" s="56">
         <v>306</v>
       </c>
-      <c r="T19" s="154"/>
-      <c r="U19" s="164"/>
-      <c r="V19" s="159">
+      <c r="T19" s="149"/>
+      <c r="U19" s="159"/>
+      <c r="V19" s="154">
         <v>310</v>
       </c>
-      <c r="W19" s="60"/>
-      <c r="X19" s="62"/>
+      <c r="W19" s="55"/>
+      <c r="X19" s="57"/>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="63" t="s">
+      <c r="B20" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="64">
-        <v>0</v>
-      </c>
-      <c r="D20" s="64">
-        <v>0</v>
-      </c>
-      <c r="E20" s="64">
-        <v>0</v>
-      </c>
-      <c r="F20" s="64">
-        <v>0</v>
-      </c>
-      <c r="G20" s="65">
+      <c r="C20" s="59">
+        <v>0</v>
+      </c>
+      <c r="D20" s="59">
+        <v>0</v>
+      </c>
+      <c r="E20" s="59">
+        <v>0</v>
+      </c>
+      <c r="F20" s="59">
+        <v>0</v>
+      </c>
+      <c r="G20" s="60">
         <v>47.480620199999997</v>
       </c>
-      <c r="H20" s="66">
+      <c r="H20" s="61">
         <v>37.5</v>
       </c>
-      <c r="I20" s="64"/>
-      <c r="J20" s="67">
-        <v>0</v>
-      </c>
-      <c r="K20" s="64"/>
-      <c r="L20" s="64"/>
-      <c r="M20" s="64"/>
-      <c r="N20" s="64"/>
-      <c r="O20" s="64"/>
-      <c r="P20" s="65">
+      <c r="I20" s="59"/>
+      <c r="J20" s="62">
+        <v>0</v>
+      </c>
+      <c r="K20" s="59"/>
+      <c r="L20" s="59"/>
+      <c r="M20" s="59"/>
+      <c r="N20" s="59"/>
+      <c r="O20" s="59"/>
+      <c r="P20" s="60">
         <v>0.44742728999999998</v>
       </c>
-      <c r="Q20" s="65">
+      <c r="Q20" s="60">
         <v>0.41163311000000002</v>
       </c>
-      <c r="R20" s="65">
+      <c r="R20" s="60">
         <v>0.92</v>
       </c>
-      <c r="S20" s="68">
+      <c r="S20" s="63">
         <v>44.7</v>
       </c>
-      <c r="T20" s="68">
+      <c r="T20" s="63">
         <v>18.399999999999999</v>
       </c>
-      <c r="U20" s="149">
+      <c r="U20" s="144">
         <v>20</v>
       </c>
-      <c r="V20" s="68">
+      <c r="V20" s="63">
         <v>662.5</v>
       </c>
-      <c r="W20" s="68">
+      <c r="W20" s="63">
         <v>599</v>
       </c>
-      <c r="X20" s="69">
+      <c r="X20" s="64">
         <v>100</v>
       </c>
-      <c r="Y20" s="69">
+      <c r="Y20" s="64">
         <v>5.5</v>
       </c>
-      <c r="Z20" s="69">
+      <c r="Z20" s="64">
         <v>1.1176999999999999</v>
       </c>
-      <c r="AA20" s="69">
+      <c r="AA20" s="64">
         <v>134</v>
       </c>
-      <c r="AB20" s="69">
+      <c r="AB20" s="64">
         <f>66.01+0.26</f>
         <v>66.27000000000001</v>
       </c>
-      <c r="AC20" s="69">
+      <c r="AC20" s="64">
         <v>12.5967</v>
       </c>
-      <c r="AD20" s="69">
+      <c r="AD20" s="64">
         <v>1565.5</v>
       </c>
-      <c r="AE20" s="69">
+      <c r="AE20" s="64">
         <v>283.64</v>
       </c>
       <c r="AF20">
         <f>T20/Y20</f>
         <v>3.3454545454545452</v>
       </c>
+      <c r="AG20" s="164">
+        <f>Z20+AC20</f>
+        <v>13.714399999999999</v>
+      </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="70" t="s">
+      <c r="B21" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="71">
-        <v>0</v>
-      </c>
-      <c r="D21" s="71">
-        <v>0</v>
-      </c>
-      <c r="E21" s="71">
-        <v>0</v>
-      </c>
-      <c r="F21" s="71">
-        <v>0</v>
-      </c>
-      <c r="G21" s="72">
+      <c r="C21" s="66">
+        <v>0</v>
+      </c>
+      <c r="D21" s="66">
+        <v>0</v>
+      </c>
+      <c r="E21" s="66">
+        <v>0</v>
+      </c>
+      <c r="F21" s="66">
+        <v>0</v>
+      </c>
+      <c r="G21" s="67">
         <v>49.418604700000003</v>
       </c>
-      <c r="H21" s="73">
+      <c r="H21" s="68">
         <v>48.863636399999997</v>
       </c>
-      <c r="I21" s="71"/>
-      <c r="J21" s="74">
-        <v>0</v>
-      </c>
-      <c r="K21" s="71"/>
-      <c r="L21" s="71"/>
-      <c r="M21" s="71"/>
-      <c r="N21" s="71"/>
-      <c r="O21" s="71"/>
-      <c r="P21" s="72">
+      <c r="I21" s="66"/>
+      <c r="J21" s="69">
+        <v>0</v>
+      </c>
+      <c r="K21" s="66"/>
+      <c r="L21" s="66"/>
+      <c r="M21" s="66"/>
+      <c r="N21" s="66"/>
+      <c r="O21" s="66"/>
+      <c r="P21" s="67">
         <v>0.25917927000000002</v>
       </c>
-      <c r="Q21" s="72">
+      <c r="Q21" s="67">
         <v>0.38660907</v>
       </c>
-      <c r="R21" s="72">
+      <c r="R21" s="67">
         <v>1.4916666700000001</v>
       </c>
-      <c r="S21" s="75">
+      <c r="S21" s="70">
         <v>46.3</v>
       </c>
-      <c r="T21" s="75">
+      <c r="T21" s="70">
         <v>17.899999999999999</v>
       </c>
-      <c r="U21" s="76">
+      <c r="U21" s="71">
         <v>12</v>
       </c>
-      <c r="V21" s="75">
+      <c r="V21" s="70">
         <v>632</v>
       </c>
-      <c r="W21" s="75">
+      <c r="W21" s="70">
         <v>104</v>
       </c>
-      <c r="X21" s="77">
+      <c r="X21" s="72">
         <v>110</v>
       </c>
-      <c r="Y21" s="77">
+      <c r="Y21" s="72">
         <v>3.84</v>
       </c>
-      <c r="Z21" s="77">
+      <c r="Z21" s="72">
         <v>1.0099</v>
       </c>
-      <c r="AA21" s="77">
+      <c r="AA21" s="72">
         <v>137</v>
       </c>
-      <c r="AB21" s="77">
+      <c r="AB21" s="72">
         <v>63.34</v>
       </c>
-      <c r="AC21" s="77">
+      <c r="AC21" s="72">
         <v>12.082800000000001</v>
       </c>
-      <c r="AD21" s="77">
+      <c r="AD21" s="72">
         <v>1970</v>
       </c>
-      <c r="AE21" s="77">
+      <c r="AE21" s="72">
         <v>512.02</v>
       </c>
       <c r="AF21">
-        <f t="shared" ref="AF21:AF43" si="0">T21/Y21</f>
+        <f t="shared" ref="AF21:AF42" si="0">T21/Y21</f>
         <v>4.661458333333333</v>
       </c>
+      <c r="AG21" s="164">
+        <f t="shared" ref="AG21:AG43" si="1">Z21+AC21</f>
+        <v>13.092700000000001</v>
+      </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="70" t="s">
+      <c r="B22" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="71">
-        <v>0</v>
-      </c>
-      <c r="D22" s="71">
-        <v>0</v>
-      </c>
-      <c r="E22" s="71">
-        <v>0</v>
-      </c>
-      <c r="F22" s="71">
-        <v>0</v>
-      </c>
-      <c r="G22" s="72">
+      <c r="C22" s="66">
+        <v>0</v>
+      </c>
+      <c r="D22" s="66">
+        <v>0</v>
+      </c>
+      <c r="E22" s="66">
+        <v>0</v>
+      </c>
+      <c r="F22" s="66">
+        <v>0</v>
+      </c>
+      <c r="G22" s="67">
         <v>57.170542699999999</v>
       </c>
-      <c r="H22" s="73">
+      <c r="H22" s="68">
         <v>20.454545499999998</v>
       </c>
-      <c r="I22" s="71"/>
-      <c r="J22" s="74">
-        <v>0</v>
-      </c>
-      <c r="K22" s="71"/>
-      <c r="L22" s="71"/>
-      <c r="M22" s="71"/>
-      <c r="N22" s="71"/>
-      <c r="O22" s="71"/>
-      <c r="P22" s="72">
+      <c r="I22" s="66"/>
+      <c r="J22" s="69">
+        <v>0</v>
+      </c>
+      <c r="K22" s="66"/>
+      <c r="L22" s="66"/>
+      <c r="M22" s="66"/>
+      <c r="N22" s="66"/>
+      <c r="O22" s="66"/>
+      <c r="P22" s="67">
         <v>0.28021015999999999</v>
       </c>
-      <c r="Q22" s="72">
+      <c r="Q22" s="67">
         <v>0.88791593999999996</v>
       </c>
-      <c r="R22" s="72">
+      <c r="R22" s="67">
         <v>3.1687500000000002</v>
       </c>
-      <c r="S22" s="75">
+      <c r="S22" s="70">
         <v>57.1</v>
       </c>
-      <c r="T22" s="75">
+      <c r="T22" s="70">
         <v>50.7</v>
       </c>
-      <c r="U22" s="76">
+      <c r="U22" s="71">
         <v>16</v>
       </c>
-      <c r="V22" s="75">
+      <c r="V22" s="70">
         <v>693</v>
       </c>
-      <c r="W22" s="75">
+      <c r="W22" s="70">
         <v>804</v>
       </c>
-      <c r="X22" s="77">
+      <c r="X22" s="72">
         <v>191</v>
       </c>
-      <c r="Y22" s="77">
+      <c r="Y22" s="72">
         <v>4.18</v>
       </c>
-      <c r="Z22" s="77">
+      <c r="Z22" s="72">
         <v>0.87560000000000004</v>
       </c>
-      <c r="AA22" s="77">
+      <c r="AA22" s="72">
         <v>135</v>
       </c>
-      <c r="AB22" s="77">
+      <c r="AB22" s="72">
         <f>60.98+0.62</f>
         <v>61.599999999999994</v>
       </c>
-      <c r="AC22" s="77">
+      <c r="AC22" s="72">
         <v>9.5932999999999993</v>
       </c>
-      <c r="AD22" s="77">
+      <c r="AD22" s="72">
         <v>976.6</v>
       </c>
-      <c r="AE22" s="77">
+      <c r="AE22" s="72">
         <v>232.64</v>
       </c>
       <c r="AF22">
         <f t="shared" si="0"/>
         <v>12.129186602870815</v>
       </c>
+      <c r="AG22" s="164">
+        <f t="shared" si="1"/>
+        <v>10.4689</v>
+      </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="70" t="s">
+      <c r="B23" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="71">
-        <v>0</v>
-      </c>
-      <c r="D23" s="71">
-        <v>0</v>
-      </c>
-      <c r="E23" s="71">
-        <v>0</v>
-      </c>
-      <c r="F23" s="71">
-        <v>0</v>
-      </c>
-      <c r="G23" s="72">
+      <c r="C23" s="66">
+        <v>0</v>
+      </c>
+      <c r="D23" s="66">
+        <v>0</v>
+      </c>
+      <c r="E23" s="66">
+        <v>0</v>
+      </c>
+      <c r="F23" s="66">
+        <v>0</v>
+      </c>
+      <c r="G23" s="67">
         <v>67.829457399999995</v>
       </c>
-      <c r="H23" s="73">
+      <c r="H23" s="68">
         <v>37.5</v>
       </c>
-      <c r="I23" s="71"/>
-      <c r="J23" s="74">
-        <v>0</v>
-      </c>
-      <c r="K23" s="71"/>
-      <c r="L23" s="71"/>
-      <c r="M23" s="71"/>
-      <c r="N23" s="71"/>
-      <c r="O23" s="71"/>
-      <c r="P23" s="72">
+      <c r="I23" s="66"/>
+      <c r="J23" s="69">
+        <v>0</v>
+      </c>
+      <c r="K23" s="66"/>
+      <c r="L23" s="66"/>
+      <c r="M23" s="66"/>
+      <c r="N23" s="66"/>
+      <c r="O23" s="66"/>
+      <c r="P23" s="67">
         <v>0.24640656999999999</v>
       </c>
-      <c r="Q23" s="72"/>
-      <c r="R23" s="72"/>
-      <c r="S23" s="75">
+      <c r="Q23" s="67"/>
+      <c r="R23" s="67"/>
+      <c r="S23" s="70">
         <v>48.7</v>
       </c>
-      <c r="T23" s="78"/>
-      <c r="U23" s="76">
+      <c r="T23" s="73"/>
+      <c r="U23" s="71">
         <v>12</v>
       </c>
-      <c r="V23" s="75">
+      <c r="V23" s="70">
         <v>697.4</v>
       </c>
-      <c r="W23" s="78"/>
-      <c r="X23" s="77">
+      <c r="W23" s="73"/>
+      <c r="X23" s="72">
         <v>566</v>
       </c>
-      <c r="Y23" s="77">
+      <c r="Y23" s="72">
         <v>4.7</v>
       </c>
-      <c r="Z23" s="77">
+      <c r="Z23" s="72">
         <v>0.9617</v>
       </c>
-      <c r="AA23" s="77">
+      <c r="AA23" s="72">
         <v>117</v>
       </c>
-      <c r="AB23" s="77">
+      <c r="AB23" s="72">
         <v>56.13</v>
       </c>
-      <c r="AC23" s="77">
+      <c r="AC23" s="72">
         <v>10.324999999999999</v>
       </c>
-      <c r="AD23" s="77">
+      <c r="AD23" s="72">
         <v>1405.3</v>
       </c>
-      <c r="AE23" s="77">
+      <c r="AE23" s="72">
         <v>298</v>
       </c>
+      <c r="AG23" s="164">
+        <f t="shared" si="1"/>
+        <v>11.2867</v>
+      </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="79" t="s">
+      <c r="B24" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="80">
-        <v>0</v>
-      </c>
-      <c r="D24" s="80">
+      <c r="C24" s="75">
+        <v>0</v>
+      </c>
+      <c r="D24" s="75">
         <v>1</v>
       </c>
-      <c r="E24" s="80">
-        <v>0</v>
-      </c>
-      <c r="F24" s="80">
-        <v>0</v>
-      </c>
-      <c r="G24" s="81">
+      <c r="E24" s="75">
+        <v>0</v>
+      </c>
+      <c r="F24" s="75">
+        <v>0</v>
+      </c>
+      <c r="G24" s="76">
         <v>59.59</v>
       </c>
-      <c r="H24" s="82">
+      <c r="H24" s="77">
         <v>42.045454599999999</v>
       </c>
-      <c r="I24" s="80"/>
-      <c r="J24" s="83">
-        <v>0</v>
-      </c>
-      <c r="K24" s="80"/>
-      <c r="L24" s="80"/>
-      <c r="M24" s="80"/>
-      <c r="N24" s="80"/>
-      <c r="O24" s="80"/>
-      <c r="P24" s="80"/>
-      <c r="Q24" s="80"/>
-      <c r="R24" s="80"/>
-      <c r="S24" s="80"/>
-      <c r="T24" s="80"/>
-      <c r="U24" s="80"/>
-      <c r="V24" s="80"/>
-      <c r="W24" s="80"/>
-      <c r="X24" s="84"/>
-      <c r="Y24" s="84">
+      <c r="I24" s="75"/>
+      <c r="J24" s="78">
+        <v>0</v>
+      </c>
+      <c r="K24" s="75"/>
+      <c r="L24" s="75"/>
+      <c r="M24" s="75"/>
+      <c r="N24" s="75"/>
+      <c r="O24" s="75"/>
+      <c r="P24" s="75"/>
+      <c r="Q24" s="75"/>
+      <c r="R24" s="75"/>
+      <c r="S24" s="75"/>
+      <c r="T24" s="75"/>
+      <c r="U24" s="75"/>
+      <c r="V24" s="75"/>
+      <c r="W24" s="75"/>
+      <c r="X24" s="79"/>
+      <c r="Y24" s="79">
         <v>6.1</v>
       </c>
-      <c r="Z24" s="84">
+      <c r="Z24" s="79">
         <v>0.83899999999999997</v>
       </c>
-      <c r="AA24" s="84">
+      <c r="AA24" s="79">
         <v>121</v>
       </c>
-      <c r="AB24" s="84">
+      <c r="AB24" s="79">
         <f>46.77+0.83</f>
         <v>47.6</v>
       </c>
-      <c r="AC24" s="84">
+      <c r="AC24" s="79">
         <v>9.7091999999999992</v>
       </c>
-      <c r="AD24" s="84">
+      <c r="AD24" s="79">
         <v>1347.49</v>
       </c>
-      <c r="AE24" s="84">
+      <c r="AE24" s="79">
         <v>219.9</v>
       </c>
+      <c r="AG24" s="164">
+        <f t="shared" si="1"/>
+        <v>10.5482</v>
+      </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="79" t="s">
+      <c r="B25" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="80">
-        <v>0</v>
-      </c>
-      <c r="D25" s="80">
+      <c r="C25" s="75">
+        <v>0</v>
+      </c>
+      <c r="D25" s="75">
         <v>1</v>
       </c>
-      <c r="E25" s="80">
-        <v>0</v>
-      </c>
-      <c r="F25" s="80">
-        <v>0</v>
-      </c>
-      <c r="G25" s="81">
+      <c r="E25" s="75">
+        <v>0</v>
+      </c>
+      <c r="F25" s="75">
+        <v>0</v>
+      </c>
+      <c r="G25" s="76">
         <v>61.53</v>
       </c>
-      <c r="H25" s="85">
+      <c r="H25" s="80">
         <v>51.136363699999997</v>
       </c>
-      <c r="I25" s="80"/>
-      <c r="J25" s="83">
-        <v>0</v>
-      </c>
-      <c r="K25" s="80"/>
-      <c r="L25" s="80"/>
-      <c r="M25" s="80"/>
-      <c r="N25" s="80"/>
-      <c r="O25" s="80"/>
-      <c r="P25" s="80"/>
-      <c r="Q25" s="80"/>
-      <c r="R25" s="80"/>
-      <c r="S25" s="80"/>
-      <c r="T25" s="80"/>
-      <c r="U25" s="80"/>
-      <c r="V25" s="80"/>
-      <c r="W25" s="80"/>
-      <c r="X25" s="84"/>
-      <c r="Y25" s="84">
+      <c r="I25" s="75"/>
+      <c r="J25" s="78">
+        <v>0</v>
+      </c>
+      <c r="K25" s="75"/>
+      <c r="L25" s="75"/>
+      <c r="M25" s="75"/>
+      <c r="N25" s="75"/>
+      <c r="O25" s="75"/>
+      <c r="P25" s="75"/>
+      <c r="Q25" s="75"/>
+      <c r="R25" s="75"/>
+      <c r="S25" s="75"/>
+      <c r="T25" s="75"/>
+      <c r="U25" s="75"/>
+      <c r="V25" s="75"/>
+      <c r="W25" s="75"/>
+      <c r="X25" s="79"/>
+      <c r="Y25" s="79">
         <v>2.7</v>
       </c>
-      <c r="Z25" s="84">
+      <c r="Z25" s="79">
         <v>0.55459999999999998</v>
       </c>
-      <c r="AA25" s="84">
+      <c r="AA25" s="79">
         <v>158</v>
       </c>
-      <c r="AB25" s="84">
+      <c r="AB25" s="79">
         <v>69.430000000000007</v>
       </c>
-      <c r="AC25" s="84">
+      <c r="AC25" s="79">
         <v>12.512700000000001</v>
       </c>
-      <c r="AD25" s="84">
+      <c r="AD25" s="79">
         <v>1340.09</v>
       </c>
-      <c r="AE25" s="84">
+      <c r="AE25" s="79">
         <v>495.33</v>
       </c>
+      <c r="AG25" s="164">
+        <f t="shared" si="1"/>
+        <v>13.067300000000001</v>
+      </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="79" t="s">
+      <c r="B26" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="80">
-        <v>0</v>
-      </c>
-      <c r="D26" s="80">
+      <c r="C26" s="75">
+        <v>0</v>
+      </c>
+      <c r="D26" s="75">
         <v>1</v>
       </c>
-      <c r="E26" s="80">
-        <v>0</v>
-      </c>
-      <c r="F26" s="80">
-        <v>0</v>
-      </c>
-      <c r="G26" s="81">
+      <c r="E26" s="75">
+        <v>0</v>
+      </c>
+      <c r="F26" s="75">
+        <v>0</v>
+      </c>
+      <c r="G26" s="76">
         <v>35.369999999999997</v>
       </c>
-      <c r="H26" s="85">
+      <c r="H26" s="80">
         <v>40.340909099999998</v>
       </c>
-      <c r="I26" s="80"/>
-      <c r="J26" s="83">
-        <v>0</v>
-      </c>
-      <c r="K26" s="80"/>
-      <c r="L26" s="80"/>
-      <c r="M26" s="80"/>
-      <c r="N26" s="80"/>
-      <c r="O26" s="80"/>
-      <c r="P26" s="80"/>
-      <c r="Q26" s="80"/>
-      <c r="R26" s="80"/>
-      <c r="S26" s="80"/>
-      <c r="T26" s="80"/>
-      <c r="U26" s="80"/>
-      <c r="V26" s="80"/>
-      <c r="W26" s="80"/>
-      <c r="X26" s="84"/>
-      <c r="Y26" s="84">
+      <c r="I26" s="75"/>
+      <c r="J26" s="78">
+        <v>0</v>
+      </c>
+      <c r="K26" s="75"/>
+      <c r="L26" s="75"/>
+      <c r="M26" s="75"/>
+      <c r="N26" s="75"/>
+      <c r="O26" s="75"/>
+      <c r="P26" s="75"/>
+      <c r="Q26" s="75"/>
+      <c r="R26" s="75"/>
+      <c r="S26" s="75"/>
+      <c r="T26" s="75"/>
+      <c r="U26" s="75"/>
+      <c r="V26" s="75"/>
+      <c r="W26" s="75"/>
+      <c r="X26" s="79"/>
+      <c r="Y26" s="79">
         <v>1.64</v>
       </c>
-      <c r="Z26" s="84">
+      <c r="Z26" s="79">
         <v>0.4622</v>
       </c>
-      <c r="AA26" s="84">
+      <c r="AA26" s="79">
         <v>120</v>
       </c>
-      <c r="AB26" s="84">
+      <c r="AB26" s="79">
         <v>45.52</v>
       </c>
-      <c r="AC26" s="84">
+      <c r="AC26" s="79">
         <v>7.8204000000000002</v>
       </c>
-      <c r="AD26" s="84">
+      <c r="AD26" s="79">
         <v>1229.77</v>
       </c>
-      <c r="AE26" s="84">
+      <c r="AE26" s="79">
         <v>748.86</v>
       </c>
+      <c r="AG26" s="164">
+        <f t="shared" si="1"/>
+        <v>8.2826000000000004</v>
+      </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="79" t="s">
+      <c r="B27" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="80">
-        <v>0</v>
-      </c>
-      <c r="D27" s="80">
+      <c r="C27" s="75">
+        <v>0</v>
+      </c>
+      <c r="D27" s="75">
         <v>1</v>
       </c>
-      <c r="E27" s="80">
-        <v>0</v>
-      </c>
-      <c r="F27" s="80">
-        <v>0</v>
-      </c>
-      <c r="G27" s="81">
+      <c r="E27" s="75">
+        <v>0</v>
+      </c>
+      <c r="F27" s="75">
+        <v>0</v>
+      </c>
+      <c r="G27" s="76">
         <v>38.76</v>
       </c>
-      <c r="H27" s="85">
+      <c r="H27" s="80">
         <v>40.340909099999998</v>
       </c>
-      <c r="I27" s="80"/>
-      <c r="J27" s="83">
-        <v>0</v>
-      </c>
-      <c r="K27" s="80"/>
-      <c r="L27" s="80"/>
-      <c r="M27" s="80"/>
-      <c r="N27" s="80"/>
-      <c r="O27" s="80"/>
-      <c r="P27" s="80"/>
-      <c r="Q27" s="80"/>
-      <c r="R27" s="80"/>
-      <c r="S27" s="80"/>
-      <c r="T27" s="80"/>
-      <c r="U27" s="80"/>
-      <c r="V27" s="80"/>
-      <c r="W27" s="80"/>
-      <c r="X27" s="84"/>
-      <c r="Y27" s="84">
+      <c r="I27" s="75"/>
+      <c r="J27" s="78">
+        <v>0</v>
+      </c>
+      <c r="K27" s="75"/>
+      <c r="L27" s="75"/>
+      <c r="M27" s="75"/>
+      <c r="N27" s="75"/>
+      <c r="O27" s="75"/>
+      <c r="P27" s="75"/>
+      <c r="Q27" s="75"/>
+      <c r="R27" s="75"/>
+      <c r="S27" s="75"/>
+      <c r="T27" s="75"/>
+      <c r="U27" s="75"/>
+      <c r="V27" s="75"/>
+      <c r="W27" s="75"/>
+      <c r="X27" s="79"/>
+      <c r="Y27" s="79">
         <v>3.3</v>
       </c>
-      <c r="Z27" s="84">
+      <c r="Z27" s="79">
         <v>0.39300000000000002</v>
       </c>
-      <c r="AA27" s="84">
+      <c r="AA27" s="79">
         <v>69</v>
       </c>
-      <c r="AB27" s="84">
+      <c r="AB27" s="79">
         <v>43.58</v>
       </c>
-      <c r="AC27" s="84">
+      <c r="AC27" s="79">
         <v>5.5315000000000003</v>
       </c>
-      <c r="AD27" s="84">
+      <c r="AD27" s="79">
         <v>1411.55</v>
       </c>
-      <c r="AE27" s="84">
+      <c r="AE27" s="79">
         <v>426.74</v>
       </c>
+      <c r="AG27" s="164">
+        <f t="shared" si="1"/>
+        <v>5.9245000000000001</v>
+      </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="86" t="s">
+      <c r="B28" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="87">
-        <v>0</v>
-      </c>
-      <c r="D28" s="87">
+      <c r="C28" s="82">
+        <v>0</v>
+      </c>
+      <c r="D28" s="82">
         <v>2</v>
       </c>
-      <c r="E28" s="87">
-        <v>0</v>
-      </c>
-      <c r="F28" s="87">
-        <v>0</v>
-      </c>
-      <c r="G28" s="88">
+      <c r="E28" s="82">
+        <v>0</v>
+      </c>
+      <c r="F28" s="82">
+        <v>0</v>
+      </c>
+      <c r="G28" s="83">
         <v>39.729999999999997</v>
       </c>
-      <c r="H28" s="89">
+      <c r="H28" s="84">
         <v>40.909090900000002</v>
       </c>
-      <c r="I28" s="87"/>
-      <c r="J28" s="90">
-        <v>0</v>
-      </c>
-      <c r="K28" s="87"/>
-      <c r="L28" s="87"/>
-      <c r="M28" s="87"/>
-      <c r="N28" s="87"/>
-      <c r="O28" s="87"/>
-      <c r="P28" s="88">
+      <c r="I28" s="82"/>
+      <c r="J28" s="85">
+        <v>0</v>
+      </c>
+      <c r="K28" s="82"/>
+      <c r="L28" s="82"/>
+      <c r="M28" s="82"/>
+      <c r="N28" s="82"/>
+      <c r="O28" s="82"/>
+      <c r="P28" s="83">
         <v>7.6394190000000001E-2</v>
       </c>
-      <c r="Q28" s="88">
+      <c r="Q28" s="83">
         <v>0.23529412</v>
       </c>
-      <c r="R28" s="88">
+      <c r="R28" s="83">
         <v>3.08</v>
       </c>
-      <c r="S28" s="91">
+      <c r="S28" s="86">
         <v>130.9</v>
       </c>
-      <c r="T28" s="91">
+      <c r="T28" s="86">
         <v>30.8</v>
       </c>
-      <c r="U28" s="92">
+      <c r="U28" s="87">
         <v>10</v>
       </c>
-      <c r="V28" s="91">
+      <c r="V28" s="86">
         <v>636.4</v>
       </c>
-      <c r="W28" s="91">
+      <c r="W28" s="86">
         <v>759</v>
       </c>
-      <c r="X28" s="93">
+      <c r="X28" s="88">
         <v>808</v>
       </c>
-      <c r="Y28" s="93">
+      <c r="Y28" s="88">
         <v>2.2999999999999998</v>
       </c>
-      <c r="Z28" s="93">
+      <c r="Z28" s="88">
         <v>0.60680000000000001</v>
       </c>
-      <c r="AA28" s="93">
+      <c r="AA28" s="88">
         <v>116</v>
       </c>
-      <c r="AB28" s="93">
+      <c r="AB28" s="88">
         <v>59.53</v>
       </c>
-      <c r="AC28" s="93">
+      <c r="AC28" s="88">
         <v>10.5433</v>
       </c>
-      <c r="AD28" s="93">
+      <c r="AD28" s="88">
         <v>1313.02</v>
       </c>
-      <c r="AE28" s="93">
+      <c r="AE28" s="88">
         <v>569.88</v>
       </c>
       <c r="AF28">
         <f t="shared" si="0"/>
         <v>13.391304347826088</v>
       </c>
+      <c r="AG28" s="164">
+        <f t="shared" si="1"/>
+        <v>11.1501</v>
+      </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="86" t="s">
+      <c r="B29" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="87">
-        <v>0</v>
-      </c>
-      <c r="D29" s="87">
+      <c r="C29" s="82">
+        <v>0</v>
+      </c>
+      <c r="D29" s="82">
         <v>2</v>
       </c>
-      <c r="E29" s="87">
-        <v>0</v>
-      </c>
-      <c r="F29" s="87">
-        <v>0</v>
-      </c>
-      <c r="G29" s="88">
+      <c r="E29" s="82">
+        <v>0</v>
+      </c>
+      <c r="F29" s="82">
+        <v>0</v>
+      </c>
+      <c r="G29" s="83">
         <v>30.04</v>
       </c>
-      <c r="H29" s="94">
+      <c r="H29" s="89">
         <v>33.5227273</v>
       </c>
-      <c r="I29" s="87"/>
-      <c r="J29" s="90">
-        <v>0</v>
-      </c>
-      <c r="K29" s="87"/>
-      <c r="L29" s="87"/>
-      <c r="M29" s="87"/>
-      <c r="N29" s="87"/>
-      <c r="O29" s="87"/>
-      <c r="P29" s="88">
+      <c r="I29" s="82"/>
+      <c r="J29" s="85">
+        <v>0</v>
+      </c>
+      <c r="K29" s="82"/>
+      <c r="L29" s="82"/>
+      <c r="M29" s="82"/>
+      <c r="N29" s="82"/>
+      <c r="O29" s="82"/>
+      <c r="P29" s="83">
         <v>0.17080745</v>
       </c>
-      <c r="Q29" s="88">
+      <c r="Q29" s="83">
         <v>0.60248447000000005</v>
       </c>
-      <c r="R29" s="88">
+      <c r="R29" s="83">
         <v>3.52727273</v>
       </c>
-      <c r="S29" s="91">
+      <c r="S29" s="86">
         <v>64.400000000000006</v>
       </c>
-      <c r="T29" s="91">
+      <c r="T29" s="86">
         <v>38.799999999999997</v>
       </c>
-      <c r="U29" s="92">
+      <c r="U29" s="87">
         <v>11</v>
       </c>
-      <c r="V29" s="91">
+      <c r="V29" s="86">
         <v>658.2</v>
       </c>
-      <c r="W29" s="91">
+      <c r="W29" s="86">
         <v>660</v>
       </c>
-      <c r="X29" s="93">
+      <c r="X29" s="88">
         <v>668</v>
       </c>
-      <c r="Y29" s="93">
+      <c r="Y29" s="88">
         <v>3.97</v>
       </c>
-      <c r="Z29" s="93">
+      <c r="Z29" s="88">
         <v>1.089</v>
       </c>
-      <c r="AA29" s="93">
+      <c r="AA29" s="88">
         <v>142</v>
       </c>
-      <c r="AB29" s="93">
+      <c r="AB29" s="88">
         <v>60.27</v>
       </c>
-      <c r="AC29" s="93">
+      <c r="AC29" s="88">
         <v>13.506399999999999</v>
       </c>
-      <c r="AD29" s="93">
+      <c r="AD29" s="88">
         <v>1361.88</v>
       </c>
-      <c r="AE29" s="93">
+      <c r="AE29" s="88">
         <v>342.04</v>
       </c>
       <c r="AF29">
         <f t="shared" si="0"/>
         <v>9.7732997481108299</v>
       </c>
+      <c r="AG29" s="164">
+        <f t="shared" si="1"/>
+        <v>14.5954</v>
+      </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="86" t="s">
+      <c r="B30" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="C30" s="87">
-        <v>0</v>
-      </c>
-      <c r="D30" s="87">
+      <c r="C30" s="82">
+        <v>0</v>
+      </c>
+      <c r="D30" s="82">
         <v>2</v>
       </c>
-      <c r="E30" s="87">
-        <v>0</v>
-      </c>
-      <c r="F30" s="87">
-        <v>0</v>
-      </c>
-      <c r="G30" s="88">
+      <c r="E30" s="82">
+        <v>0</v>
+      </c>
+      <c r="F30" s="82">
+        <v>0</v>
+      </c>
+      <c r="G30" s="83">
         <v>46.03</v>
       </c>
-      <c r="H30" s="94">
+      <c r="H30" s="89">
         <v>39.7727273</v>
       </c>
-      <c r="I30" s="87"/>
-      <c r="J30" s="90">
-        <v>0</v>
-      </c>
-      <c r="K30" s="87"/>
-      <c r="L30" s="87"/>
-      <c r="M30" s="87"/>
-      <c r="N30" s="87"/>
-      <c r="O30" s="87"/>
-      <c r="P30" s="88">
+      <c r="I30" s="82"/>
+      <c r="J30" s="85">
+        <v>0</v>
+      </c>
+      <c r="K30" s="82"/>
+      <c r="L30" s="82"/>
+      <c r="M30" s="82"/>
+      <c r="N30" s="82"/>
+      <c r="O30" s="82"/>
+      <c r="P30" s="83">
         <v>0.12936611000000001</v>
       </c>
-      <c r="Q30" s="88">
+      <c r="Q30" s="83">
         <v>0.23027167000000001</v>
       </c>
-      <c r="R30" s="88">
+      <c r="R30" s="83">
         <v>1.78</v>
       </c>
-      <c r="S30" s="91">
+      <c r="S30" s="86">
         <v>77.3</v>
       </c>
-      <c r="T30" s="91">
+      <c r="T30" s="86">
         <v>17.8</v>
       </c>
-      <c r="U30" s="92">
+      <c r="U30" s="87">
         <v>10</v>
       </c>
-      <c r="V30" s="91">
+      <c r="V30" s="86">
         <v>640.70000000000005</v>
       </c>
-      <c r="W30" s="91">
+      <c r="W30" s="86">
         <v>665</v>
       </c>
-      <c r="X30" s="93">
+      <c r="X30" s="88">
         <v>920</v>
       </c>
-      <c r="Y30" s="93">
+      <c r="Y30" s="88">
         <v>6.33</v>
       </c>
-      <c r="Z30" s="93">
+      <c r="Z30" s="88">
         <v>1.0049999999999999</v>
       </c>
-      <c r="AA30" s="93">
+      <c r="AA30" s="88">
         <v>85</v>
       </c>
-      <c r="AB30" s="93">
+      <c r="AB30" s="88">
         <v>39.89</v>
       </c>
-      <c r="AC30" s="93">
+      <c r="AC30" s="88">
         <v>11.229100000000001</v>
       </c>
-      <c r="AD30" s="93">
+      <c r="AD30" s="88">
         <v>1263.72</v>
       </c>
-      <c r="AE30" s="93">
+      <c r="AE30" s="88">
         <v>198.64</v>
       </c>
       <c r="AF30">
         <f t="shared" si="0"/>
         <v>2.8120063191153237</v>
       </c>
+      <c r="AG30" s="164">
+        <f t="shared" si="1"/>
+        <v>12.234100000000002</v>
+      </c>
     </row>
-    <row r="31" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" s="95" t="s">
+      <c r="B31" s="90" t="s">
         <v>14</v>
       </c>
-      <c r="C31" s="96">
-        <v>0</v>
-      </c>
-      <c r="D31" s="96">
+      <c r="C31" s="91">
+        <v>0</v>
+      </c>
+      <c r="D31" s="91">
         <v>2</v>
       </c>
-      <c r="E31" s="96">
-        <v>0</v>
-      </c>
-      <c r="F31" s="96">
-        <v>0</v>
-      </c>
-      <c r="G31" s="97">
+      <c r="E31" s="91">
+        <v>0</v>
+      </c>
+      <c r="F31" s="91">
+        <v>0</v>
+      </c>
+      <c r="G31" s="92">
         <v>64.44</v>
       </c>
-      <c r="H31" s="98">
+      <c r="H31" s="93">
         <v>39.7727273</v>
       </c>
-      <c r="I31" s="99"/>
-      <c r="J31" s="100">
-        <v>0</v>
-      </c>
-      <c r="K31" s="96"/>
-      <c r="L31" s="96"/>
-      <c r="M31" s="96"/>
-      <c r="N31" s="96"/>
-      <c r="O31" s="96"/>
-      <c r="P31" s="97">
+      <c r="I31" s="94"/>
+      <c r="J31" s="95">
+        <v>0</v>
+      </c>
+      <c r="K31" s="91"/>
+      <c r="L31" s="91"/>
+      <c r="M31" s="91"/>
+      <c r="N31" s="91"/>
+      <c r="O31" s="91"/>
+      <c r="P31" s="92">
         <v>0.38626609000000001</v>
       </c>
-      <c r="Q31" s="97">
+      <c r="Q31" s="92">
         <v>0.75321888000000004</v>
       </c>
-      <c r="R31" s="97">
+      <c r="R31" s="92">
         <v>1.95</v>
       </c>
-      <c r="S31" s="101">
+      <c r="S31" s="96">
         <v>46.6</v>
       </c>
-      <c r="T31" s="101">
+      <c r="T31" s="96">
         <v>35.1</v>
       </c>
-      <c r="U31" s="102">
+      <c r="U31" s="97">
         <v>18</v>
       </c>
-      <c r="V31" s="101">
+      <c r="V31" s="96">
         <v>723.5</v>
       </c>
-      <c r="W31" s="101">
+      <c r="W31" s="96">
         <v>131</v>
       </c>
-      <c r="X31" s="103">
+      <c r="X31" s="98">
         <v>130</v>
       </c>
-      <c r="Y31" s="103">
+      <c r="Y31" s="98">
         <v>3.41</v>
       </c>
-      <c r="Z31" s="103">
+      <c r="Z31" s="98">
         <v>0.50919999999999999</v>
       </c>
-      <c r="AA31" s="103">
+      <c r="AA31" s="98">
         <v>71</v>
       </c>
-      <c r="AB31" s="103">
+      <c r="AB31" s="98">
         <v>53.12</v>
       </c>
-      <c r="AC31" s="103">
+      <c r="AC31" s="98">
         <v>6.9410999999999996</v>
       </c>
-      <c r="AD31" s="103">
+      <c r="AD31" s="98">
         <v>1253.58</v>
       </c>
-      <c r="AE31" s="103">
+      <c r="AE31" s="98">
         <v>366.62</v>
       </c>
       <c r="AF31">
         <f t="shared" si="0"/>
         <v>10.293255131964809</v>
       </c>
+      <c r="AG31" s="164">
+        <f t="shared" si="1"/>
+        <v>7.4502999999999995</v>
+      </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="104" t="s">
+      <c r="B32" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="C32" s="105">
+      <c r="C32" s="100">
         <v>1</v>
       </c>
-      <c r="D32" s="105">
-        <v>0</v>
-      </c>
-      <c r="E32" s="106">
+      <c r="D32" s="100">
+        <v>0</v>
+      </c>
+      <c r="E32" s="101">
         <v>75</v>
       </c>
-      <c r="F32" s="106">
+      <c r="F32" s="101">
         <v>17.857142899999999</v>
       </c>
-      <c r="G32" s="106">
+      <c r="G32" s="101">
         <v>70.25</v>
       </c>
-      <c r="H32" s="107">
+      <c r="H32" s="102">
         <v>47.159090900000002</v>
       </c>
-      <c r="I32" s="106"/>
-      <c r="J32" s="108">
+      <c r="I32" s="101"/>
+      <c r="J32" s="103">
         <v>67.27</v>
       </c>
-      <c r="K32" s="105"/>
-      <c r="L32" s="105"/>
-      <c r="M32" s="105"/>
-      <c r="N32" s="105"/>
-      <c r="O32" s="105"/>
-      <c r="P32" s="106">
+      <c r="K32" s="100"/>
+      <c r="L32" s="100"/>
+      <c r="M32" s="100"/>
+      <c r="N32" s="100"/>
+      <c r="O32" s="100"/>
+      <c r="P32" s="101">
         <v>0.31674207999999998</v>
       </c>
-      <c r="Q32" s="106">
+      <c r="Q32" s="101">
         <v>0.35746605999999997</v>
       </c>
-      <c r="R32" s="106">
+      <c r="R32" s="101">
         <v>1.12857143</v>
       </c>
-      <c r="S32" s="109">
+      <c r="S32" s="104">
         <v>44.2</v>
       </c>
-      <c r="T32" s="109">
+      <c r="T32" s="104">
         <v>15.8</v>
       </c>
-      <c r="U32" s="110">
+      <c r="U32" s="105">
         <v>14</v>
       </c>
-      <c r="V32" s="109">
+      <c r="V32" s="104">
         <v>636.4</v>
       </c>
-      <c r="W32" s="109">
+      <c r="W32" s="104">
         <v>883</v>
       </c>
-      <c r="X32" s="111">
+      <c r="X32" s="106">
         <v>150</v>
       </c>
-      <c r="Y32" s="111">
+      <c r="Y32" s="106">
         <v>2.38</v>
       </c>
-      <c r="Z32" s="111">
+      <c r="Z32" s="106">
         <v>0.74480000000000002</v>
       </c>
-      <c r="AA32" s="111">
+      <c r="AA32" s="106">
         <v>145</v>
       </c>
-      <c r="AB32" s="111">
+      <c r="AB32" s="106">
         <v>55.63</v>
       </c>
-      <c r="AC32" s="111">
+      <c r="AC32" s="106">
         <v>11.422000000000001</v>
       </c>
-      <c r="AD32" s="111">
+      <c r="AD32" s="106">
         <v>1207.1500000000001</v>
       </c>
-      <c r="AE32" s="111">
+      <c r="AE32" s="106">
         <v>506.21</v>
       </c>
       <c r="AF32">
         <f t="shared" si="0"/>
         <v>6.6386554621848743</v>
       </c>
+      <c r="AG32" s="164">
+        <f t="shared" si="1"/>
+        <v>12.1668</v>
+      </c>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" s="112" t="s">
+      <c r="B33" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="113">
+      <c r="C33" s="108">
         <v>1</v>
       </c>
-      <c r="D33" s="113">
-        <v>0</v>
-      </c>
-      <c r="E33" s="114">
+      <c r="D33" s="108">
+        <v>0</v>
+      </c>
+      <c r="E33" s="109">
         <v>85.294117700000001</v>
       </c>
-      <c r="F33" s="115">
+      <c r="F33" s="110">
         <v>29.411764699999999</v>
       </c>
-      <c r="G33" s="114">
+      <c r="G33" s="109">
         <v>83.82</v>
       </c>
-      <c r="H33" s="116">
+      <c r="H33" s="111">
         <v>35.2272727</v>
       </c>
-      <c r="I33" s="115"/>
-      <c r="J33" s="117">
+      <c r="I33" s="110"/>
+      <c r="J33" s="112">
         <v>63.19</v>
       </c>
-      <c r="K33" s="113"/>
-      <c r="L33" s="113"/>
-      <c r="M33" s="113"/>
-      <c r="N33" s="113"/>
-      <c r="O33" s="113"/>
-      <c r="P33" s="114">
+      <c r="K33" s="108"/>
+      <c r="L33" s="108"/>
+      <c r="M33" s="108"/>
+      <c r="N33" s="108"/>
+      <c r="O33" s="108"/>
+      <c r="P33" s="109">
         <v>0.37383178</v>
       </c>
-      <c r="Q33" s="114">
+      <c r="Q33" s="109">
         <v>0.58177570000000001</v>
       </c>
-      <c r="R33" s="114">
+      <c r="R33" s="109">
         <v>1.5562499999999999</v>
       </c>
-      <c r="S33" s="115">
+      <c r="S33" s="110">
         <v>42.8</v>
       </c>
-      <c r="T33" s="115">
+      <c r="T33" s="110">
         <v>24.9</v>
       </c>
-      <c r="U33" s="118">
+      <c r="U33" s="113">
         <v>16</v>
       </c>
-      <c r="V33" s="115">
+      <c r="V33" s="110">
         <v>658.2</v>
       </c>
-      <c r="W33" s="115">
+      <c r="W33" s="110">
         <v>111</v>
       </c>
-      <c r="X33" s="119">
+      <c r="X33" s="114">
         <v>120</v>
       </c>
-      <c r="Y33" s="119">
+      <c r="Y33" s="114">
         <v>7.29</v>
       </c>
-      <c r="Z33" s="119">
+      <c r="Z33" s="114">
         <v>0.81930000000000003</v>
       </c>
-      <c r="AA33" s="119">
+      <c r="AA33" s="114">
         <v>109</v>
       </c>
-      <c r="AB33" s="119">
+      <c r="AB33" s="114">
         <v>56.17</v>
       </c>
-      <c r="AC33" s="119">
+      <c r="AC33" s="114">
         <v>9.0335999999999999</v>
       </c>
-      <c r="AD33" s="119">
+      <c r="AD33" s="114">
         <v>1222.1400000000001</v>
       </c>
-      <c r="AE33" s="119">
+      <c r="AE33" s="114">
         <v>166.65</v>
       </c>
       <c r="AF33">
         <f t="shared" si="0"/>
         <v>3.4156378600823043</v>
       </c>
+      <c r="AG33" s="164">
+        <f t="shared" si="1"/>
+        <v>9.8529</v>
+      </c>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="112" t="s">
+      <c r="B34" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="113">
+      <c r="C34" s="108">
         <v>1</v>
       </c>
-      <c r="D34" s="113">
-        <v>0</v>
-      </c>
-      <c r="E34" s="114">
+      <c r="D34" s="108">
+        <v>0</v>
+      </c>
+      <c r="E34" s="109">
         <v>86.486486499999998</v>
       </c>
-      <c r="F34" s="115">
+      <c r="F34" s="110">
         <v>24.864864900000001</v>
       </c>
-      <c r="G34" s="114" t="s">
+      <c r="G34" s="109" t="s">
         <v>15</v>
       </c>
-      <c r="H34" s="116">
+      <c r="H34" s="111">
         <v>48.863636399999997</v>
       </c>
-      <c r="I34" s="115"/>
-      <c r="J34" s="117">
+      <c r="I34" s="110"/>
+      <c r="J34" s="112">
         <v>112.11</v>
       </c>
-      <c r="K34" s="113"/>
-      <c r="L34" s="113"/>
-      <c r="M34" s="113"/>
-      <c r="N34" s="113"/>
-      <c r="O34" s="113"/>
-      <c r="P34" s="114">
+      <c r="K34" s="108"/>
+      <c r="L34" s="108"/>
+      <c r="M34" s="108"/>
+      <c r="N34" s="108"/>
+      <c r="O34" s="108"/>
+      <c r="P34" s="109">
         <v>0.23076922999999999</v>
       </c>
-      <c r="Q34" s="114">
+      <c r="Q34" s="109">
         <v>0.26346153999999999</v>
       </c>
-      <c r="R34" s="114">
+      <c r="R34" s="109">
         <v>1.14166667</v>
       </c>
-      <c r="S34" s="115">
+      <c r="S34" s="110">
         <v>52</v>
       </c>
-      <c r="T34" s="115">
+      <c r="T34" s="110">
         <v>13.7</v>
       </c>
-      <c r="U34" s="118">
+      <c r="U34" s="113">
         <v>12</v>
       </c>
-      <c r="V34" s="115">
+      <c r="V34" s="110">
         <v>636.4</v>
       </c>
-      <c r="W34" s="115">
+      <c r="W34" s="110">
         <v>127</v>
       </c>
-      <c r="X34" s="119">
+      <c r="X34" s="114">
         <v>170</v>
       </c>
-      <c r="Y34" s="119">
+      <c r="Y34" s="114">
         <v>3.3</v>
       </c>
-      <c r="Z34" s="119">
+      <c r="Z34" s="114">
         <v>0.89429999999999998</v>
       </c>
-      <c r="AA34" s="119">
+      <c r="AA34" s="114">
         <v>117</v>
       </c>
-      <c r="AB34" s="119">
+      <c r="AB34" s="114">
         <v>56.04</v>
       </c>
-      <c r="AC34" s="119">
+      <c r="AC34" s="114">
         <v>10.404500000000001</v>
       </c>
-      <c r="AD34" s="119">
+      <c r="AD34" s="114">
         <v>1093.95</v>
       </c>
-      <c r="AE34" s="119">
+      <c r="AE34" s="114">
         <v>330.5</v>
       </c>
       <c r="AF34">
         <f t="shared" si="0"/>
         <v>4.1515151515151514</v>
       </c>
+      <c r="AG34" s="164">
+        <f t="shared" si="1"/>
+        <v>11.2988</v>
+      </c>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" s="112" t="s">
+      <c r="B35" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="113">
+      <c r="C35" s="108">
         <v>1</v>
       </c>
-      <c r="D35" s="113">
-        <v>0</v>
-      </c>
-      <c r="E35" s="114">
+      <c r="D35" s="108">
+        <v>0</v>
+      </c>
+      <c r="E35" s="109">
         <v>72.413793100000007</v>
       </c>
-      <c r="F35" s="115">
+      <c r="F35" s="110">
         <v>15.862068969999999</v>
       </c>
-      <c r="G35" s="114">
+      <c r="G35" s="109">
         <v>87.69</v>
       </c>
-      <c r="H35" s="116">
+      <c r="H35" s="111">
         <v>55.681818200000002</v>
       </c>
-      <c r="I35" s="115"/>
-      <c r="J35" s="117">
+      <c r="I35" s="110"/>
+      <c r="J35" s="112">
         <v>78.48</v>
       </c>
-      <c r="K35" s="113"/>
-      <c r="L35" s="113"/>
-      <c r="M35" s="113"/>
-      <c r="N35" s="113"/>
-      <c r="O35" s="113"/>
-      <c r="P35" s="114"/>
-      <c r="Q35" s="114">
+      <c r="K35" s="108"/>
+      <c r="L35" s="108"/>
+      <c r="M35" s="108"/>
+      <c r="N35" s="108"/>
+      <c r="O35" s="108"/>
+      <c r="P35" s="109"/>
+      <c r="Q35" s="109">
         <v>0.25914397</v>
       </c>
-      <c r="R35" s="114"/>
-      <c r="S35" s="115">
+      <c r="R35" s="109"/>
+      <c r="S35" s="110">
         <v>128.5</v>
       </c>
-      <c r="T35" s="115">
+      <c r="T35" s="110">
         <v>33.299999999999997</v>
       </c>
-      <c r="U35" s="120"/>
-      <c r="V35" s="115">
+      <c r="U35" s="115"/>
+      <c r="V35" s="110">
         <v>610.20000000000005</v>
       </c>
-      <c r="W35" s="115">
+      <c r="W35" s="110">
         <v>105</v>
       </c>
-      <c r="X35" s="121"/>
-      <c r="Y35" s="121">
+      <c r="X35" s="116"/>
+      <c r="Y35" s="116">
         <v>4.22</v>
       </c>
-      <c r="Z35" s="121">
+      <c r="Z35" s="116">
         <v>0.54300000000000004</v>
       </c>
-      <c r="AA35" s="121">
+      <c r="AA35" s="116">
         <v>76</v>
       </c>
-      <c r="AB35" s="121">
+      <c r="AB35" s="116">
         <v>40.119999999999997</v>
       </c>
-      <c r="AC35" s="121">
+      <c r="AC35" s="116">
         <v>6.6025</v>
       </c>
-      <c r="AD35" s="121">
+      <c r="AD35" s="116">
         <v>1343.07</v>
       </c>
-      <c r="AE35" s="121">
+      <c r="AE35" s="116">
         <v>317.26</v>
       </c>
       <c r="AF35">
         <f t="shared" si="0"/>
         <v>7.890995260663507</v>
       </c>
+      <c r="AG35" s="164">
+        <f t="shared" si="1"/>
+        <v>7.1455000000000002</v>
+      </c>
     </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" s="122" t="s">
+      <c r="B36" s="117" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="123">
+      <c r="C36" s="118">
         <v>1</v>
       </c>
-      <c r="D36" s="123">
+      <c r="D36" s="118">
         <v>1</v>
       </c>
-      <c r="E36" s="124">
+      <c r="E36" s="119">
         <v>75</v>
       </c>
-      <c r="F36" s="124">
+      <c r="F36" s="119">
         <v>11.071428600000001</v>
       </c>
-      <c r="G36" s="124">
+      <c r="G36" s="119">
         <v>108.042636</v>
       </c>
-      <c r="H36" s="125">
+      <c r="H36" s="120">
         <v>38.068181799999998</v>
       </c>
-      <c r="I36" s="124"/>
-      <c r="J36" s="126">
+      <c r="I36" s="119"/>
+      <c r="J36" s="121">
         <v>58.09</v>
       </c>
-      <c r="K36" s="123"/>
-      <c r="L36" s="123"/>
-      <c r="M36" s="123"/>
-      <c r="N36" s="123"/>
-      <c r="O36" s="123"/>
-      <c r="P36" s="124"/>
-      <c r="Q36" s="123"/>
-      <c r="R36" s="124"/>
-      <c r="S36" s="123"/>
-      <c r="T36" s="124"/>
-      <c r="U36" s="123"/>
-      <c r="V36" s="124"/>
-      <c r="W36" s="123"/>
-      <c r="X36" s="127"/>
-      <c r="Y36" s="127">
+      <c r="K36" s="118"/>
+      <c r="L36" s="118"/>
+      <c r="M36" s="118"/>
+      <c r="N36" s="118"/>
+      <c r="O36" s="118"/>
+      <c r="P36" s="119"/>
+      <c r="Q36" s="118"/>
+      <c r="R36" s="119"/>
+      <c r="S36" s="118"/>
+      <c r="T36" s="119"/>
+      <c r="U36" s="118"/>
+      <c r="V36" s="119"/>
+      <c r="W36" s="118"/>
+      <c r="X36" s="122"/>
+      <c r="Y36" s="122">
         <v>8.61</v>
       </c>
-      <c r="Z36" s="127">
+      <c r="Z36" s="122">
         <v>1.0141</v>
       </c>
-      <c r="AA36" s="127">
+      <c r="AA36" s="122">
         <v>128</v>
       </c>
-      <c r="AB36" s="127">
+      <c r="AB36" s="122">
         <v>69.31</v>
       </c>
-      <c r="AC36" s="127">
+      <c r="AC36" s="122">
         <v>11.479200000000001</v>
       </c>
-      <c r="AD36" s="127">
+      <c r="AD36" s="122">
         <v>1313.44</v>
       </c>
-      <c r="AE36" s="127">
+      <c r="AE36" s="122">
         <v>151.55000000000001</v>
       </c>
+      <c r="AG36" s="164">
+        <f t="shared" si="1"/>
+        <v>12.493300000000001</v>
+      </c>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" s="122" t="s">
+      <c r="B37" s="117" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="123">
+      <c r="C37" s="118">
         <v>1</v>
       </c>
-      <c r="D37" s="123">
+      <c r="D37" s="118">
         <v>1</v>
       </c>
-      <c r="E37" s="124">
+      <c r="E37" s="119">
         <v>97.142857100000001</v>
       </c>
-      <c r="F37" s="128">
+      <c r="F37" s="123">
         <v>20.285714299999999</v>
       </c>
-      <c r="G37" s="124">
+      <c r="G37" s="119">
         <v>84.302325600000003</v>
       </c>
-      <c r="H37" s="129">
+      <c r="H37" s="124">
         <v>48.295454599999999</v>
       </c>
-      <c r="I37" s="128"/>
-      <c r="J37" s="130">
+      <c r="I37" s="123"/>
+      <c r="J37" s="125">
         <v>100.9</v>
       </c>
-      <c r="K37" s="123"/>
-      <c r="L37" s="123"/>
-      <c r="M37" s="123"/>
-      <c r="N37" s="123"/>
-      <c r="O37" s="123"/>
-      <c r="P37" s="124"/>
-      <c r="Q37" s="123"/>
-      <c r="R37" s="124"/>
-      <c r="S37" s="123"/>
-      <c r="T37" s="124"/>
-      <c r="U37" s="123"/>
-      <c r="V37" s="124"/>
-      <c r="W37" s="123"/>
-      <c r="X37" s="127"/>
-      <c r="Y37" s="127">
+      <c r="K37" s="118"/>
+      <c r="L37" s="118"/>
+      <c r="M37" s="118"/>
+      <c r="N37" s="118"/>
+      <c r="O37" s="118"/>
+      <c r="P37" s="119"/>
+      <c r="Q37" s="118"/>
+      <c r="R37" s="119"/>
+      <c r="S37" s="118"/>
+      <c r="T37" s="119"/>
+      <c r="U37" s="118"/>
+      <c r="V37" s="119"/>
+      <c r="W37" s="118"/>
+      <c r="X37" s="122"/>
+      <c r="Y37" s="122">
         <v>6.73</v>
       </c>
-      <c r="Z37" s="127">
+      <c r="Z37" s="122">
         <v>0.90800000000000003</v>
       </c>
-      <c r="AA37" s="127">
+      <c r="AA37" s="122">
         <v>112</v>
       </c>
-      <c r="AB37" s="127">
+      <c r="AB37" s="122">
         <v>58.19</v>
       </c>
-      <c r="AC37" s="127">
+      <c r="AC37" s="122">
         <v>9.5004000000000008</v>
       </c>
-      <c r="AD37" s="127">
+      <c r="AD37" s="122">
         <v>1371.83</v>
       </c>
-      <c r="AE37" s="127">
+      <c r="AE37" s="122">
         <v>202.84</v>
       </c>
+      <c r="AG37" s="164">
+        <f t="shared" si="1"/>
+        <v>10.4084</v>
+      </c>
     </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="B38" s="122" t="s">
+      <c r="B38" s="117" t="s">
         <v>14</v>
       </c>
-      <c r="C38" s="123">
+      <c r="C38" s="118">
         <v>1</v>
       </c>
-      <c r="D38" s="123">
+      <c r="D38" s="118">
         <v>1</v>
       </c>
-      <c r="E38" s="124">
+      <c r="E38" s="119">
         <v>90.476190500000001</v>
       </c>
-      <c r="F38" s="128">
+      <c r="F38" s="123">
         <v>31.6666667</v>
       </c>
-      <c r="G38" s="124">
+      <c r="G38" s="119">
         <v>94.9612403</v>
       </c>
-      <c r="H38" s="129">
+      <c r="H38" s="124">
         <v>41.4772727</v>
       </c>
-      <c r="I38" s="128"/>
-      <c r="J38" s="130">
+      <c r="I38" s="123"/>
+      <c r="J38" s="125">
         <v>83.57</v>
       </c>
-      <c r="K38" s="123"/>
-      <c r="L38" s="123"/>
-      <c r="M38" s="123"/>
-      <c r="N38" s="123"/>
-      <c r="O38" s="123"/>
-      <c r="P38" s="124"/>
-      <c r="Q38" s="123"/>
-      <c r="R38" s="124"/>
-      <c r="S38" s="123"/>
-      <c r="T38" s="124"/>
-      <c r="U38" s="123"/>
-      <c r="V38" s="124"/>
-      <c r="W38" s="123"/>
-      <c r="X38" s="127"/>
-      <c r="Y38" s="127">
+      <c r="K38" s="118"/>
+      <c r="L38" s="118"/>
+      <c r="M38" s="118"/>
+      <c r="N38" s="118"/>
+      <c r="O38" s="118"/>
+      <c r="P38" s="119"/>
+      <c r="Q38" s="118"/>
+      <c r="R38" s="119"/>
+      <c r="S38" s="118"/>
+      <c r="T38" s="119"/>
+      <c r="U38" s="118"/>
+      <c r="V38" s="119"/>
+      <c r="W38" s="118"/>
+      <c r="X38" s="122"/>
+      <c r="Y38" s="122">
         <v>2.4300000000000002</v>
       </c>
-      <c r="Z38" s="127">
+      <c r="Z38" s="122">
         <v>0.51919999999999999</v>
       </c>
-      <c r="AA38" s="127">
+      <c r="AA38" s="122">
         <v>127</v>
       </c>
-      <c r="AB38" s="127">
+      <c r="AB38" s="122">
         <v>58.88</v>
       </c>
-      <c r="AC38" s="127">
+      <c r="AC38" s="122">
         <v>11.9574</v>
       </c>
-      <c r="AD38" s="127">
+      <c r="AD38" s="122">
         <v>1347.44</v>
       </c>
-      <c r="AE38" s="127">
+      <c r="AE38" s="122">
         <v>553.5</v>
       </c>
+      <c r="AG38" s="164">
+        <f t="shared" si="1"/>
+        <v>12.476599999999999</v>
+      </c>
     </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="B39" s="122" t="s">
+      <c r="B39" s="117" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="123">
+      <c r="C39" s="118">
         <v>1</v>
       </c>
-      <c r="D39" s="123">
+      <c r="D39" s="118">
         <v>1</v>
       </c>
-      <c r="E39" s="124">
+      <c r="E39" s="119">
         <v>48.387096769999999</v>
       </c>
-      <c r="F39" s="124">
+      <c r="F39" s="119">
         <v>7.4193548390000004</v>
       </c>
-      <c r="G39" s="124">
+      <c r="G39" s="119">
         <v>83.333333400000001</v>
       </c>
-      <c r="H39" s="129">
+      <c r="H39" s="124">
         <v>51.704545500000002</v>
       </c>
-      <c r="I39" s="128"/>
-      <c r="J39" s="130">
+      <c r="I39" s="123"/>
+      <c r="J39" s="125">
         <v>20.38</v>
       </c>
-      <c r="K39" s="123"/>
-      <c r="L39" s="123"/>
-      <c r="M39" s="123"/>
-      <c r="N39" s="123"/>
-      <c r="O39" s="123"/>
-      <c r="P39" s="124"/>
-      <c r="Q39" s="123"/>
-      <c r="R39" s="124"/>
-      <c r="S39" s="123"/>
-      <c r="T39" s="124"/>
-      <c r="U39" s="123"/>
-      <c r="V39" s="124"/>
-      <c r="W39" s="123"/>
-      <c r="X39" s="127"/>
-      <c r="Y39" s="127">
+      <c r="K39" s="118"/>
+      <c r="L39" s="118"/>
+      <c r="M39" s="118"/>
+      <c r="N39" s="118"/>
+      <c r="O39" s="118"/>
+      <c r="P39" s="119"/>
+      <c r="Q39" s="118"/>
+      <c r="R39" s="119"/>
+      <c r="S39" s="118"/>
+      <c r="T39" s="119"/>
+      <c r="U39" s="118"/>
+      <c r="V39" s="119"/>
+      <c r="W39" s="118"/>
+      <c r="X39" s="122"/>
+      <c r="Y39" s="122">
         <v>2.21</v>
       </c>
-      <c r="Z39" s="127">
+      <c r="Z39" s="122">
         <v>0.59340000000000004</v>
       </c>
-      <c r="AA39" s="127">
+      <c r="AA39" s="122">
         <v>110</v>
       </c>
-      <c r="AB39" s="127">
+      <c r="AB39" s="122">
         <v>54.48</v>
       </c>
-      <c r="AC39" s="127">
+      <c r="AC39" s="122">
         <v>9.8055000000000003</v>
       </c>
-      <c r="AD39" s="127">
+      <c r="AD39" s="122">
         <v>1129.82</v>
       </c>
-      <c r="AE39" s="127">
+      <c r="AE39" s="122">
         <v>510.23</v>
       </c>
+      <c r="AG39" s="164">
+        <f t="shared" si="1"/>
+        <v>10.398900000000001</v>
+      </c>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="B40" s="131" t="s">
+      <c r="B40" s="126" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="132">
+      <c r="C40" s="127">
         <v>1</v>
       </c>
-      <c r="D40" s="132">
+      <c r="D40" s="127">
         <v>2</v>
       </c>
-      <c r="E40" s="133">
+      <c r="E40" s="128">
         <v>78.787878800000001</v>
       </c>
-      <c r="F40" s="133">
+      <c r="F40" s="128">
         <v>22.121212100000001</v>
       </c>
-      <c r="G40" s="133">
+      <c r="G40" s="128">
         <v>96.41</v>
       </c>
-      <c r="H40" s="134">
+      <c r="H40" s="129">
         <v>59.090909099999998</v>
       </c>
-      <c r="I40" s="135"/>
-      <c r="J40" s="136">
+      <c r="I40" s="130"/>
+      <c r="J40" s="131">
         <v>55.04</v>
       </c>
-      <c r="K40" s="132"/>
-      <c r="L40" s="132"/>
-      <c r="M40" s="132"/>
-      <c r="N40" s="132"/>
-      <c r="O40" s="132"/>
-      <c r="P40" s="133">
+      <c r="K40" s="127"/>
+      <c r="L40" s="127"/>
+      <c r="M40" s="127"/>
+      <c r="N40" s="127"/>
+      <c r="O40" s="127"/>
+      <c r="P40" s="128">
         <v>0.19438444999999999</v>
       </c>
-      <c r="Q40" s="133">
+      <c r="Q40" s="128">
         <v>0.30237581000000002</v>
       </c>
-      <c r="R40" s="133">
+      <c r="R40" s="128">
         <v>1.5555555599999999</v>
       </c>
-      <c r="S40" s="137">
+      <c r="S40" s="132">
         <v>92.6</v>
       </c>
-      <c r="T40" s="137">
+      <c r="T40" s="132">
         <v>28</v>
       </c>
-      <c r="U40" s="138">
+      <c r="U40" s="133">
         <v>18</v>
       </c>
-      <c r="V40" s="137">
+      <c r="V40" s="132">
         <v>632</v>
       </c>
-      <c r="W40" s="137">
+      <c r="W40" s="132">
         <v>113</v>
       </c>
-      <c r="X40" s="139">
+      <c r="X40" s="134">
         <v>574</v>
       </c>
-      <c r="Y40" s="139">
+      <c r="Y40" s="134">
         <v>2.4</v>
       </c>
-      <c r="Z40" s="139">
+      <c r="Z40" s="134">
         <v>0.61670000000000003</v>
       </c>
-      <c r="AA40" s="139">
+      <c r="AA40" s="134">
         <v>138</v>
       </c>
-      <c r="AB40" s="139">
+      <c r="AB40" s="134">
         <v>52.21</v>
       </c>
-      <c r="AC40" s="139">
+      <c r="AC40" s="134">
         <v>11.1843</v>
       </c>
-      <c r="AD40" s="139">
+      <c r="AD40" s="134">
         <v>1201.3</v>
       </c>
-      <c r="AE40" s="139">
+      <c r="AE40" s="134">
         <v>499.54</v>
       </c>
       <c r="AF40">
         <f t="shared" si="0"/>
         <v>11.666666666666668</v>
       </c>
+      <c r="AG40" s="164">
+        <f t="shared" si="1"/>
+        <v>11.801</v>
+      </c>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="B41" s="131" t="s">
+      <c r="B41" s="126" t="s">
         <v>14</v>
       </c>
-      <c r="C41" s="132">
+      <c r="C41" s="127">
         <v>1</v>
       </c>
-      <c r="D41" s="132">
+      <c r="D41" s="127">
         <v>2</v>
       </c>
-      <c r="E41" s="133">
+      <c r="E41" s="128">
         <v>80.4878049</v>
       </c>
-      <c r="F41" s="137">
+      <c r="F41" s="132">
         <v>22.926829300000001</v>
       </c>
-      <c r="G41" s="133">
+      <c r="G41" s="128">
         <v>97.87</v>
       </c>
-      <c r="H41" s="140">
+      <c r="H41" s="135">
         <v>58.5227273</v>
       </c>
-      <c r="I41" s="132"/>
-      <c r="J41" s="141">
+      <c r="I41" s="127"/>
+      <c r="J41" s="136">
         <v>27.52</v>
       </c>
-      <c r="K41" s="132"/>
-      <c r="L41" s="132"/>
-      <c r="M41" s="132"/>
-      <c r="N41" s="132"/>
-      <c r="O41" s="132"/>
-      <c r="P41" s="133">
+      <c r="K41" s="127"/>
+      <c r="L41" s="127"/>
+      <c r="M41" s="127"/>
+      <c r="N41" s="127"/>
+      <c r="O41" s="127"/>
+      <c r="P41" s="128">
         <v>0.10805501000000001</v>
       </c>
-      <c r="Q41" s="133">
+      <c r="Q41" s="128">
         <v>0.18123771999999999</v>
       </c>
-      <c r="R41" s="133">
+      <c r="R41" s="128">
         <v>1.6772727300000001</v>
       </c>
-      <c r="S41" s="137">
+      <c r="S41" s="132">
         <v>203.6</v>
       </c>
-      <c r="T41" s="137">
+      <c r="T41" s="132">
         <v>36.9</v>
       </c>
-      <c r="U41" s="138">
+      <c r="U41" s="133">
         <v>22</v>
       </c>
-      <c r="V41" s="137">
+      <c r="V41" s="132">
         <v>662.5</v>
       </c>
-      <c r="W41" s="137">
+      <c r="W41" s="132">
         <v>993</v>
       </c>
-      <c r="X41" s="139">
+      <c r="X41" s="134">
         <v>817</v>
       </c>
-      <c r="Y41" s="139">
+      <c r="Y41" s="134">
         <v>2.12</v>
       </c>
-      <c r="Z41" s="139">
+      <c r="Z41" s="134">
         <v>0.60489999999999999</v>
       </c>
-      <c r="AA41" s="139">
+      <c r="AA41" s="134">
         <v>134</v>
       </c>
-      <c r="AB41" s="139">
+      <c r="AB41" s="134">
         <v>63.87</v>
       </c>
-      <c r="AC41" s="139">
+      <c r="AC41" s="134">
         <v>12.145300000000001</v>
       </c>
-      <c r="AD41" s="139">
+      <c r="AD41" s="134">
         <v>1280.06</v>
       </c>
-      <c r="AE41" s="139">
+      <c r="AE41" s="134">
         <v>602.79999999999995</v>
       </c>
       <c r="AF41">
         <f t="shared" si="0"/>
         <v>17.40566037735849</v>
       </c>
+      <c r="AG41" s="164">
+        <f t="shared" si="1"/>
+        <v>12.750200000000001</v>
+      </c>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="B42" s="131" t="s">
+      <c r="B42" s="126" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="132">
+      <c r="C42" s="127">
         <v>1</v>
       </c>
-      <c r="D42" s="132">
+      <c r="D42" s="127">
         <v>2</v>
       </c>
-      <c r="E42" s="133">
+      <c r="E42" s="128">
         <v>78.571428600000004</v>
       </c>
-      <c r="F42" s="137">
+      <c r="F42" s="132">
         <v>17.428571399999999</v>
       </c>
-      <c r="G42" s="133">
+      <c r="G42" s="128">
         <v>77.52</v>
       </c>
-      <c r="H42" s="140">
+      <c r="H42" s="135">
         <v>43.181818200000002</v>
       </c>
-      <c r="I42" s="132"/>
-      <c r="J42" s="141">
+      <c r="I42" s="127"/>
+      <c r="J42" s="136">
         <v>61.15</v>
       </c>
-      <c r="K42" s="132"/>
-      <c r="L42" s="132"/>
-      <c r="M42" s="132"/>
-      <c r="N42" s="132"/>
-      <c r="O42" s="132"/>
-      <c r="P42" s="133">
+      <c r="K42" s="127"/>
+      <c r="L42" s="127"/>
+      <c r="M42" s="127"/>
+      <c r="N42" s="127"/>
+      <c r="O42" s="127"/>
+      <c r="P42" s="128">
         <v>0.11928429</v>
       </c>
-      <c r="Q42" s="133">
+      <c r="Q42" s="128">
         <v>0.19615639000000001</v>
       </c>
-      <c r="R42" s="133">
+      <c r="R42" s="128">
         <v>1.64444444</v>
       </c>
-      <c r="S42" s="137">
+      <c r="S42" s="132">
         <v>150.9</v>
       </c>
-      <c r="T42" s="137">
+      <c r="T42" s="132">
         <v>29.6</v>
       </c>
-      <c r="U42" s="138">
+      <c r="U42" s="133">
         <v>18</v>
       </c>
-      <c r="V42" s="137">
+      <c r="V42" s="132">
         <v>658.2</v>
       </c>
-      <c r="W42" s="137">
+      <c r="W42" s="132">
         <v>110</v>
       </c>
-      <c r="X42" s="139">
+      <c r="X42" s="134">
         <v>751</v>
       </c>
-      <c r="Y42" s="139">
+      <c r="Y42" s="134">
         <v>2.8</v>
       </c>
-      <c r="Z42" s="139">
+      <c r="Z42" s="134">
         <v>0.76349999999999996</v>
       </c>
-      <c r="AA42" s="139">
+      <c r="AA42" s="134">
         <v>129</v>
       </c>
-      <c r="AB42" s="139">
+      <c r="AB42" s="134">
         <v>62.27</v>
       </c>
-      <c r="AC42" s="139">
+      <c r="AC42" s="134">
         <v>11.507</v>
       </c>
-      <c r="AD42" s="139">
+      <c r="AD42" s="134">
         <v>1266.1500000000001</v>
       </c>
-      <c r="AE42" s="139">
+      <c r="AE42" s="134">
         <v>451.2</v>
       </c>
       <c r="AF42">
         <f t="shared" si="0"/>
         <v>10.571428571428573</v>
       </c>
+      <c r="AG42" s="164">
+        <f t="shared" si="1"/>
+        <v>12.2705</v>
+      </c>
     </row>
-    <row r="43" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="B43" s="142" t="s">
+      <c r="B43" s="137" t="s">
         <v>14</v>
       </c>
-      <c r="C43" s="143">
+      <c r="C43" s="138">
         <v>1</v>
       </c>
-      <c r="D43" s="143">
+      <c r="D43" s="138">
         <v>2</v>
       </c>
-      <c r="E43" s="144">
+      <c r="E43" s="139">
         <v>68.571428569999995</v>
       </c>
-      <c r="F43" s="144">
+      <c r="F43" s="139">
         <v>17.38095238</v>
       </c>
-      <c r="G43" s="144">
+      <c r="G43" s="139">
         <v>84.79</v>
       </c>
-      <c r="H43" s="145">
+      <c r="H43" s="140">
         <v>64.204545499999995</v>
       </c>
-      <c r="I43" s="143"/>
-      <c r="J43" s="146">
+      <c r="I43" s="138"/>
+      <c r="J43" s="141">
         <v>60.13</v>
       </c>
-      <c r="K43" s="143"/>
-      <c r="L43" s="143"/>
-      <c r="M43" s="143"/>
-      <c r="N43" s="143"/>
-      <c r="O43" s="143"/>
-      <c r="P43" s="143"/>
-      <c r="Q43" s="143"/>
-      <c r="R43" s="143"/>
-      <c r="S43" s="147"/>
-      <c r="T43" s="147"/>
-      <c r="U43" s="147"/>
-      <c r="V43" s="147"/>
-      <c r="W43" s="147"/>
-      <c r="X43" s="148"/>
-      <c r="Y43" s="148">
+      <c r="K43" s="138"/>
+      <c r="L43" s="138"/>
+      <c r="M43" s="138"/>
+      <c r="N43" s="138"/>
+      <c r="O43" s="138"/>
+      <c r="P43" s="138"/>
+      <c r="Q43" s="138"/>
+      <c r="R43" s="138"/>
+      <c r="S43" s="142"/>
+      <c r="T43" s="142"/>
+      <c r="U43" s="142"/>
+      <c r="V43" s="142"/>
+      <c r="W43" s="142"/>
+      <c r="X43" s="143"/>
+      <c r="Y43" s="143">
         <v>1.97</v>
       </c>
-      <c r="Z43" s="148">
+      <c r="Z43" s="143">
         <v>0.67500000000000004</v>
       </c>
-      <c r="AA43" s="148">
+      <c r="AA43" s="143">
         <v>125</v>
       </c>
-      <c r="AB43" s="148">
+      <c r="AB43" s="143">
         <v>53.07</v>
       </c>
-      <c r="AC43" s="148">
+      <c r="AC43" s="143">
         <v>10.924200000000001</v>
       </c>
-      <c r="AD43" s="148">
+      <c r="AD43" s="143">
         <v>1274.79</v>
       </c>
-      <c r="AE43" s="148">
+      <c r="AE43" s="143">
         <v>646.1</v>
+      </c>
+      <c r="AG43" s="164">
+        <f t="shared" si="1"/>
+        <v>11.599200000000002</v>
       </c>
     </row>
   </sheetData>

--- a/BD Cobre.xlsx
+++ b/BD Cobre.xlsx
@@ -1,18 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julip\GitHub\Cobre\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF981FB-2CC2-4AA7-802E-13AB12B2D646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="236"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="236" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -135,7 +152,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -627,7 +644,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1107,14 +1124,13 @@
     <xf numFmtId="2" fontId="4" fillId="14" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1384,14 +1400,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AG43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1489,13 +1505,13 @@
       <c r="AD1" s="162" t="s">
         <v>31</v>
       </c>
-      <c r="AE1" s="163" t="s">
+      <c r="AE1" t="s">
         <v>32</v>
       </c>
-      <c r="AF1" s="163" t="s">
+      <c r="AF1" t="s">
         <v>33</v>
       </c>
-      <c r="AG1" s="163" t="s">
+      <c r="AG1" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2582,7 +2598,7 @@
         <f>T20/Y20</f>
         <v>3.3454545454545452</v>
       </c>
-      <c r="AG20" s="164">
+      <c r="AG20" s="163">
         <f>Z20+AC20</f>
         <v>13.714399999999999</v>
       </c>
@@ -2673,7 +2689,7 @@
         <f t="shared" ref="AF21:AF42" si="0">T21/Y21</f>
         <v>4.661458333333333</v>
       </c>
-      <c r="AG21" s="164">
+      <c r="AG21" s="163">
         <f t="shared" ref="AG21:AG43" si="1">Z21+AC21</f>
         <v>13.092700000000001</v>
       </c>
@@ -2765,7 +2781,7 @@
         <f t="shared" si="0"/>
         <v>12.129186602870815</v>
       </c>
-      <c r="AG22" s="164">
+      <c r="AG22" s="163">
         <f t="shared" si="1"/>
         <v>10.4689</v>
       </c>
@@ -2844,7 +2860,7 @@
       <c r="AE23" s="72">
         <v>298</v>
       </c>
-      <c r="AG23" s="164">
+      <c r="AG23" s="163">
         <f t="shared" si="1"/>
         <v>11.2867</v>
       </c>
@@ -2914,7 +2930,7 @@
       <c r="AE24" s="79">
         <v>219.9</v>
       </c>
-      <c r="AG24" s="164">
+      <c r="AG24" s="163">
         <f t="shared" si="1"/>
         <v>10.5482</v>
       </c>
@@ -2983,7 +2999,7 @@
       <c r="AE25" s="79">
         <v>495.33</v>
       </c>
-      <c r="AG25" s="164">
+      <c r="AG25" s="163">
         <f t="shared" si="1"/>
         <v>13.067300000000001</v>
       </c>
@@ -3052,7 +3068,7 @@
       <c r="AE26" s="79">
         <v>748.86</v>
       </c>
-      <c r="AG26" s="164">
+      <c r="AG26" s="163">
         <f t="shared" si="1"/>
         <v>8.2826000000000004</v>
       </c>
@@ -3121,7 +3137,7 @@
       <c r="AE27" s="79">
         <v>426.74</v>
       </c>
-      <c r="AG27" s="164">
+      <c r="AG27" s="163">
         <f t="shared" si="1"/>
         <v>5.9245000000000001</v>
       </c>
@@ -3212,7 +3228,7 @@
         <f t="shared" si="0"/>
         <v>13.391304347826088</v>
       </c>
-      <c r="AG28" s="164">
+      <c r="AG28" s="163">
         <f t="shared" si="1"/>
         <v>11.1501</v>
       </c>
@@ -3303,7 +3319,7 @@
         <f t="shared" si="0"/>
         <v>9.7732997481108299</v>
       </c>
-      <c r="AG29" s="164">
+      <c r="AG29" s="163">
         <f t="shared" si="1"/>
         <v>14.5954</v>
       </c>
@@ -3394,7 +3410,7 @@
         <f t="shared" si="0"/>
         <v>2.8120063191153237</v>
       </c>
-      <c r="AG30" s="164">
+      <c r="AG30" s="163">
         <f t="shared" si="1"/>
         <v>12.234100000000002</v>
       </c>
@@ -3485,7 +3501,7 @@
         <f t="shared" si="0"/>
         <v>10.293255131964809</v>
       </c>
-      <c r="AG31" s="164">
+      <c r="AG31" s="163">
         <f t="shared" si="1"/>
         <v>7.4502999999999995</v>
       </c>
@@ -3576,7 +3592,7 @@
         <f t="shared" si="0"/>
         <v>6.6386554621848743</v>
       </c>
-      <c r="AG32" s="164">
+      <c r="AG32" s="163">
         <f t="shared" si="1"/>
         <v>12.1668</v>
       </c>
@@ -3667,7 +3683,7 @@
         <f t="shared" si="0"/>
         <v>3.4156378600823043</v>
       </c>
-      <c r="AG33" s="164">
+      <c r="AG33" s="163">
         <f t="shared" si="1"/>
         <v>9.8529</v>
       </c>
@@ -3758,7 +3774,7 @@
         <f t="shared" si="0"/>
         <v>4.1515151515151514</v>
       </c>
-      <c r="AG34" s="164">
+      <c r="AG34" s="163">
         <f t="shared" si="1"/>
         <v>11.2988</v>
       </c>
@@ -3841,7 +3857,7 @@
         <f t="shared" si="0"/>
         <v>7.890995260663507</v>
       </c>
-      <c r="AG35" s="164">
+      <c r="AG35" s="163">
         <f t="shared" si="1"/>
         <v>7.1455000000000002</v>
       </c>
@@ -3910,7 +3926,7 @@
       <c r="AE36" s="122">
         <v>151.55000000000001</v>
       </c>
-      <c r="AG36" s="164">
+      <c r="AG36" s="163">
         <f t="shared" si="1"/>
         <v>12.493300000000001</v>
       </c>
@@ -3979,7 +3995,7 @@
       <c r="AE37" s="122">
         <v>202.84</v>
       </c>
-      <c r="AG37" s="164">
+      <c r="AG37" s="163">
         <f t="shared" si="1"/>
         <v>10.4084</v>
       </c>
@@ -4048,7 +4064,7 @@
       <c r="AE38" s="122">
         <v>553.5</v>
       </c>
-      <c r="AG38" s="164">
+      <c r="AG38" s="163">
         <f t="shared" si="1"/>
         <v>12.476599999999999</v>
       </c>
@@ -4117,7 +4133,7 @@
       <c r="AE39" s="122">
         <v>510.23</v>
       </c>
-      <c r="AG39" s="164">
+      <c r="AG39" s="163">
         <f t="shared" si="1"/>
         <v>10.398900000000001</v>
       </c>
@@ -4208,7 +4224,7 @@
         <f t="shared" si="0"/>
         <v>11.666666666666668</v>
       </c>
-      <c r="AG40" s="164">
+      <c r="AG40" s="163">
         <f t="shared" si="1"/>
         <v>11.801</v>
       </c>
@@ -4299,7 +4315,7 @@
         <f t="shared" si="0"/>
         <v>17.40566037735849</v>
       </c>
-      <c r="AG41" s="164">
+      <c r="AG41" s="163">
         <f t="shared" si="1"/>
         <v>12.750200000000001</v>
       </c>
@@ -4390,7 +4406,7 @@
         <f t="shared" si="0"/>
         <v>10.571428571428573</v>
       </c>
-      <c r="AG42" s="164">
+      <c r="AG42" s="163">
         <f t="shared" si="1"/>
         <v>12.2705</v>
       </c>
@@ -4459,7 +4475,7 @@
       <c r="AE43" s="143">
         <v>646.1</v>
       </c>
-      <c r="AG43" s="164">
+      <c r="AG43" s="163">
         <f t="shared" si="1"/>
         <v>11.599200000000002</v>
       </c>

--- a/BD Cobre.xlsx
+++ b/BD Cobre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julip\GitHub\Cobre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF981FB-2CC2-4AA7-802E-13AB12B2D646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD86618E-53A9-41CD-AEA7-E880D0AF1230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="236" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20490" yWindow="780" windowWidth="20460" windowHeight="10770" tabRatio="236" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="36">
   <si>
     <t>id</t>
   </si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t>FT</t>
-  </si>
-  <si>
-    <t>In vitro</t>
   </si>
   <si>
     <t>in vivo</t>
@@ -1428,10 +1425,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>4</v>
@@ -1443,7 +1440,7 @@
         <v>6</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>7</v>
@@ -1461,66 +1458,66 @@
         <v>11</v>
       </c>
       <c r="P1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="S1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="V1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y1" s="161" t="s">
         <v>25</v>
       </c>
-      <c r="U1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="161" t="s">
+      <c r="Z1" s="161" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" s="161" t="s">
+      <c r="AA1" s="161" t="s">
         <v>27</v>
       </c>
-      <c r="AA1" s="161" t="s">
+      <c r="AB1" s="161" t="s">
         <v>28</v>
       </c>
-      <c r="AB1" s="161" t="s">
+      <c r="AC1" s="161" t="s">
         <v>29</v>
       </c>
-      <c r="AC1" s="161" t="s">
+      <c r="AD1" s="162" t="s">
         <v>30</v>
       </c>
-      <c r="AD1" s="162" t="s">
+      <c r="AE1" t="s">
         <v>31</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>32</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>33</v>
       </c>
-      <c r="AG1" t="s">
-        <v>34</v>
-      </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C2" s="7">
         <v>0</v>
@@ -1575,8 +1572,8 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>13</v>
+      <c r="B3" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="C3" s="12">
         <v>0</v>
@@ -1618,7 +1615,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" s="12">
         <v>0</v>
@@ -1660,7 +1657,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" s="16">
         <v>0</v>
@@ -1716,7 +1713,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" s="16">
         <v>0</v>
@@ -1772,7 +1769,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="16">
         <v>0</v>
@@ -1828,7 +1825,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="21">
         <v>0</v>
@@ -1884,7 +1881,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" s="21">
         <v>0</v>
@@ -1940,7 +1937,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" s="23">
         <v>0</v>
@@ -1996,7 +1993,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="31">
         <v>1</v>
@@ -2056,7 +2053,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" s="36">
         <v>1</v>
@@ -2116,7 +2113,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" s="36">
         <v>1</v>
@@ -2158,7 +2155,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" s="41">
         <v>1</v>
@@ -2218,7 +2215,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="41">
         <v>1</v>
@@ -2278,7 +2275,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="41">
         <v>1</v>
@@ -2336,7 +2333,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" s="47">
         <v>1</v>
@@ -2396,7 +2393,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" s="47">
         <v>1</v>
@@ -2456,7 +2453,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="52" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" s="52">
         <v>1</v>
@@ -2516,7 +2513,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C20" s="59">
         <v>0</v>
@@ -2608,7 +2605,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="65" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C21" s="66">
         <v>0</v>
@@ -2699,7 +2696,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="65" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C22" s="66">
         <v>0</v>
@@ -2791,7 +2788,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="65" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C23" s="66">
         <v>0</v>
@@ -2870,7 +2867,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C24" s="75">
         <v>0</v>
@@ -2940,7 +2937,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C25" s="75">
         <v>0</v>
@@ -3009,7 +3006,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26" s="75">
         <v>0</v>
@@ -3078,7 +3075,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C27" s="75">
         <v>0</v>
@@ -3147,7 +3144,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="81" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C28" s="82">
         <v>0</v>
@@ -3238,7 +3235,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="81" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C29" s="82">
         <v>0</v>
@@ -3329,7 +3326,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="81" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C30" s="82">
         <v>0</v>
@@ -3420,7 +3417,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="90" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C31" s="91">
         <v>0</v>
@@ -3511,7 +3508,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="99" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C32" s="100">
         <v>1</v>
@@ -3602,7 +3599,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="107" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C33" s="108">
         <v>1</v>
@@ -3693,7 +3690,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="107" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C34" s="108">
         <v>1</v>
@@ -3708,7 +3705,7 @@
         <v>24.864864900000001</v>
       </c>
       <c r="G34" s="109" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H34" s="111">
         <v>48.863636399999997</v>
@@ -3784,7 +3781,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="107" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C35" s="108">
         <v>1</v>
@@ -3867,7 +3864,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="117" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C36" s="118">
         <v>1</v>
@@ -3936,7 +3933,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="117" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C37" s="118">
         <v>1</v>
@@ -4005,7 +4002,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="117" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C38" s="118">
         <v>1</v>
@@ -4074,7 +4071,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="117" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C39" s="118">
         <v>1</v>
@@ -4143,7 +4140,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="126" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C40" s="127">
         <v>1</v>
@@ -4234,7 +4231,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="126" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C41" s="127">
         <v>1</v>
@@ -4325,7 +4322,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="126" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C42" s="127">
         <v>1</v>
@@ -4416,7 +4413,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="137" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C43" s="138">
         <v>1</v>

--- a/BD Cobre.xlsx
+++ b/BD Cobre.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julip\GitHub\Cobre\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD86618E-53A9-41CD-AEA7-E880D0AF1230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20490" yWindow="780" windowWidth="20460" windowHeight="10770" tabRatio="236" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20490" yWindow="780" windowWidth="20460" windowHeight="10770" tabRatio="236"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="45">
   <si>
     <t>id</t>
   </si>
@@ -54,9 +48,6 @@
   </si>
   <si>
     <t>gt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esporas </t>
   </si>
   <si>
     <t>Fe</t>
@@ -145,11 +136,41 @@
   <si>
     <t>in vitro</t>
   </si>
+  <si>
+    <t>Arb</t>
+  </si>
+  <si>
+    <t>Vesic</t>
+  </si>
+  <si>
+    <t>EsporasIntraRad</t>
+  </si>
+  <si>
+    <t>Entrada</t>
+  </si>
+  <si>
+    <t>MicelioExtra</t>
+  </si>
+  <si>
+    <t>MicelioMM</t>
+  </si>
+  <si>
+    <t>MicelioS</t>
+  </si>
+  <si>
+    <t>EsporasMM</t>
+  </si>
+  <si>
+    <t>EsporasS</t>
+  </si>
+  <si>
+    <t>LargoRaizMM</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -191,7 +212,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -276,8 +297,14 @@
         <bgColor rgb="FFF9CB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="26">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -636,12 +663,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -800,9 +851,6 @@
     <xf numFmtId="2" fontId="4" fillId="7" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -920,9 +968,6 @@
     <xf numFmtId="2" fontId="4" fillId="10" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1028,9 +1073,6 @@
     <xf numFmtId="2" fontId="4" fillId="13" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="13" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1123,11 +1165,49 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="8" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="8" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="11" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1397,21 +1477,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG43"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AP43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="10" max="11" width="14.5703125" customWidth="1"/>
+    <col min="12" max="14" width="9.85546875" customWidth="1"/>
+    <col min="15" max="15" width="15.85546875" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1425,99 +1509,126 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" s="172" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="S1" s="5" t="s">
+      <c r="AC1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="AD1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF1" s="161" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="AH1" s="158" t="s">
         <v>24</v>
       </c>
-      <c r="U1" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y1" s="161" t="s">
+      <c r="AI1" s="158" t="s">
         <v>25</v>
       </c>
-      <c r="Z1" s="161" t="s">
+      <c r="AJ1" s="158" t="s">
         <v>26</v>
       </c>
-      <c r="AA1" s="161" t="s">
+      <c r="AK1" s="158" t="s">
         <v>27</v>
       </c>
-      <c r="AB1" s="161" t="s">
+      <c r="AL1" s="158" t="s">
         <v>28</v>
       </c>
-      <c r="AC1" s="161" t="s">
+      <c r="AM1" s="159" t="s">
         <v>29</v>
       </c>
-      <c r="AD1" s="162" t="s">
+      <c r="AN1" t="s">
         <v>30</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AO1" t="s">
         <v>31</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AP1" t="s">
         <v>32</v>
       </c>
-      <c r="AG1" t="s">
-        <v>33</v>
-      </c>
     </row>
-    <row r="2" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="7">
         <v>0</v>
@@ -1531,49 +1642,64 @@
       <c r="F2" s="7">
         <v>0</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="7">
+        <v>0</v>
+      </c>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7">
+        <v>62.7</v>
+      </c>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="8">
         <v>5.5172413793103452</v>
       </c>
-      <c r="H2" s="8">
+      <c r="Q2" s="8">
         <v>19.65217391304348</v>
       </c>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="7">
+      <c r="R2" s="9"/>
+      <c r="S2" s="7">
         <v>2.6</v>
       </c>
-      <c r="L2" s="10">
+      <c r="T2" s="10">
         <v>50</v>
       </c>
-      <c r="M2" s="10">
+      <c r="U2" s="10">
         <v>44</v>
       </c>
-      <c r="N2" s="10">
+      <c r="V2" s="10">
         <v>37</v>
       </c>
-      <c r="O2" s="10">
+      <c r="W2" s="10">
         <v>30</v>
       </c>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="10">
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="7"/>
+      <c r="AA2" s="10">
         <v>103</v>
       </c>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9">
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="9">
         <v>410</v>
       </c>
-      <c r="W2" s="9"/>
-      <c r="X2" s="11"/>
+      <c r="AE2" s="9"/>
+      <c r="AF2" s="162">
+        <v>459.3</v>
+      </c>
+      <c r="AG2" s="11"/>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" s="12">
         <v>0</v>
@@ -1587,35 +1713,50 @@
       <c r="F3" s="12">
         <v>0</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="7">
+        <v>0</v>
+      </c>
+      <c r="H3" s="160"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="160"/>
+      <c r="K3" s="160"/>
+      <c r="L3" s="160">
+        <v>101</v>
+      </c>
+      <c r="M3" s="160"/>
+      <c r="N3" s="160"/>
+      <c r="O3" s="160"/>
+      <c r="P3" s="13">
         <v>4.6394984326018811</v>
       </c>
-      <c r="H3" s="13">
+      <c r="Q3" s="13">
         <v>20.086956521739133</v>
       </c>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
+      <c r="R3" s="14"/>
       <c r="S3" s="12"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="15"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+      <c r="V3" s="12"/>
+      <c r="W3" s="12"/>
+      <c r="X3" s="12"/>
+      <c r="Y3" s="12"/>
+      <c r="Z3" s="12"/>
+      <c r="AA3" s="12"/>
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="14"/>
+      <c r="AD3" s="14"/>
+      <c r="AE3" s="14"/>
+      <c r="AF3" s="163">
+        <v>536.6</v>
+      </c>
+      <c r="AG3" s="15"/>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" s="12">
         <v>0</v>
@@ -1629,35 +1770,48 @@
       <c r="F4" s="12">
         <v>0</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="7">
+        <v>0</v>
+      </c>
+      <c r="H4" s="160"/>
+      <c r="I4" s="160"/>
+      <c r="J4" s="160"/>
+      <c r="K4" s="160"/>
+      <c r="L4" s="160">
+        <v>88.5</v>
+      </c>
+      <c r="M4" s="160"/>
+      <c r="N4" s="160"/>
+      <c r="O4" s="160"/>
+      <c r="P4" s="13">
         <v>4.8902821316614427</v>
       </c>
-      <c r="H4" s="13">
+      <c r="Q4" s="13">
         <v>22</v>
       </c>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
+      <c r="R4" s="14"/>
       <c r="S4" s="12"/>
-      <c r="T4" s="14"/>
-      <c r="U4" s="14"/>
-      <c r="V4" s="14"/>
-      <c r="W4" s="14"/>
-      <c r="X4" s="15"/>
+      <c r="T4" s="12"/>
+      <c r="U4" s="12"/>
+      <c r="V4" s="12"/>
+      <c r="W4" s="12"/>
+      <c r="X4" s="12"/>
+      <c r="Y4" s="12"/>
+      <c r="Z4" s="12"/>
+      <c r="AA4" s="12"/>
+      <c r="AB4" s="14"/>
+      <c r="AC4" s="14"/>
+      <c r="AD4" s="14"/>
+      <c r="AE4" s="14"/>
+      <c r="AF4" s="163"/>
+      <c r="AG4" s="15"/>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" s="16">
         <v>0</v>
@@ -1671,49 +1825,66 @@
       <c r="F5" s="16">
         <v>0</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="16">
+        <v>0</v>
+      </c>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16">
+        <v>14.7</v>
+      </c>
+      <c r="M5" s="16">
+        <v>5</v>
+      </c>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="17">
         <v>3.0721003134796243</v>
       </c>
-      <c r="H5" s="17">
+      <c r="Q5" s="17">
         <v>22.260869565217391</v>
       </c>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="16">
+      <c r="R5" s="18"/>
+      <c r="S5" s="16">
         <v>2.6</v>
       </c>
-      <c r="L5" s="19">
+      <c r="T5" s="19">
         <v>99</v>
       </c>
-      <c r="M5" s="19">
+      <c r="U5" s="19">
         <v>50</v>
       </c>
-      <c r="N5" s="19">
+      <c r="V5" s="19">
         <v>30</v>
       </c>
-      <c r="O5" s="19">
+      <c r="W5" s="19">
         <v>30</v>
       </c>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
-      <c r="S5" s="19">
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="16"/>
+      <c r="AA5" s="19">
         <v>206</v>
       </c>
-      <c r="T5" s="18"/>
-      <c r="U5" s="18"/>
-      <c r="V5" s="18">
+      <c r="AB5" s="18"/>
+      <c r="AC5" s="18"/>
+      <c r="AD5" s="18">
         <v>430</v>
       </c>
-      <c r="W5" s="18"/>
-      <c r="X5" s="20"/>
+      <c r="AE5" s="18"/>
+      <c r="AF5" s="18">
+        <v>479.2</v>
+      </c>
+      <c r="AG5" s="20"/>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" s="16">
         <v>0</v>
@@ -1727,49 +1898,66 @@
       <c r="F6" s="16">
         <v>0</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="16">
+        <v>0</v>
+      </c>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16">
+        <v>14.7</v>
+      </c>
+      <c r="M6" s="16">
+        <v>5</v>
+      </c>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="17">
         <v>5.6457680250783708</v>
       </c>
-      <c r="H6" s="17">
+      <c r="Q6" s="17">
         <v>23.608695652173914</v>
       </c>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="19">
+      <c r="R6" s="18"/>
+      <c r="S6" s="19">
         <v>2.6</v>
       </c>
-      <c r="L6" s="19">
+      <c r="T6" s="19">
         <v>97</v>
       </c>
-      <c r="M6" s="19">
+      <c r="U6" s="19">
         <v>56</v>
       </c>
-      <c r="N6" s="19">
+      <c r="V6" s="19">
         <v>25</v>
       </c>
-      <c r="O6" s="19">
+      <c r="W6" s="19">
         <v>30</v>
       </c>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="19">
+      <c r="X6" s="16"/>
+      <c r="Y6" s="16"/>
+      <c r="Z6" s="16"/>
+      <c r="AA6" s="19">
         <v>203</v>
       </c>
-      <c r="T6" s="18"/>
-      <c r="U6" s="18"/>
-      <c r="V6" s="18">
+      <c r="AB6" s="18"/>
+      <c r="AC6" s="18"/>
+      <c r="AD6" s="18">
         <v>410</v>
       </c>
-      <c r="W6" s="18"/>
-      <c r="X6" s="20"/>
+      <c r="AE6" s="18"/>
+      <c r="AF6" s="18">
+        <v>421.8</v>
+      </c>
+      <c r="AG6" s="20"/>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" s="16">
         <v>0</v>
@@ -1783,49 +1971,66 @@
       <c r="F7" s="16">
         <v>0</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="16">
+        <v>0</v>
+      </c>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16">
+        <v>15.5</v>
+      </c>
+      <c r="M7" s="16">
+        <v>10</v>
+      </c>
+      <c r="N7" s="16"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="17">
         <v>4.7021943573667713</v>
       </c>
-      <c r="H7" s="17">
+      <c r="Q7" s="17">
         <v>25.913043478260867</v>
       </c>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="19">
+      <c r="R7" s="18"/>
+      <c r="S7" s="19">
         <v>2.6</v>
       </c>
-      <c r="L7" s="19">
+      <c r="T7" s="19">
         <v>100</v>
       </c>
-      <c r="M7" s="19">
+      <c r="U7" s="19">
         <v>42</v>
       </c>
-      <c r="N7" s="19">
+      <c r="V7" s="19">
         <v>32</v>
       </c>
-      <c r="O7" s="19">
+      <c r="W7" s="19">
         <v>30</v>
       </c>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
-      <c r="S7" s="19">
+      <c r="X7" s="16"/>
+      <c r="Y7" s="16"/>
+      <c r="Z7" s="16"/>
+      <c r="AA7" s="19">
         <v>184</v>
       </c>
-      <c r="T7" s="18"/>
-      <c r="U7" s="18"/>
-      <c r="V7" s="18">
+      <c r="AB7" s="18"/>
+      <c r="AC7" s="18"/>
+      <c r="AD7" s="18">
         <v>430</v>
       </c>
-      <c r="W7" s="18"/>
-      <c r="X7" s="20"/>
+      <c r="AE7" s="18"/>
+      <c r="AF7" s="18">
+        <v>536.6</v>
+      </c>
+      <c r="AG7" s="20"/>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" s="21">
         <v>0</v>
@@ -1839,49 +2044,66 @@
       <c r="F8" s="21">
         <v>0</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="21">
+        <v>0</v>
+      </c>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="M8" s="21">
+        <v>5</v>
+      </c>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="22">
         <v>3.8557993730407527</v>
       </c>
-      <c r="H8" s="22">
+      <c r="Q8" s="22">
         <v>22</v>
       </c>
-      <c r="I8" s="23"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="21">
+      <c r="R8" s="21"/>
+      <c r="S8" s="21">
         <v>2.5</v>
       </c>
-      <c r="L8" s="24">
+      <c r="T8" s="24">
         <v>93</v>
       </c>
-      <c r="M8" s="24">
+      <c r="U8" s="24">
         <v>57</v>
       </c>
-      <c r="N8" s="24">
+      <c r="V8" s="24">
         <v>32</v>
       </c>
-      <c r="O8" s="24">
+      <c r="W8" s="24">
         <v>30</v>
       </c>
-      <c r="P8" s="21"/>
-      <c r="Q8" s="21"/>
-      <c r="R8" s="21"/>
-      <c r="S8" s="24">
+      <c r="X8" s="21"/>
+      <c r="Y8" s="21"/>
+      <c r="Z8" s="21"/>
+      <c r="AA8" s="24">
         <v>278</v>
       </c>
-      <c r="T8" s="25"/>
-      <c r="U8" s="25"/>
-      <c r="V8" s="25">
+      <c r="AB8" s="25"/>
+      <c r="AC8" s="25"/>
+      <c r="AD8" s="25">
         <v>410</v>
       </c>
-      <c r="W8" s="25"/>
-      <c r="X8" s="26"/>
+      <c r="AE8" s="25"/>
+      <c r="AF8" s="164">
+        <v>319.5</v>
+      </c>
+      <c r="AG8" s="26"/>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9" s="21">
         <v>0</v>
@@ -1895,49 +2117,66 @@
       <c r="F9" s="21">
         <v>0</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="21">
+        <v>0</v>
+      </c>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="M9" s="21">
+        <v>9</v>
+      </c>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="22">
         <v>4.3260188087774303</v>
       </c>
-      <c r="H9" s="22">
+      <c r="Q9" s="22">
         <v>22.869565217391305</v>
       </c>
-      <c r="I9" s="23"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="24">
-        <v>2.6</v>
-      </c>
-      <c r="L9" s="24">
-        <v>97</v>
-      </c>
-      <c r="M9" s="24">
-        <v>40</v>
-      </c>
-      <c r="N9" s="24">
-        <v>29</v>
-      </c>
-      <c r="O9" s="24">
-        <v>30</v>
-      </c>
-      <c r="P9" s="21"/>
-      <c r="Q9" s="21"/>
       <c r="R9" s="21"/>
       <c r="S9" s="24">
+        <v>2.6</v>
+      </c>
+      <c r="T9" s="24">
+        <v>97</v>
+      </c>
+      <c r="U9" s="24">
+        <v>40</v>
+      </c>
+      <c r="V9" s="24">
+        <v>29</v>
+      </c>
+      <c r="W9" s="24">
+        <v>30</v>
+      </c>
+      <c r="X9" s="21"/>
+      <c r="Y9" s="21"/>
+      <c r="Z9" s="21"/>
+      <c r="AA9" s="24">
         <v>269</v>
       </c>
-      <c r="T9" s="25"/>
-      <c r="U9" s="25"/>
-      <c r="V9" s="25">
+      <c r="AB9" s="25"/>
+      <c r="AC9" s="25"/>
+      <c r="AD9" s="25">
         <v>410</v>
       </c>
-      <c r="W9" s="25"/>
-      <c r="X9" s="26"/>
+      <c r="AE9" s="25"/>
+      <c r="AF9" s="164">
+        <v>337</v>
+      </c>
+      <c r="AG9" s="26"/>
     </row>
-    <row r="10" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="23">
         <v>0</v>
@@ -1951,49 +2190,66 @@
       <c r="F10" s="23">
         <v>0</v>
       </c>
-      <c r="G10" s="27">
-        <v>4.2946708463949852</v>
-      </c>
-      <c r="H10" s="27">
-        <v>20.173913043478262</v>
-      </c>
+      <c r="G10" s="23">
+        <v>0</v>
+      </c>
+      <c r="H10" s="23"/>
       <c r="I10" s="23"/>
       <c r="J10" s="23"/>
-      <c r="K10" s="28">
-        <v>2.6</v>
-      </c>
-      <c r="L10" s="28">
-        <v>97</v>
-      </c>
-      <c r="M10" s="28">
-        <v>46</v>
-      </c>
-      <c r="N10" s="28">
-        <v>22</v>
-      </c>
-      <c r="O10" s="28">
-        <v>30</v>
-      </c>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M10" s="23">
+        <v>7</v>
+      </c>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="27">
+        <v>4.2946708463949852</v>
+      </c>
+      <c r="Q10" s="27">
+        <v>20.173913043478262</v>
+      </c>
       <c r="R10" s="23"/>
       <c r="S10" s="28">
+        <v>2.6</v>
+      </c>
+      <c r="T10" s="28">
+        <v>97</v>
+      </c>
+      <c r="U10" s="28">
+        <v>46</v>
+      </c>
+      <c r="V10" s="28">
+        <v>22</v>
+      </c>
+      <c r="W10" s="28">
+        <v>30</v>
+      </c>
+      <c r="X10" s="23"/>
+      <c r="Y10" s="23"/>
+      <c r="Z10" s="23"/>
+      <c r="AA10" s="28">
         <v>287</v>
       </c>
-      <c r="T10" s="29"/>
-      <c r="U10" s="29"/>
-      <c r="V10" s="29">
+      <c r="AB10" s="29"/>
+      <c r="AC10" s="29"/>
+      <c r="AD10" s="29">
         <v>420</v>
       </c>
-      <c r="W10" s="29"/>
-      <c r="X10" s="30"/>
+      <c r="AE10" s="29"/>
+      <c r="AF10" s="165">
+        <v>549.1</v>
+      </c>
+      <c r="AG10" s="30"/>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" s="31">
         <v>1</v>
@@ -2008,52 +2264,79 @@
         <v>42.68</v>
       </c>
       <c r="G11" s="32">
+        <v>32.93</v>
+      </c>
+      <c r="H11" s="32">
+        <v>48.78</v>
+      </c>
+      <c r="I11" s="32">
+        <v>73.17</v>
+      </c>
+      <c r="J11" s="32">
+        <v>97.56</v>
+      </c>
+      <c r="K11" s="32">
+        <v>2026.8</v>
+      </c>
+      <c r="L11" s="32">
+        <v>62.7</v>
+      </c>
+      <c r="M11" s="32">
+        <v>100</v>
+      </c>
+      <c r="N11" s="32">
+        <v>263</v>
+      </c>
+      <c r="O11" s="32">
+        <v>78.05</v>
+      </c>
+      <c r="P11" s="32">
         <v>4.2946708463949852</v>
       </c>
-      <c r="H11" s="32">
+      <c r="Q11" s="32">
         <v>20.956521739130434</v>
       </c>
-      <c r="I11" s="33">
-        <v>100</v>
-      </c>
-      <c r="J11" s="33">
+      <c r="R11" s="33">
         <v>62.7</v>
       </c>
-      <c r="K11" s="34">
+      <c r="S11" s="34">
         <v>2.6</v>
       </c>
-      <c r="L11" s="34">
+      <c r="T11" s="34">
         <v>53</v>
       </c>
-      <c r="M11" s="34">
+      <c r="U11" s="34">
         <v>48</v>
       </c>
-      <c r="N11" s="34">
+      <c r="V11" s="34">
         <v>29</v>
       </c>
-      <c r="O11" s="34">
+      <c r="W11" s="34">
         <v>30</v>
       </c>
-      <c r="P11" s="31"/>
-      <c r="Q11" s="31"/>
-      <c r="R11" s="31"/>
-      <c r="S11" s="34">
+      <c r="X11" s="31"/>
+      <c r="Y11" s="31"/>
+      <c r="Z11" s="31"/>
+      <c r="AA11" s="34">
         <v>99</v>
       </c>
-      <c r="T11" s="145"/>
-      <c r="U11" s="155"/>
-      <c r="V11" s="150">
+      <c r="AB11" s="142"/>
+      <c r="AC11" s="152"/>
+      <c r="AD11" s="147">
         <v>410</v>
       </c>
-      <c r="W11" s="33"/>
-      <c r="X11" s="35"/>
+      <c r="AE11" s="33"/>
+      <c r="AF11" s="142">
+        <v>693.9</v>
+      </c>
+      <c r="AG11" s="35"/>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" s="36">
         <v>1</v>
@@ -2068,52 +2351,79 @@
         <v>58.59</v>
       </c>
       <c r="G12" s="37">
+        <v>86.11</v>
+      </c>
+      <c r="H12" s="37">
+        <v>69.44</v>
+      </c>
+      <c r="I12" s="37">
+        <v>61.11</v>
+      </c>
+      <c r="J12" s="37">
+        <v>72.72</v>
+      </c>
+      <c r="K12" s="37">
+        <v>596.5</v>
+      </c>
+      <c r="L12" s="37">
+        <v>101</v>
+      </c>
+      <c r="M12" s="37">
+        <v>168</v>
+      </c>
+      <c r="N12" s="37">
+        <v>154</v>
+      </c>
+      <c r="O12" s="37">
+        <v>83.33</v>
+      </c>
+      <c r="P12" s="37">
         <v>4.0125391849529786</v>
       </c>
-      <c r="H12" s="37">
+      <c r="Q12" s="37">
         <v>23.043478260869566</v>
       </c>
-      <c r="I12" s="38">
-        <v>168</v>
-      </c>
-      <c r="J12" s="38">
+      <c r="R12" s="38">
         <v>101</v>
       </c>
-      <c r="K12" s="39">
+      <c r="S12" s="39">
         <v>2.7</v>
       </c>
-      <c r="L12" s="39">
+      <c r="T12" s="39">
         <v>45</v>
       </c>
-      <c r="M12" s="39">
+      <c r="U12" s="39">
         <v>42</v>
       </c>
-      <c r="N12" s="39">
+      <c r="V12" s="39">
         <v>27</v>
       </c>
-      <c r="O12" s="39">
+      <c r="W12" s="39">
         <v>30</v>
       </c>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
-      <c r="S12" s="39">
+      <c r="X12" s="36"/>
+      <c r="Y12" s="36"/>
+      <c r="Z12" s="36"/>
+      <c r="AA12" s="39">
         <v>101</v>
       </c>
-      <c r="T12" s="146"/>
-      <c r="U12" s="156"/>
-      <c r="V12" s="151">
+      <c r="AB12" s="143"/>
+      <c r="AC12" s="153"/>
+      <c r="AD12" s="148">
         <v>450</v>
       </c>
-      <c r="W12" s="38"/>
-      <c r="X12" s="40"/>
+      <c r="AE12" s="38"/>
+      <c r="AF12" s="143">
+        <v>681.4</v>
+      </c>
+      <c r="AG12" s="40"/>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" s="36">
         <v>1</v>
@@ -2129,33 +2439,44 @@
       </c>
       <c r="G13" s="37"/>
       <c r="H13" s="37"/>
-      <c r="I13" s="38">
+      <c r="I13" s="37"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="37">
+        <v>1297.9000000000001</v>
+      </c>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37">
         <v>154</v>
       </c>
-      <c r="J13" s="38">
+      <c r="N13" s="37"/>
+      <c r="O13" s="37"/>
+      <c r="P13" s="37"/>
+      <c r="Q13" s="37"/>
+      <c r="R13" s="38">
         <v>88.5</v>
       </c>
-      <c r="K13" s="36"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
       <c r="S13" s="36"/>
-      <c r="T13" s="146"/>
-      <c r="U13" s="156"/>
-      <c r="V13" s="151"/>
-      <c r="W13" s="38"/>
-      <c r="X13" s="40"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="36"/>
+      <c r="V13" s="36"/>
+      <c r="W13" s="36"/>
+      <c r="X13" s="36"/>
+      <c r="Y13" s="36"/>
+      <c r="Z13" s="36"/>
+      <c r="AA13" s="36"/>
+      <c r="AB13" s="143"/>
+      <c r="AC13" s="153"/>
+      <c r="AD13" s="148"/>
+      <c r="AE13" s="38"/>
+      <c r="AF13" s="143"/>
+      <c r="AG13" s="40"/>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" s="41">
         <v>1</v>
@@ -2169,53 +2490,80 @@
       <c r="F14" s="42">
         <v>29.41</v>
       </c>
-      <c r="G14" s="160">
+      <c r="G14" s="42">
+        <v>55.88</v>
+      </c>
+      <c r="H14" s="42">
+        <v>32.35</v>
+      </c>
+      <c r="I14" s="42">
+        <v>55.88</v>
+      </c>
+      <c r="J14" s="42">
+        <v>88.23</v>
+      </c>
+      <c r="K14" s="42">
+        <v>2486</v>
+      </c>
+      <c r="L14" s="42">
+        <v>124.6</v>
+      </c>
+      <c r="M14" s="42">
+        <v>184</v>
+      </c>
+      <c r="N14" s="42">
+        <v>93</v>
+      </c>
+      <c r="O14" s="42">
+        <v>44.12</v>
+      </c>
+      <c r="P14" s="157">
         <v>10.501567398119123</v>
       </c>
-      <c r="H14" s="42">
+      <c r="Q14" s="42">
         <v>19.434782608695652</v>
       </c>
-      <c r="I14" s="43">
-        <v>184</v>
-      </c>
-      <c r="J14" s="43">
+      <c r="R14" s="43">
         <v>124.6</v>
       </c>
-      <c r="K14" s="44">
+      <c r="S14" s="44">
         <v>2.4</v>
       </c>
-      <c r="L14" s="44">
+      <c r="T14" s="44">
         <v>89</v>
       </c>
-      <c r="M14" s="44">
+      <c r="U14" s="44">
         <v>63</v>
       </c>
-      <c r="N14" s="44">
+      <c r="V14" s="44">
         <v>30</v>
       </c>
-      <c r="O14" s="44">
+      <c r="W14" s="44">
         <v>15</v>
       </c>
-      <c r="P14" s="41"/>
-      <c r="Q14" s="41"/>
-      <c r="R14" s="41"/>
-      <c r="S14" s="44">
+      <c r="X14" s="41"/>
+      <c r="Y14" s="41"/>
+      <c r="Z14" s="41"/>
+      <c r="AA14" s="44">
         <v>171</v>
       </c>
-      <c r="T14" s="147"/>
-      <c r="U14" s="157"/>
-      <c r="V14" s="152">
+      <c r="AB14" s="144"/>
+      <c r="AC14" s="154"/>
+      <c r="AD14" s="149">
         <v>400</v>
       </c>
-      <c r="W14" s="43"/>
-      <c r="X14" s="45"/>
+      <c r="AE14" s="43"/>
+      <c r="AF14" s="43">
+        <v>451.8</v>
+      </c>
+      <c r="AG14" s="45"/>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" s="41">
         <v>1</v>
@@ -2230,52 +2578,79 @@
         <v>49.39</v>
       </c>
       <c r="G15" s="42">
+        <v>66.67</v>
+      </c>
+      <c r="H15" s="42">
+        <v>15.15</v>
+      </c>
+      <c r="I15" s="42">
+        <v>30.3</v>
+      </c>
+      <c r="J15" s="42">
+        <v>93.93</v>
+      </c>
+      <c r="K15" s="42">
+        <v>414.3</v>
+      </c>
+      <c r="L15" s="42">
+        <v>202</v>
+      </c>
+      <c r="M15" s="42">
+        <v>468</v>
+      </c>
+      <c r="N15" s="42">
+        <v>81</v>
+      </c>
+      <c r="O15" s="42">
+        <v>36.36</v>
+      </c>
+      <c r="P15" s="42">
         <v>3.949843260188088</v>
       </c>
-      <c r="H15" s="42">
+      <c r="Q15" s="42">
         <v>20.521739130434781</v>
       </c>
-      <c r="I15" s="43">
-        <v>468</v>
-      </c>
-      <c r="J15" s="43">
+      <c r="R15" s="43">
         <v>202</v>
       </c>
-      <c r="K15" s="44">
+      <c r="S15" s="44">
         <v>2.5</v>
       </c>
-      <c r="L15" s="44">
+      <c r="T15" s="44">
         <v>94</v>
       </c>
-      <c r="M15" s="44">
+      <c r="U15" s="44">
         <v>61</v>
       </c>
-      <c r="N15" s="44">
+      <c r="V15" s="44">
         <v>24</v>
       </c>
-      <c r="O15" s="44">
+      <c r="W15" s="44">
         <v>30</v>
       </c>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="41"/>
-      <c r="R15" s="41"/>
-      <c r="S15" s="44">
+      <c r="X15" s="41"/>
+      <c r="Y15" s="41"/>
+      <c r="Z15" s="41"/>
+      <c r="AA15" s="44">
         <v>208</v>
       </c>
-      <c r="T15" s="147"/>
-      <c r="U15" s="157"/>
-      <c r="V15" s="152">
+      <c r="AB15" s="144"/>
+      <c r="AC15" s="154"/>
+      <c r="AD15" s="149">
         <v>410</v>
       </c>
-      <c r="W15" s="43"/>
-      <c r="X15" s="45"/>
+      <c r="AE15" s="43"/>
+      <c r="AF15" s="43">
+        <v>486.7</v>
+      </c>
+      <c r="AG15" s="45"/>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" s="41">
         <v>1</v>
@@ -2290,50 +2665,77 @@
         <v>44.29</v>
       </c>
       <c r="G16" s="42">
+        <v>80</v>
+      </c>
+      <c r="H16" s="42">
+        <v>37.14</v>
+      </c>
+      <c r="I16" s="42">
+        <v>45.71</v>
+      </c>
+      <c r="J16" s="42">
+        <v>91.43</v>
+      </c>
+      <c r="K16" s="42">
+        <v>713.9</v>
+      </c>
+      <c r="L16" s="42">
+        <v>133.4</v>
+      </c>
+      <c r="M16" s="42">
+        <v>683</v>
+      </c>
+      <c r="N16" s="42">
+        <v>94</v>
+      </c>
+      <c r="O16" s="42">
+        <v>22.86</v>
+      </c>
+      <c r="P16" s="42">
         <v>2.7586206896551726</v>
       </c>
-      <c r="H16" s="46"/>
-      <c r="I16" s="43">
-        <v>683</v>
-      </c>
-      <c r="J16" s="43">
+      <c r="Q16" s="46"/>
+      <c r="R16" s="43">
         <v>133.4</v>
       </c>
-      <c r="K16" s="44">
+      <c r="S16" s="44">
         <v>2.6</v>
       </c>
-      <c r="L16" s="44">
+      <c r="T16" s="44">
         <v>58</v>
       </c>
-      <c r="M16" s="44">
+      <c r="U16" s="44">
         <v>51</v>
       </c>
-      <c r="N16" s="44">
+      <c r="V16" s="44">
         <v>38</v>
       </c>
-      <c r="O16" s="44">
+      <c r="W16" s="44">
         <v>15</v>
       </c>
-      <c r="P16" s="41"/>
-      <c r="Q16" s="41"/>
-      <c r="R16" s="41"/>
-      <c r="S16" s="44">
+      <c r="X16" s="41"/>
+      <c r="Y16" s="41"/>
+      <c r="Z16" s="41"/>
+      <c r="AA16" s="44">
         <v>94</v>
       </c>
-      <c r="T16" s="147"/>
-      <c r="U16" s="157"/>
-      <c r="V16" s="152">
+      <c r="AB16" s="144"/>
+      <c r="AC16" s="154"/>
+      <c r="AD16" s="149">
         <v>400</v>
       </c>
-      <c r="W16" s="43"/>
-      <c r="X16" s="45"/>
+      <c r="AE16" s="43"/>
+      <c r="AF16" s="43">
+        <v>526.70000000000005</v>
+      </c>
+      <c r="AG16" s="45"/>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" s="47">
         <v>1</v>
@@ -2348,52 +2750,79 @@
         <v>35</v>
       </c>
       <c r="G17" s="48">
+        <v>67.650000000000006</v>
+      </c>
+      <c r="H17" s="48">
+        <v>26.47</v>
+      </c>
+      <c r="I17" s="48">
+        <v>64.709999999999994</v>
+      </c>
+      <c r="J17" s="48">
+        <v>100</v>
+      </c>
+      <c r="K17" s="48">
+        <v>2533.4</v>
+      </c>
+      <c r="L17" s="48">
+        <v>55.3</v>
+      </c>
+      <c r="M17" s="48">
+        <v>12</v>
+      </c>
+      <c r="N17" s="48">
+        <v>220</v>
+      </c>
+      <c r="O17" s="48">
+        <v>32.35</v>
+      </c>
+      <c r="P17" s="48">
         <v>3.0094043887147337</v>
       </c>
-      <c r="H17" s="48">
+      <c r="Q17" s="48">
         <v>20.695652173913043</v>
       </c>
-      <c r="I17" s="49">
-        <v>12</v>
-      </c>
-      <c r="J17" s="49">
+      <c r="R17" s="49">
         <v>55.3</v>
       </c>
-      <c r="K17" s="50">
+      <c r="S17" s="50">
         <v>2.4</v>
       </c>
-      <c r="L17" s="50">
+      <c r="T17" s="50">
         <v>94</v>
       </c>
-      <c r="M17" s="50">
+      <c r="U17" s="50">
         <v>57</v>
       </c>
-      <c r="N17" s="50">
+      <c r="V17" s="50">
         <v>32</v>
       </c>
-      <c r="O17" s="50">
+      <c r="W17" s="50">
         <v>30</v>
       </c>
-      <c r="P17" s="47"/>
-      <c r="Q17" s="47"/>
-      <c r="R17" s="47"/>
-      <c r="S17" s="50">
+      <c r="X17" s="47"/>
+      <c r="Y17" s="47"/>
+      <c r="Z17" s="47"/>
+      <c r="AA17" s="50">
         <v>342</v>
       </c>
-      <c r="T17" s="148"/>
-      <c r="U17" s="158"/>
-      <c r="V17" s="153">
+      <c r="AB17" s="145"/>
+      <c r="AC17" s="155"/>
+      <c r="AD17" s="150">
         <v>390</v>
       </c>
-      <c r="W17" s="49"/>
-      <c r="X17" s="51"/>
+      <c r="AE17" s="49"/>
+      <c r="AF17" s="145">
+        <v>379.4</v>
+      </c>
+      <c r="AG17" s="51"/>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" s="47">
         <v>1</v>
@@ -2408,52 +2837,79 @@
         <v>37.72</v>
       </c>
       <c r="G18" s="48">
+        <v>74.36</v>
+      </c>
+      <c r="H18" s="48">
+        <v>43.59</v>
+      </c>
+      <c r="I18" s="48">
+        <v>56.41</v>
+      </c>
+      <c r="J18" s="48">
+        <v>97.44</v>
+      </c>
+      <c r="K18" s="48">
+        <v>3105</v>
+      </c>
+      <c r="L18" s="48">
+        <v>61.9</v>
+      </c>
+      <c r="M18" s="48">
+        <v>6</v>
+      </c>
+      <c r="N18" s="48">
+        <v>376</v>
+      </c>
+      <c r="O18" s="48">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="P18" s="48">
         <v>3.6677115987460818</v>
       </c>
-      <c r="H18" s="48">
+      <c r="Q18" s="48">
         <v>22.826086956521742</v>
       </c>
-      <c r="I18" s="49">
-        <v>6</v>
-      </c>
-      <c r="J18" s="49">
+      <c r="R18" s="49">
         <v>61.9</v>
       </c>
-      <c r="K18" s="50">
+      <c r="S18" s="50">
         <v>2.5</v>
       </c>
-      <c r="L18" s="50">
+      <c r="T18" s="50">
         <v>91</v>
       </c>
-      <c r="M18" s="50">
+      <c r="U18" s="50">
         <v>68</v>
       </c>
-      <c r="N18" s="50">
+      <c r="V18" s="50">
         <v>30</v>
       </c>
-      <c r="O18" s="50">
+      <c r="W18" s="50">
         <v>30</v>
       </c>
-      <c r="P18" s="47"/>
-      <c r="Q18" s="47"/>
-      <c r="R18" s="47"/>
-      <c r="S18" s="50">
+      <c r="X18" s="47"/>
+      <c r="Y18" s="47"/>
+      <c r="Z18" s="47"/>
+      <c r="AA18" s="50">
         <v>248</v>
       </c>
-      <c r="T18" s="148"/>
-      <c r="U18" s="158"/>
-      <c r="V18" s="153">
+      <c r="AB18" s="145"/>
+      <c r="AC18" s="155"/>
+      <c r="AD18" s="150">
         <v>390</v>
       </c>
-      <c r="W18" s="49"/>
-      <c r="X18" s="51"/>
+      <c r="AE18" s="49"/>
+      <c r="AF18" s="145">
+        <v>938.5</v>
+      </c>
+      <c r="AG18" s="51"/>
     </row>
-    <row r="19" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="52" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19" s="52">
         <v>1</v>
@@ -2468,2011 +2924,2264 @@
         <v>48.67</v>
       </c>
       <c r="G19" s="53">
+        <v>80.56</v>
+      </c>
+      <c r="H19" s="53">
+        <v>38.89</v>
+      </c>
+      <c r="I19" s="53">
+        <v>72.22</v>
+      </c>
+      <c r="J19" s="53">
+        <v>100</v>
+      </c>
+      <c r="K19" s="53">
+        <v>4086</v>
+      </c>
+      <c r="L19" s="53">
+        <v>92.9</v>
+      </c>
+      <c r="M19" s="53">
+        <v>8</v>
+      </c>
+      <c r="N19" s="53">
+        <v>596</v>
+      </c>
+      <c r="O19" s="53">
+        <v>75</v>
+      </c>
+      <c r="P19" s="53">
         <v>4.5454545454545459</v>
       </c>
-      <c r="H19" s="53">
+      <c r="Q19" s="53">
         <v>20.913043478260871</v>
       </c>
-      <c r="I19" s="54">
-        <v>8</v>
-      </c>
-      <c r="J19" s="55">
+      <c r="R19" s="54">
         <v>92.9</v>
       </c>
-      <c r="K19" s="56">
+      <c r="S19" s="55">
         <v>2.2999999999999998</v>
       </c>
-      <c r="L19" s="56">
+      <c r="T19" s="55">
         <v>91</v>
       </c>
-      <c r="M19" s="56">
+      <c r="U19" s="55">
         <v>30</v>
       </c>
-      <c r="N19" s="56">
+      <c r="V19" s="55">
         <v>25</v>
       </c>
-      <c r="O19" s="56">
+      <c r="W19" s="55">
         <v>40</v>
       </c>
-      <c r="P19" s="52"/>
-      <c r="Q19" s="52"/>
-      <c r="R19" s="52"/>
-      <c r="S19" s="56">
+      <c r="X19" s="52"/>
+      <c r="Y19" s="52"/>
+      <c r="Z19" s="52"/>
+      <c r="AA19" s="55">
         <v>306</v>
       </c>
-      <c r="T19" s="149"/>
-      <c r="U19" s="159"/>
-      <c r="V19" s="154">
+      <c r="AB19" s="146"/>
+      <c r="AC19" s="156"/>
+      <c r="AD19" s="151">
         <v>310</v>
       </c>
-      <c r="W19" s="55"/>
-      <c r="X19" s="57"/>
+      <c r="AE19" s="54"/>
+      <c r="AF19" s="146">
+        <v>649</v>
+      </c>
+      <c r="AG19" s="56"/>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="58" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="59">
-        <v>0</v>
-      </c>
-      <c r="D20" s="59">
-        <v>0</v>
-      </c>
-      <c r="E20" s="59">
-        <v>0</v>
-      </c>
-      <c r="F20" s="59">
-        <v>0</v>
-      </c>
-      <c r="G20" s="60">
+      <c r="B20" s="57" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="58">
+        <v>0</v>
+      </c>
+      <c r="D20" s="58">
+        <v>0</v>
+      </c>
+      <c r="E20" s="58">
+        <v>0</v>
+      </c>
+      <c r="F20" s="58">
+        <v>0</v>
+      </c>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="58"/>
+      <c r="K20" s="58"/>
+      <c r="L20" s="58"/>
+      <c r="M20" s="58"/>
+      <c r="N20" s="58"/>
+      <c r="O20" s="58"/>
+      <c r="P20" s="59">
         <v>47.480620199999997</v>
       </c>
-      <c r="H20" s="61">
+      <c r="Q20" s="60">
         <v>37.5</v>
       </c>
-      <c r="I20" s="59"/>
-      <c r="J20" s="62">
-        <v>0</v>
-      </c>
-      <c r="K20" s="59"/>
-      <c r="L20" s="59"/>
-      <c r="M20" s="59"/>
-      <c r="N20" s="59"/>
-      <c r="O20" s="59"/>
-      <c r="P20" s="60">
+      <c r="R20" s="61">
+        <v>0</v>
+      </c>
+      <c r="S20" s="58"/>
+      <c r="T20" s="58"/>
+      <c r="U20" s="58"/>
+      <c r="V20" s="58"/>
+      <c r="W20" s="58"/>
+      <c r="X20" s="59">
         <v>0.44742728999999998</v>
       </c>
-      <c r="Q20" s="60">
+      <c r="Y20" s="59">
         <v>0.41163311000000002</v>
       </c>
-      <c r="R20" s="60">
+      <c r="Z20" s="59">
         <v>0.92</v>
       </c>
-      <c r="S20" s="63">
+      <c r="AA20" s="62">
         <v>44.7</v>
       </c>
-      <c r="T20" s="63">
+      <c r="AB20" s="62">
         <v>18.399999999999999</v>
       </c>
-      <c r="U20" s="144">
+      <c r="AC20" s="141">
         <v>20</v>
       </c>
-      <c r="V20" s="63">
+      <c r="AD20" s="62">
         <v>662.5</v>
       </c>
-      <c r="W20" s="63">
+      <c r="AE20" s="62">
         <v>599</v>
       </c>
-      <c r="X20" s="64">
+      <c r="AF20" s="166"/>
+      <c r="AG20" s="63">
         <v>100</v>
       </c>
-      <c r="Y20" s="64">
+      <c r="AH20" s="63">
         <v>5.5</v>
       </c>
-      <c r="Z20" s="64">
+      <c r="AI20" s="63">
         <v>1.1176999999999999</v>
       </c>
-      <c r="AA20" s="64">
+      <c r="AJ20" s="63">
         <v>134</v>
       </c>
-      <c r="AB20" s="64">
+      <c r="AK20" s="63">
         <f>66.01+0.26</f>
         <v>66.27000000000001</v>
       </c>
-      <c r="AC20" s="64">
+      <c r="AL20" s="63">
         <v>12.5967</v>
       </c>
-      <c r="AD20" s="64">
+      <c r="AM20" s="63">
         <v>1565.5</v>
       </c>
-      <c r="AE20" s="64">
+      <c r="AN20" s="63">
         <v>283.64</v>
       </c>
-      <c r="AF20">
-        <f>T20/Y20</f>
+      <c r="AO20" s="63">
+        <f>AB20/AH20</f>
         <v>3.3454545454545452</v>
       </c>
-      <c r="AG20" s="163">
-        <f>Z20+AC20</f>
+      <c r="AP20" s="63">
+        <f>AI20+AL20</f>
         <v>13.714399999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="65" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="66">
-        <v>0</v>
-      </c>
-      <c r="D21" s="66">
-        <v>0</v>
-      </c>
-      <c r="E21" s="66">
-        <v>0</v>
-      </c>
-      <c r="F21" s="66">
-        <v>0</v>
-      </c>
-      <c r="G21" s="67">
+      <c r="B21" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="65">
+        <v>0</v>
+      </c>
+      <c r="D21" s="65">
+        <v>0</v>
+      </c>
+      <c r="E21" s="65">
+        <v>0</v>
+      </c>
+      <c r="F21" s="65">
+        <v>0</v>
+      </c>
+      <c r="G21" s="65"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="65"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="65"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="65"/>
+      <c r="P21" s="66">
         <v>49.418604700000003</v>
       </c>
-      <c r="H21" s="68">
+      <c r="Q21" s="67">
         <v>48.863636399999997</v>
       </c>
-      <c r="I21" s="66"/>
-      <c r="J21" s="69">
-        <v>0</v>
-      </c>
-      <c r="K21" s="66"/>
-      <c r="L21" s="66"/>
-      <c r="M21" s="66"/>
-      <c r="N21" s="66"/>
-      <c r="O21" s="66"/>
-      <c r="P21" s="67">
+      <c r="R21" s="68">
+        <v>0</v>
+      </c>
+      <c r="S21" s="65"/>
+      <c r="T21" s="65"/>
+      <c r="U21" s="65"/>
+      <c r="V21" s="65"/>
+      <c r="W21" s="65"/>
+      <c r="X21" s="66">
         <v>0.25917927000000002</v>
       </c>
-      <c r="Q21" s="67">
+      <c r="Y21" s="66">
         <v>0.38660907</v>
       </c>
-      <c r="R21" s="67">
+      <c r="Z21" s="66">
         <v>1.4916666700000001</v>
       </c>
-      <c r="S21" s="70">
+      <c r="AA21" s="69">
         <v>46.3</v>
       </c>
-      <c r="T21" s="70">
+      <c r="AB21" s="69">
         <v>17.899999999999999</v>
       </c>
-      <c r="U21" s="71">
+      <c r="AC21" s="70">
         <v>12</v>
       </c>
-      <c r="V21" s="70">
+      <c r="AD21" s="69">
         <v>632</v>
       </c>
-      <c r="W21" s="70">
+      <c r="AE21" s="69">
         <v>104</v>
       </c>
-      <c r="X21" s="72">
+      <c r="AF21" s="67"/>
+      <c r="AG21" s="71">
         <v>110</v>
       </c>
-      <c r="Y21" s="72">
+      <c r="AH21" s="71">
         <v>3.84</v>
       </c>
-      <c r="Z21" s="72">
+      <c r="AI21" s="71">
         <v>1.0099</v>
       </c>
-      <c r="AA21" s="72">
+      <c r="AJ21" s="71">
         <v>137</v>
       </c>
-      <c r="AB21" s="72">
+      <c r="AK21" s="71">
         <v>63.34</v>
       </c>
-      <c r="AC21" s="72">
+      <c r="AL21" s="71">
         <v>12.082800000000001</v>
       </c>
-      <c r="AD21" s="72">
+      <c r="AM21" s="71">
         <v>1970</v>
       </c>
-      <c r="AE21" s="72">
+      <c r="AN21" s="71">
         <v>512.02</v>
       </c>
-      <c r="AF21">
-        <f t="shared" ref="AF21:AF42" si="0">T21/Y21</f>
+      <c r="AO21" s="71">
+        <f t="shared" ref="AO21:AO42" si="0">AB21/AH21</f>
         <v>4.661458333333333</v>
       </c>
-      <c r="AG21" s="163">
-        <f t="shared" ref="AG21:AG43" si="1">Z21+AC21</f>
+      <c r="AP21" s="71">
+        <f t="shared" ref="AP21:AP43" si="1">AI21+AL21</f>
         <v>13.092700000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="65" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="66">
-        <v>0</v>
-      </c>
-      <c r="D22" s="66">
-        <v>0</v>
-      </c>
-      <c r="E22" s="66">
-        <v>0</v>
-      </c>
-      <c r="F22" s="66">
-        <v>0</v>
-      </c>
-      <c r="G22" s="67">
+      <c r="B22" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="65">
+        <v>0</v>
+      </c>
+      <c r="D22" s="65">
+        <v>0</v>
+      </c>
+      <c r="E22" s="65">
+        <v>0</v>
+      </c>
+      <c r="F22" s="65">
+        <v>0</v>
+      </c>
+      <c r="G22" s="65"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="65"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="65"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="65"/>
+      <c r="P22" s="66">
         <v>57.170542699999999</v>
       </c>
-      <c r="H22" s="68">
+      <c r="Q22" s="67">
         <v>20.454545499999998</v>
       </c>
-      <c r="I22" s="66"/>
-      <c r="J22" s="69">
-        <v>0</v>
-      </c>
-      <c r="K22" s="66"/>
-      <c r="L22" s="66"/>
-      <c r="M22" s="66"/>
-      <c r="N22" s="66"/>
-      <c r="O22" s="66"/>
-      <c r="P22" s="67">
+      <c r="R22" s="68">
+        <v>0</v>
+      </c>
+      <c r="S22" s="65"/>
+      <c r="T22" s="65"/>
+      <c r="U22" s="65"/>
+      <c r="V22" s="65"/>
+      <c r="W22" s="65"/>
+      <c r="X22" s="66">
         <v>0.28021015999999999</v>
       </c>
-      <c r="Q22" s="67">
+      <c r="Y22" s="66">
         <v>0.88791593999999996</v>
       </c>
-      <c r="R22" s="67">
+      <c r="Z22" s="66">
         <v>3.1687500000000002</v>
       </c>
-      <c r="S22" s="70">
+      <c r="AA22" s="69">
         <v>57.1</v>
       </c>
-      <c r="T22" s="70">
+      <c r="AB22" s="69">
         <v>50.7</v>
       </c>
-      <c r="U22" s="71">
+      <c r="AC22" s="70">
         <v>16</v>
       </c>
-      <c r="V22" s="70">
+      <c r="AD22" s="69">
         <v>693</v>
       </c>
-      <c r="W22" s="70">
+      <c r="AE22" s="69">
         <v>804</v>
       </c>
-      <c r="X22" s="72">
+      <c r="AF22" s="67"/>
+      <c r="AG22" s="71">
         <v>191</v>
       </c>
-      <c r="Y22" s="72">
+      <c r="AH22" s="71">
         <v>4.18</v>
       </c>
-      <c r="Z22" s="72">
+      <c r="AI22" s="71">
         <v>0.87560000000000004</v>
       </c>
-      <c r="AA22" s="72">
+      <c r="AJ22" s="71">
         <v>135</v>
       </c>
-      <c r="AB22" s="72">
+      <c r="AK22" s="71">
         <f>60.98+0.62</f>
         <v>61.599999999999994</v>
       </c>
-      <c r="AC22" s="72">
+      <c r="AL22" s="71">
         <v>9.5932999999999993</v>
       </c>
-      <c r="AD22" s="72">
+      <c r="AM22" s="71">
         <v>976.6</v>
       </c>
-      <c r="AE22" s="72">
+      <c r="AN22" s="71">
         <v>232.64</v>
       </c>
-      <c r="AF22">
+      <c r="AO22" s="71">
         <f t="shared" si="0"/>
         <v>12.129186602870815</v>
       </c>
-      <c r="AG22" s="163">
+      <c r="AP22" s="71">
         <f t="shared" si="1"/>
         <v>10.4689</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="65" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="66">
-        <v>0</v>
-      </c>
-      <c r="D23" s="66">
-        <v>0</v>
-      </c>
-      <c r="E23" s="66">
-        <v>0</v>
-      </c>
-      <c r="F23" s="66">
-        <v>0</v>
-      </c>
-      <c r="G23" s="67">
+      <c r="B23" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="65">
+        <v>0</v>
+      </c>
+      <c r="D23" s="65">
+        <v>0</v>
+      </c>
+      <c r="E23" s="65">
+        <v>0</v>
+      </c>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="65"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="65"/>
+      <c r="M23" s="65"/>
+      <c r="N23" s="65"/>
+      <c r="O23" s="65"/>
+      <c r="P23" s="66">
         <v>67.829457399999995</v>
       </c>
-      <c r="H23" s="68">
+      <c r="Q23" s="67">
         <v>37.5</v>
       </c>
-      <c r="I23" s="66"/>
-      <c r="J23" s="69">
-        <v>0</v>
-      </c>
-      <c r="K23" s="66"/>
-      <c r="L23" s="66"/>
-      <c r="M23" s="66"/>
-      <c r="N23" s="66"/>
-      <c r="O23" s="66"/>
-      <c r="P23" s="67">
+      <c r="R23" s="68">
+        <v>0</v>
+      </c>
+      <c r="S23" s="65"/>
+      <c r="T23" s="65"/>
+      <c r="U23" s="65"/>
+      <c r="V23" s="65"/>
+      <c r="W23" s="65"/>
+      <c r="X23" s="66">
         <v>0.24640656999999999</v>
       </c>
-      <c r="Q23" s="67"/>
-      <c r="R23" s="67"/>
-      <c r="S23" s="70">
+      <c r="Y23" s="66"/>
+      <c r="Z23" s="66"/>
+      <c r="AA23" s="69">
         <v>48.7</v>
       </c>
-      <c r="T23" s="73"/>
-      <c r="U23" s="71">
+      <c r="AB23" s="72"/>
+      <c r="AC23" s="70">
         <v>12</v>
       </c>
-      <c r="V23" s="70">
+      <c r="AD23" s="69">
         <v>697.4</v>
       </c>
-      <c r="W23" s="73"/>
-      <c r="X23" s="72">
+      <c r="AE23" s="72"/>
+      <c r="AF23" s="167"/>
+      <c r="AG23" s="71">
         <v>566</v>
       </c>
-      <c r="Y23" s="72">
+      <c r="AH23" s="71">
         <v>4.7</v>
       </c>
-      <c r="Z23" s="72">
+      <c r="AI23" s="71">
         <v>0.9617</v>
       </c>
-      <c r="AA23" s="72">
+      <c r="AJ23" s="71">
         <v>117</v>
       </c>
-      <c r="AB23" s="72">
+      <c r="AK23" s="71">
         <v>56.13</v>
       </c>
-      <c r="AC23" s="72">
+      <c r="AL23" s="71">
         <v>10.324999999999999</v>
       </c>
-      <c r="AD23" s="72">
+      <c r="AM23" s="71">
         <v>1405.3</v>
       </c>
-      <c r="AE23" s="72">
+      <c r="AN23" s="71">
         <v>298</v>
       </c>
-      <c r="AG23" s="163">
+      <c r="AO23" s="71"/>
+      <c r="AP23" s="71">
         <f t="shared" si="1"/>
         <v>11.2867</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="74" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="75">
-        <v>0</v>
-      </c>
-      <c r="D24" s="75">
+      <c r="B24" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="74">
+        <v>0</v>
+      </c>
+      <c r="D24" s="74">
         <v>1</v>
       </c>
-      <c r="E24" s="75">
-        <v>0</v>
-      </c>
-      <c r="F24" s="75">
-        <v>0</v>
-      </c>
-      <c r="G24" s="76">
+      <c r="E24" s="74">
+        <v>0</v>
+      </c>
+      <c r="F24" s="74">
+        <v>0</v>
+      </c>
+      <c r="G24" s="74"/>
+      <c r="H24" s="74"/>
+      <c r="I24" s="74"/>
+      <c r="J24" s="74"/>
+      <c r="K24" s="74"/>
+      <c r="L24" s="74"/>
+      <c r="M24" s="74"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="74"/>
+      <c r="P24" s="75">
         <v>59.59</v>
       </c>
-      <c r="H24" s="77">
+      <c r="Q24" s="76">
         <v>42.045454599999999</v>
       </c>
-      <c r="I24" s="75"/>
-      <c r="J24" s="78">
-        <v>0</v>
-      </c>
-      <c r="K24" s="75"/>
-      <c r="L24" s="75"/>
-      <c r="M24" s="75"/>
-      <c r="N24" s="75"/>
-      <c r="O24" s="75"/>
-      <c r="P24" s="75"/>
-      <c r="Q24" s="75"/>
-      <c r="R24" s="75"/>
-      <c r="S24" s="75"/>
-      <c r="T24" s="75"/>
-      <c r="U24" s="75"/>
-      <c r="V24" s="75"/>
-      <c r="W24" s="75"/>
-      <c r="X24" s="79"/>
-      <c r="Y24" s="79">
+      <c r="R24" s="77">
+        <v>0</v>
+      </c>
+      <c r="S24" s="74"/>
+      <c r="T24" s="74"/>
+      <c r="U24" s="74"/>
+      <c r="V24" s="74"/>
+      <c r="W24" s="74"/>
+      <c r="X24" s="74"/>
+      <c r="Y24" s="74"/>
+      <c r="Z24" s="74"/>
+      <c r="AA24" s="74"/>
+      <c r="AB24" s="74"/>
+      <c r="AC24" s="74"/>
+      <c r="AD24" s="74"/>
+      <c r="AE24" s="74"/>
+      <c r="AF24" s="168"/>
+      <c r="AG24" s="78"/>
+      <c r="AH24" s="78">
         <v>6.1</v>
       </c>
-      <c r="Z24" s="79">
+      <c r="AI24" s="78">
         <v>0.83899999999999997</v>
       </c>
-      <c r="AA24" s="79">
+      <c r="AJ24" s="78">
         <v>121</v>
       </c>
-      <c r="AB24" s="79">
+      <c r="AK24" s="78">
         <f>46.77+0.83</f>
         <v>47.6</v>
       </c>
-      <c r="AC24" s="79">
+      <c r="AL24" s="78">
         <v>9.7091999999999992</v>
       </c>
-      <c r="AD24" s="79">
+      <c r="AM24" s="78">
         <v>1347.49</v>
       </c>
-      <c r="AE24" s="79">
+      <c r="AN24" s="78">
         <v>219.9</v>
       </c>
-      <c r="AG24" s="163">
+      <c r="AO24" s="78"/>
+      <c r="AP24" s="78">
         <f t="shared" si="1"/>
         <v>10.5482</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="74" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="75">
-        <v>0</v>
-      </c>
-      <c r="D25" s="75">
+      <c r="B25" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="74">
+        <v>0</v>
+      </c>
+      <c r="D25" s="74">
         <v>1</v>
       </c>
-      <c r="E25" s="75">
-        <v>0</v>
-      </c>
-      <c r="F25" s="75">
-        <v>0</v>
-      </c>
-      <c r="G25" s="76">
+      <c r="E25" s="74">
+        <v>0</v>
+      </c>
+      <c r="F25" s="74">
+        <v>0</v>
+      </c>
+      <c r="G25" s="74"/>
+      <c r="H25" s="74"/>
+      <c r="I25" s="74"/>
+      <c r="J25" s="74"/>
+      <c r="K25" s="74"/>
+      <c r="L25" s="74"/>
+      <c r="M25" s="74"/>
+      <c r="N25" s="74"/>
+      <c r="O25" s="74"/>
+      <c r="P25" s="75">
         <v>61.53</v>
       </c>
-      <c r="H25" s="80">
+      <c r="Q25" s="79">
         <v>51.136363699999997</v>
       </c>
-      <c r="I25" s="75"/>
-      <c r="J25" s="78">
-        <v>0</v>
-      </c>
-      <c r="K25" s="75"/>
-      <c r="L25" s="75"/>
-      <c r="M25" s="75"/>
-      <c r="N25" s="75"/>
-      <c r="O25" s="75"/>
-      <c r="P25" s="75"/>
-      <c r="Q25" s="75"/>
-      <c r="R25" s="75"/>
-      <c r="S25" s="75"/>
-      <c r="T25" s="75"/>
-      <c r="U25" s="75"/>
-      <c r="V25" s="75"/>
-      <c r="W25" s="75"/>
-      <c r="X25" s="79"/>
-      <c r="Y25" s="79">
+      <c r="R25" s="77">
+        <v>0</v>
+      </c>
+      <c r="S25" s="74"/>
+      <c r="T25" s="74"/>
+      <c r="U25" s="74"/>
+      <c r="V25" s="74"/>
+      <c r="W25" s="74"/>
+      <c r="X25" s="74"/>
+      <c r="Y25" s="74"/>
+      <c r="Z25" s="74"/>
+      <c r="AA25" s="74"/>
+      <c r="AB25" s="74"/>
+      <c r="AC25" s="74"/>
+      <c r="AD25" s="74"/>
+      <c r="AE25" s="74"/>
+      <c r="AF25" s="168"/>
+      <c r="AG25" s="78"/>
+      <c r="AH25" s="78">
         <v>2.7</v>
       </c>
-      <c r="Z25" s="79">
+      <c r="AI25" s="78">
         <v>0.55459999999999998</v>
       </c>
-      <c r="AA25" s="79">
+      <c r="AJ25" s="78">
         <v>158</v>
       </c>
-      <c r="AB25" s="79">
+      <c r="AK25" s="78">
         <v>69.430000000000007</v>
       </c>
-      <c r="AC25" s="79">
+      <c r="AL25" s="78">
         <v>12.512700000000001</v>
       </c>
-      <c r="AD25" s="79">
+      <c r="AM25" s="78">
         <v>1340.09</v>
       </c>
-      <c r="AE25" s="79">
+      <c r="AN25" s="78">
         <v>495.33</v>
       </c>
-      <c r="AG25" s="163">
+      <c r="AO25" s="78"/>
+      <c r="AP25" s="78">
         <f t="shared" si="1"/>
         <v>13.067300000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="74" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="75">
-        <v>0</v>
-      </c>
-      <c r="D26" s="75">
+      <c r="B26" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="74">
+        <v>0</v>
+      </c>
+      <c r="D26" s="74">
         <v>1</v>
       </c>
-      <c r="E26" s="75">
-        <v>0</v>
-      </c>
-      <c r="F26" s="75">
-        <v>0</v>
-      </c>
-      <c r="G26" s="76">
+      <c r="E26" s="74">
+        <v>0</v>
+      </c>
+      <c r="F26" s="74">
+        <v>0</v>
+      </c>
+      <c r="G26" s="74"/>
+      <c r="H26" s="74"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="74"/>
+      <c r="K26" s="74"/>
+      <c r="L26" s="74"/>
+      <c r="M26" s="74"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="74"/>
+      <c r="P26" s="75">
         <v>35.369999999999997</v>
       </c>
-      <c r="H26" s="80">
+      <c r="Q26" s="79">
         <v>40.340909099999998</v>
       </c>
-      <c r="I26" s="75"/>
-      <c r="J26" s="78">
-        <v>0</v>
-      </c>
-      <c r="K26" s="75"/>
-      <c r="L26" s="75"/>
-      <c r="M26" s="75"/>
-      <c r="N26" s="75"/>
-      <c r="O26" s="75"/>
-      <c r="P26" s="75"/>
-      <c r="Q26" s="75"/>
-      <c r="R26" s="75"/>
-      <c r="S26" s="75"/>
-      <c r="T26" s="75"/>
-      <c r="U26" s="75"/>
-      <c r="V26" s="75"/>
-      <c r="W26" s="75"/>
-      <c r="X26" s="79"/>
-      <c r="Y26" s="79">
+      <c r="R26" s="77">
+        <v>0</v>
+      </c>
+      <c r="S26" s="74"/>
+      <c r="T26" s="74"/>
+      <c r="U26" s="74"/>
+      <c r="V26" s="74"/>
+      <c r="W26" s="74"/>
+      <c r="X26" s="74"/>
+      <c r="Y26" s="74"/>
+      <c r="Z26" s="74"/>
+      <c r="AA26" s="74"/>
+      <c r="AB26" s="74"/>
+      <c r="AC26" s="74"/>
+      <c r="AD26" s="74"/>
+      <c r="AE26" s="74"/>
+      <c r="AF26" s="168"/>
+      <c r="AG26" s="78"/>
+      <c r="AH26" s="78">
         <v>1.64</v>
       </c>
-      <c r="Z26" s="79">
+      <c r="AI26" s="78">
         <v>0.4622</v>
       </c>
-      <c r="AA26" s="79">
+      <c r="AJ26" s="78">
         <v>120</v>
       </c>
-      <c r="AB26" s="79">
+      <c r="AK26" s="78">
         <v>45.52</v>
       </c>
-      <c r="AC26" s="79">
+      <c r="AL26" s="78">
         <v>7.8204000000000002</v>
       </c>
-      <c r="AD26" s="79">
+      <c r="AM26" s="78">
         <v>1229.77</v>
       </c>
-      <c r="AE26" s="79">
+      <c r="AN26" s="78">
         <v>748.86</v>
       </c>
-      <c r="AG26" s="163">
+      <c r="AO26" s="78"/>
+      <c r="AP26" s="78">
         <f t="shared" si="1"/>
         <v>8.2826000000000004</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="74" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="75">
-        <v>0</v>
-      </c>
-      <c r="D27" s="75">
+      <c r="B27" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="74">
+        <v>0</v>
+      </c>
+      <c r="D27" s="74">
         <v>1</v>
       </c>
-      <c r="E27" s="75">
-        <v>0</v>
-      </c>
-      <c r="F27" s="75">
-        <v>0</v>
-      </c>
-      <c r="G27" s="76">
+      <c r="E27" s="74">
+        <v>0</v>
+      </c>
+      <c r="F27" s="74">
+        <v>0</v>
+      </c>
+      <c r="G27" s="74"/>
+      <c r="H27" s="74"/>
+      <c r="I27" s="74"/>
+      <c r="J27" s="74"/>
+      <c r="K27" s="74"/>
+      <c r="L27" s="74"/>
+      <c r="M27" s="74"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="74"/>
+      <c r="P27" s="75">
         <v>38.76</v>
       </c>
-      <c r="H27" s="80">
+      <c r="Q27" s="79">
         <v>40.340909099999998</v>
       </c>
-      <c r="I27" s="75"/>
-      <c r="J27" s="78">
-        <v>0</v>
-      </c>
-      <c r="K27" s="75"/>
-      <c r="L27" s="75"/>
-      <c r="M27" s="75"/>
-      <c r="N27" s="75"/>
-      <c r="O27" s="75"/>
-      <c r="P27" s="75"/>
-      <c r="Q27" s="75"/>
-      <c r="R27" s="75"/>
-      <c r="S27" s="75"/>
-      <c r="T27" s="75"/>
-      <c r="U27" s="75"/>
-      <c r="V27" s="75"/>
-      <c r="W27" s="75"/>
-      <c r="X27" s="79"/>
-      <c r="Y27" s="79">
+      <c r="R27" s="77">
+        <v>0</v>
+      </c>
+      <c r="S27" s="74"/>
+      <c r="T27" s="74"/>
+      <c r="U27" s="74"/>
+      <c r="V27" s="74"/>
+      <c r="W27" s="74"/>
+      <c r="X27" s="74"/>
+      <c r="Y27" s="74"/>
+      <c r="Z27" s="74"/>
+      <c r="AA27" s="74"/>
+      <c r="AB27" s="74"/>
+      <c r="AC27" s="74"/>
+      <c r="AD27" s="74"/>
+      <c r="AE27" s="74"/>
+      <c r="AF27" s="168"/>
+      <c r="AG27" s="78"/>
+      <c r="AH27" s="78">
         <v>3.3</v>
       </c>
-      <c r="Z27" s="79">
+      <c r="AI27" s="78">
         <v>0.39300000000000002</v>
       </c>
-      <c r="AA27" s="79">
+      <c r="AJ27" s="78">
         <v>69</v>
       </c>
-      <c r="AB27" s="79">
+      <c r="AK27" s="78">
         <v>43.58</v>
       </c>
-      <c r="AC27" s="79">
+      <c r="AL27" s="78">
         <v>5.5315000000000003</v>
       </c>
-      <c r="AD27" s="79">
+      <c r="AM27" s="78">
         <v>1411.55</v>
       </c>
-      <c r="AE27" s="79">
+      <c r="AN27" s="78">
         <v>426.74</v>
       </c>
-      <c r="AG27" s="163">
+      <c r="AO27" s="78"/>
+      <c r="AP27" s="78">
         <f t="shared" si="1"/>
         <v>5.9245000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="81" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="82">
-        <v>0</v>
-      </c>
-      <c r="D28" s="82">
+      <c r="B28" s="80" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="81">
+        <v>0</v>
+      </c>
+      <c r="D28" s="81">
         <v>2</v>
       </c>
-      <c r="E28" s="82">
-        <v>0</v>
-      </c>
-      <c r="F28" s="82">
-        <v>0</v>
-      </c>
-      <c r="G28" s="83">
+      <c r="E28" s="81">
+        <v>0</v>
+      </c>
+      <c r="F28" s="81">
+        <v>0</v>
+      </c>
+      <c r="G28" s="81"/>
+      <c r="H28" s="81"/>
+      <c r="I28" s="81"/>
+      <c r="J28" s="81"/>
+      <c r="K28" s="81"/>
+      <c r="L28" s="81"/>
+      <c r="M28" s="81"/>
+      <c r="N28" s="81"/>
+      <c r="O28" s="81"/>
+      <c r="P28" s="82">
         <v>39.729999999999997</v>
       </c>
-      <c r="H28" s="84">
+      <c r="Q28" s="83">
         <v>40.909090900000002</v>
       </c>
-      <c r="I28" s="82"/>
-      <c r="J28" s="85">
-        <v>0</v>
-      </c>
-      <c r="K28" s="82"/>
-      <c r="L28" s="82"/>
-      <c r="M28" s="82"/>
-      <c r="N28" s="82"/>
-      <c r="O28" s="82"/>
-      <c r="P28" s="83">
+      <c r="R28" s="84">
+        <v>0</v>
+      </c>
+      <c r="S28" s="81"/>
+      <c r="T28" s="81"/>
+      <c r="U28" s="81"/>
+      <c r="V28" s="81"/>
+      <c r="W28" s="81"/>
+      <c r="X28" s="82">
         <v>7.6394190000000001E-2</v>
       </c>
-      <c r="Q28" s="83">
+      <c r="Y28" s="82">
         <v>0.23529412</v>
       </c>
-      <c r="R28" s="83">
+      <c r="Z28" s="82">
         <v>3.08</v>
       </c>
-      <c r="S28" s="86">
+      <c r="AA28" s="85">
         <v>130.9</v>
       </c>
-      <c r="T28" s="86">
+      <c r="AB28" s="85">
         <v>30.8</v>
       </c>
-      <c r="U28" s="87">
+      <c r="AC28" s="86">
         <v>10</v>
       </c>
-      <c r="V28" s="86">
+      <c r="AD28" s="85">
         <v>636.4</v>
       </c>
-      <c r="W28" s="86">
+      <c r="AE28" s="85">
         <v>759</v>
       </c>
-      <c r="X28" s="88">
+      <c r="AF28" s="88"/>
+      <c r="AG28" s="87">
         <v>808</v>
       </c>
-      <c r="Y28" s="88">
+      <c r="AH28" s="87">
         <v>2.2999999999999998</v>
       </c>
-      <c r="Z28" s="88">
+      <c r="AI28" s="87">
         <v>0.60680000000000001</v>
       </c>
-      <c r="AA28" s="88">
+      <c r="AJ28" s="87">
         <v>116</v>
       </c>
-      <c r="AB28" s="88">
+      <c r="AK28" s="87">
         <v>59.53</v>
       </c>
-      <c r="AC28" s="88">
+      <c r="AL28" s="87">
         <v>10.5433</v>
       </c>
-      <c r="AD28" s="88">
+      <c r="AM28" s="87">
         <v>1313.02</v>
       </c>
-      <c r="AE28" s="88">
+      <c r="AN28" s="87">
         <v>569.88</v>
       </c>
-      <c r="AF28">
+      <c r="AO28" s="87">
         <f t="shared" si="0"/>
         <v>13.391304347826088</v>
       </c>
-      <c r="AG28" s="163">
+      <c r="AP28" s="87">
         <f t="shared" si="1"/>
         <v>11.1501</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="81" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="82">
-        <v>0</v>
-      </c>
-      <c r="D29" s="82">
+      <c r="B29" s="80" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="81">
+        <v>0</v>
+      </c>
+      <c r="D29" s="81">
         <v>2</v>
       </c>
-      <c r="E29" s="82">
-        <v>0</v>
-      </c>
-      <c r="F29" s="82">
-        <v>0</v>
-      </c>
-      <c r="G29" s="83">
+      <c r="E29" s="81">
+        <v>0</v>
+      </c>
+      <c r="F29" s="81">
+        <v>0</v>
+      </c>
+      <c r="G29" s="81"/>
+      <c r="H29" s="81"/>
+      <c r="I29" s="81"/>
+      <c r="J29" s="81"/>
+      <c r="K29" s="81"/>
+      <c r="L29" s="81"/>
+      <c r="M29" s="81"/>
+      <c r="N29" s="81"/>
+      <c r="O29" s="81"/>
+      <c r="P29" s="82">
         <v>30.04</v>
       </c>
-      <c r="H29" s="89">
+      <c r="Q29" s="88">
         <v>33.5227273</v>
       </c>
-      <c r="I29" s="82"/>
-      <c r="J29" s="85">
-        <v>0</v>
-      </c>
-      <c r="K29" s="82"/>
-      <c r="L29" s="82"/>
-      <c r="M29" s="82"/>
-      <c r="N29" s="82"/>
-      <c r="O29" s="82"/>
-      <c r="P29" s="83">
+      <c r="R29" s="84">
+        <v>0</v>
+      </c>
+      <c r="S29" s="81"/>
+      <c r="T29" s="81"/>
+      <c r="U29" s="81"/>
+      <c r="V29" s="81"/>
+      <c r="W29" s="81"/>
+      <c r="X29" s="82">
         <v>0.17080745</v>
       </c>
-      <c r="Q29" s="83">
+      <c r="Y29" s="82">
         <v>0.60248447000000005</v>
       </c>
-      <c r="R29" s="83">
+      <c r="Z29" s="82">
         <v>3.52727273</v>
       </c>
-      <c r="S29" s="86">
+      <c r="AA29" s="85">
         <v>64.400000000000006</v>
       </c>
-      <c r="T29" s="86">
+      <c r="AB29" s="85">
         <v>38.799999999999997</v>
       </c>
-      <c r="U29" s="87">
+      <c r="AC29" s="86">
         <v>11</v>
       </c>
-      <c r="V29" s="86">
+      <c r="AD29" s="85">
         <v>658.2</v>
       </c>
-      <c r="W29" s="86">
+      <c r="AE29" s="85">
         <v>660</v>
       </c>
-      <c r="X29" s="88">
+      <c r="AF29" s="88"/>
+      <c r="AG29" s="87">
         <v>668</v>
       </c>
-      <c r="Y29" s="88">
+      <c r="AH29" s="87">
         <v>3.97</v>
       </c>
-      <c r="Z29" s="88">
+      <c r="AI29" s="87">
         <v>1.089</v>
       </c>
-      <c r="AA29" s="88">
+      <c r="AJ29" s="87">
         <v>142</v>
       </c>
-      <c r="AB29" s="88">
+      <c r="AK29" s="87">
         <v>60.27</v>
       </c>
-      <c r="AC29" s="88">
+      <c r="AL29" s="87">
         <v>13.506399999999999</v>
       </c>
-      <c r="AD29" s="88">
+      <c r="AM29" s="87">
         <v>1361.88</v>
       </c>
-      <c r="AE29" s="88">
+      <c r="AN29" s="87">
         <v>342.04</v>
       </c>
-      <c r="AF29">
+      <c r="AO29" s="87">
         <f t="shared" si="0"/>
         <v>9.7732997481108299</v>
       </c>
-      <c r="AG29" s="163">
+      <c r="AP29" s="87">
         <f t="shared" si="1"/>
         <v>14.5954</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="81" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="82">
-        <v>0</v>
-      </c>
-      <c r="D30" s="82">
+      <c r="B30" s="80" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="81">
+        <v>0</v>
+      </c>
+      <c r="D30" s="81">
         <v>2</v>
       </c>
-      <c r="E30" s="82">
-        <v>0</v>
-      </c>
-      <c r="F30" s="82">
-        <v>0</v>
-      </c>
-      <c r="G30" s="83">
+      <c r="E30" s="81">
+        <v>0</v>
+      </c>
+      <c r="F30" s="81">
+        <v>0</v>
+      </c>
+      <c r="G30" s="81"/>
+      <c r="H30" s="81"/>
+      <c r="I30" s="81"/>
+      <c r="J30" s="81"/>
+      <c r="K30" s="81"/>
+      <c r="L30" s="81"/>
+      <c r="M30" s="81"/>
+      <c r="N30" s="81"/>
+      <c r="O30" s="81"/>
+      <c r="P30" s="82">
         <v>46.03</v>
       </c>
-      <c r="H30" s="89">
+      <c r="Q30" s="88">
         <v>39.7727273</v>
       </c>
-      <c r="I30" s="82"/>
-      <c r="J30" s="85">
-        <v>0</v>
-      </c>
-      <c r="K30" s="82"/>
-      <c r="L30" s="82"/>
-      <c r="M30" s="82"/>
-      <c r="N30" s="82"/>
-      <c r="O30" s="82"/>
-      <c r="P30" s="83">
+      <c r="R30" s="84">
+        <v>0</v>
+      </c>
+      <c r="S30" s="81"/>
+      <c r="T30" s="81"/>
+      <c r="U30" s="81"/>
+      <c r="V30" s="81"/>
+      <c r="W30" s="81"/>
+      <c r="X30" s="82">
         <v>0.12936611000000001</v>
       </c>
-      <c r="Q30" s="83">
+      <c r="Y30" s="82">
         <v>0.23027167000000001</v>
       </c>
-      <c r="R30" s="83">
+      <c r="Z30" s="82">
         <v>1.78</v>
       </c>
-      <c r="S30" s="86">
+      <c r="AA30" s="85">
         <v>77.3</v>
       </c>
-      <c r="T30" s="86">
+      <c r="AB30" s="85">
         <v>17.8</v>
       </c>
-      <c r="U30" s="87">
+      <c r="AC30" s="86">
         <v>10</v>
       </c>
-      <c r="V30" s="86">
+      <c r="AD30" s="85">
         <v>640.70000000000005</v>
       </c>
-      <c r="W30" s="86">
+      <c r="AE30" s="85">
         <v>665</v>
       </c>
-      <c r="X30" s="88">
+      <c r="AF30" s="88"/>
+      <c r="AG30" s="87">
         <v>920</v>
       </c>
-      <c r="Y30" s="88">
+      <c r="AH30" s="87">
         <v>6.33</v>
       </c>
-      <c r="Z30" s="88">
+      <c r="AI30" s="87">
         <v>1.0049999999999999</v>
       </c>
-      <c r="AA30" s="88">
+      <c r="AJ30" s="87">
         <v>85</v>
       </c>
-      <c r="AB30" s="88">
+      <c r="AK30" s="87">
         <v>39.89</v>
       </c>
-      <c r="AC30" s="88">
+      <c r="AL30" s="87">
         <v>11.229100000000001</v>
       </c>
-      <c r="AD30" s="88">
+      <c r="AM30" s="87">
         <v>1263.72</v>
       </c>
-      <c r="AE30" s="88">
+      <c r="AN30" s="87">
         <v>198.64</v>
       </c>
-      <c r="AF30">
+      <c r="AO30" s="87">
         <f t="shared" si="0"/>
         <v>2.8120063191153237</v>
       </c>
-      <c r="AG30" s="163">
+      <c r="AP30" s="87">
         <f t="shared" si="1"/>
         <v>12.234100000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" s="90" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" s="91">
-        <v>0</v>
-      </c>
-      <c r="D31" s="91">
+      <c r="B31" s="89" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="90">
+        <v>0</v>
+      </c>
+      <c r="D31" s="90">
         <v>2</v>
       </c>
-      <c r="E31" s="91">
-        <v>0</v>
-      </c>
-      <c r="F31" s="91">
-        <v>0</v>
-      </c>
-      <c r="G31" s="92">
+      <c r="E31" s="90">
+        <v>0</v>
+      </c>
+      <c r="F31" s="90">
+        <v>0</v>
+      </c>
+      <c r="G31" s="90"/>
+      <c r="H31" s="90"/>
+      <c r="I31" s="90"/>
+      <c r="J31" s="90"/>
+      <c r="K31" s="90"/>
+      <c r="L31" s="90"/>
+      <c r="M31" s="90"/>
+      <c r="N31" s="90"/>
+      <c r="O31" s="90"/>
+      <c r="P31" s="91">
         <v>64.44</v>
       </c>
-      <c r="H31" s="93">
+      <c r="Q31" s="92">
         <v>39.7727273</v>
       </c>
-      <c r="I31" s="94"/>
-      <c r="J31" s="95">
-        <v>0</v>
-      </c>
-      <c r="K31" s="91"/>
-      <c r="L31" s="91"/>
-      <c r="M31" s="91"/>
-      <c r="N31" s="91"/>
-      <c r="O31" s="91"/>
-      <c r="P31" s="92">
+      <c r="R31" s="93">
+        <v>0</v>
+      </c>
+      <c r="S31" s="90"/>
+      <c r="T31" s="90"/>
+      <c r="U31" s="90"/>
+      <c r="V31" s="90"/>
+      <c r="W31" s="90"/>
+      <c r="X31" s="91">
         <v>0.38626609000000001</v>
       </c>
-      <c r="Q31" s="92">
+      <c r="Y31" s="91">
         <v>0.75321888000000004</v>
       </c>
-      <c r="R31" s="92">
+      <c r="Z31" s="91">
         <v>1.95</v>
       </c>
-      <c r="S31" s="96">
+      <c r="AA31" s="94">
         <v>46.6</v>
       </c>
-      <c r="T31" s="96">
+      <c r="AB31" s="94">
         <v>35.1</v>
       </c>
-      <c r="U31" s="97">
+      <c r="AC31" s="95">
         <v>18</v>
       </c>
-      <c r="V31" s="96">
+      <c r="AD31" s="94">
         <v>723.5</v>
       </c>
-      <c r="W31" s="96">
+      <c r="AE31" s="94">
         <v>131</v>
       </c>
-      <c r="X31" s="98">
+      <c r="AF31" s="92"/>
+      <c r="AG31" s="96">
         <v>130</v>
       </c>
-      <c r="Y31" s="98">
+      <c r="AH31" s="96">
         <v>3.41</v>
       </c>
-      <c r="Z31" s="98">
+      <c r="AI31" s="96">
         <v>0.50919999999999999</v>
       </c>
-      <c r="AA31" s="98">
+      <c r="AJ31" s="96">
         <v>71</v>
       </c>
-      <c r="AB31" s="98">
+      <c r="AK31" s="96">
         <v>53.12</v>
       </c>
-      <c r="AC31" s="98">
+      <c r="AL31" s="96">
         <v>6.9410999999999996</v>
       </c>
-      <c r="AD31" s="98">
+      <c r="AM31" s="96">
         <v>1253.58</v>
       </c>
-      <c r="AE31" s="98">
+      <c r="AN31" s="96">
         <v>366.62</v>
       </c>
-      <c r="AF31">
+      <c r="AO31" s="96">
         <f t="shared" si="0"/>
         <v>10.293255131964809</v>
       </c>
-      <c r="AG31" s="163">
+      <c r="AP31" s="96">
         <f t="shared" si="1"/>
         <v>7.4502999999999995</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="99" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32" s="100">
+      <c r="B32" s="97" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="98">
         <v>1</v>
       </c>
-      <c r="D32" s="100">
-        <v>0</v>
-      </c>
-      <c r="E32" s="101">
+      <c r="D32" s="98">
+        <v>0</v>
+      </c>
+      <c r="E32" s="99">
         <v>75</v>
       </c>
-      <c r="F32" s="101">
+      <c r="F32" s="99">
         <v>17.857142899999999</v>
       </c>
-      <c r="G32" s="101">
+      <c r="G32" s="99"/>
+      <c r="H32" s="99"/>
+      <c r="I32" s="99"/>
+      <c r="J32" s="99"/>
+      <c r="K32" s="99"/>
+      <c r="L32" s="99"/>
+      <c r="M32" s="99"/>
+      <c r="N32" s="99"/>
+      <c r="O32" s="99"/>
+      <c r="P32" s="99">
         <v>70.25</v>
       </c>
-      <c r="H32" s="102">
+      <c r="Q32" s="100">
         <v>47.159090900000002</v>
       </c>
-      <c r="I32" s="101"/>
-      <c r="J32" s="103">
+      <c r="R32" s="101">
         <v>67.27</v>
       </c>
-      <c r="K32" s="100"/>
-      <c r="L32" s="100"/>
-      <c r="M32" s="100"/>
-      <c r="N32" s="100"/>
-      <c r="O32" s="100"/>
-      <c r="P32" s="101">
+      <c r="S32" s="98"/>
+      <c r="T32" s="98"/>
+      <c r="U32" s="98"/>
+      <c r="V32" s="98"/>
+      <c r="W32" s="98"/>
+      <c r="X32" s="99">
         <v>0.31674207999999998</v>
       </c>
-      <c r="Q32" s="101">
+      <c r="Y32" s="99">
         <v>0.35746605999999997</v>
       </c>
-      <c r="R32" s="101">
+      <c r="Z32" s="99">
         <v>1.12857143</v>
       </c>
-      <c r="S32" s="104">
+      <c r="AA32" s="102">
         <v>44.2</v>
       </c>
-      <c r="T32" s="104">
+      <c r="AB32" s="102">
         <v>15.8</v>
       </c>
-      <c r="U32" s="105">
+      <c r="AC32" s="103">
         <v>14</v>
       </c>
-      <c r="V32" s="104">
+      <c r="AD32" s="102">
         <v>636.4</v>
       </c>
-      <c r="W32" s="104">
+      <c r="AE32" s="102">
         <v>883</v>
       </c>
-      <c r="X32" s="106">
+      <c r="AF32" s="169"/>
+      <c r="AG32" s="104">
         <v>150</v>
       </c>
-      <c r="Y32" s="106">
+      <c r="AH32" s="104">
         <v>2.38</v>
       </c>
-      <c r="Z32" s="106">
+      <c r="AI32" s="104">
         <v>0.74480000000000002</v>
       </c>
-      <c r="AA32" s="106">
+      <c r="AJ32" s="104">
         <v>145</v>
       </c>
-      <c r="AB32" s="106">
+      <c r="AK32" s="104">
         <v>55.63</v>
       </c>
-      <c r="AC32" s="106">
+      <c r="AL32" s="104">
         <v>11.422000000000001</v>
       </c>
-      <c r="AD32" s="106">
+      <c r="AM32" s="104">
         <v>1207.1500000000001</v>
       </c>
-      <c r="AE32" s="106">
+      <c r="AN32" s="104">
         <v>506.21</v>
       </c>
-      <c r="AF32">
+      <c r="AO32" s="104">
         <f t="shared" si="0"/>
         <v>6.6386554621848743</v>
       </c>
-      <c r="AG32" s="163">
+      <c r="AP32" s="104">
         <f t="shared" si="1"/>
         <v>12.1668</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" s="107" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" s="108">
+      <c r="B33" s="105" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="106">
         <v>1</v>
       </c>
-      <c r="D33" s="108">
-        <v>0</v>
-      </c>
-      <c r="E33" s="109">
+      <c r="D33" s="106">
+        <v>0</v>
+      </c>
+      <c r="E33" s="107">
         <v>85.294117700000001</v>
       </c>
-      <c r="F33" s="110">
+      <c r="F33" s="108">
         <v>29.411764699999999</v>
       </c>
-      <c r="G33" s="109">
-        <v>83.82</v>
-      </c>
-      <c r="H33" s="111">
-        <v>35.2272727</v>
-      </c>
-      <c r="I33" s="110"/>
-      <c r="J33" s="112">
-        <v>63.19</v>
-      </c>
+      <c r="G33" s="108"/>
+      <c r="H33" s="108"/>
+      <c r="I33" s="108"/>
+      <c r="J33" s="108"/>
       <c r="K33" s="108"/>
       <c r="L33" s="108"/>
       <c r="M33" s="108"/>
       <c r="N33" s="108"/>
       <c r="O33" s="108"/>
-      <c r="P33" s="109">
+      <c r="P33" s="107">
+        <v>83.82</v>
+      </c>
+      <c r="Q33" s="109">
+        <v>35.2272727</v>
+      </c>
+      <c r="R33" s="110">
+        <v>63.19</v>
+      </c>
+      <c r="S33" s="106"/>
+      <c r="T33" s="106"/>
+      <c r="U33" s="106"/>
+      <c r="V33" s="106"/>
+      <c r="W33" s="106"/>
+      <c r="X33" s="107">
         <v>0.37383178</v>
       </c>
-      <c r="Q33" s="109">
+      <c r="Y33" s="107">
         <v>0.58177570000000001</v>
       </c>
-      <c r="R33" s="109">
+      <c r="Z33" s="107">
         <v>1.5562499999999999</v>
       </c>
-      <c r="S33" s="110">
+      <c r="AA33" s="108">
         <v>42.8</v>
       </c>
-      <c r="T33" s="110">
+      <c r="AB33" s="108">
         <v>24.9</v>
       </c>
-      <c r="U33" s="113">
+      <c r="AC33" s="111">
         <v>16</v>
       </c>
-      <c r="V33" s="110">
+      <c r="AD33" s="108">
         <v>658.2</v>
       </c>
-      <c r="W33" s="110">
+      <c r="AE33" s="108">
         <v>111</v>
       </c>
-      <c r="X33" s="114">
+      <c r="AF33" s="109"/>
+      <c r="AG33" s="112">
         <v>120</v>
       </c>
-      <c r="Y33" s="114">
+      <c r="AH33" s="112">
         <v>7.29</v>
       </c>
-      <c r="Z33" s="114">
+      <c r="AI33" s="112">
         <v>0.81930000000000003</v>
       </c>
-      <c r="AA33" s="114">
+      <c r="AJ33" s="112">
         <v>109</v>
       </c>
-      <c r="AB33" s="114">
+      <c r="AK33" s="112">
         <v>56.17</v>
       </c>
-      <c r="AC33" s="114">
+      <c r="AL33" s="112">
         <v>9.0335999999999999</v>
       </c>
-      <c r="AD33" s="114">
+      <c r="AM33" s="112">
         <v>1222.1400000000001</v>
       </c>
-      <c r="AE33" s="114">
+      <c r="AN33" s="112">
         <v>166.65</v>
       </c>
-      <c r="AF33">
+      <c r="AO33" s="112">
         <f t="shared" si="0"/>
         <v>3.4156378600823043</v>
       </c>
-      <c r="AG33" s="163">
+      <c r="AP33" s="112">
         <f t="shared" si="1"/>
         <v>9.8529</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="107" t="s">
-        <v>13</v>
-      </c>
-      <c r="C34" s="108">
+      <c r="B34" s="105" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="106">
         <v>1</v>
       </c>
-      <c r="D34" s="108">
-        <v>0</v>
-      </c>
-      <c r="E34" s="109">
+      <c r="D34" s="106">
+        <v>0</v>
+      </c>
+      <c r="E34" s="107">
         <v>86.486486499999998</v>
       </c>
-      <c r="F34" s="110">
+      <c r="F34" s="108">
         <v>24.864864900000001</v>
       </c>
-      <c r="G34" s="109" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" s="111">
-        <v>48.863636399999997</v>
-      </c>
-      <c r="I34" s="110"/>
-      <c r="J34" s="112">
-        <v>112.11</v>
-      </c>
+      <c r="G34" s="108"/>
+      <c r="H34" s="108"/>
+      <c r="I34" s="108"/>
+      <c r="J34" s="108"/>
       <c r="K34" s="108"/>
       <c r="L34" s="108"/>
       <c r="M34" s="108"/>
       <c r="N34" s="108"/>
       <c r="O34" s="108"/>
-      <c r="P34" s="109">
+      <c r="P34" s="107" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q34" s="109">
+        <v>48.863636399999997</v>
+      </c>
+      <c r="R34" s="110">
+        <v>112.11</v>
+      </c>
+      <c r="S34" s="106"/>
+      <c r="T34" s="106"/>
+      <c r="U34" s="106"/>
+      <c r="V34" s="106"/>
+      <c r="W34" s="106"/>
+      <c r="X34" s="107">
         <v>0.23076922999999999</v>
       </c>
-      <c r="Q34" s="109">
+      <c r="Y34" s="107">
         <v>0.26346153999999999</v>
       </c>
-      <c r="R34" s="109">
+      <c r="Z34" s="107">
         <v>1.14166667</v>
       </c>
-      <c r="S34" s="110">
+      <c r="AA34" s="108">
         <v>52</v>
       </c>
-      <c r="T34" s="110">
+      <c r="AB34" s="108">
         <v>13.7</v>
       </c>
-      <c r="U34" s="113">
+      <c r="AC34" s="111">
         <v>12</v>
       </c>
-      <c r="V34" s="110">
+      <c r="AD34" s="108">
         <v>636.4</v>
       </c>
-      <c r="W34" s="110">
+      <c r="AE34" s="108">
         <v>127</v>
       </c>
-      <c r="X34" s="114">
+      <c r="AF34" s="109"/>
+      <c r="AG34" s="112">
         <v>170</v>
       </c>
-      <c r="Y34" s="114">
+      <c r="AH34" s="112">
         <v>3.3</v>
       </c>
-      <c r="Z34" s="114">
+      <c r="AI34" s="112">
         <v>0.89429999999999998</v>
       </c>
-      <c r="AA34" s="114">
+      <c r="AJ34" s="112">
         <v>117</v>
       </c>
-      <c r="AB34" s="114">
+      <c r="AK34" s="112">
         <v>56.04</v>
       </c>
-      <c r="AC34" s="114">
+      <c r="AL34" s="112">
         <v>10.404500000000001</v>
       </c>
-      <c r="AD34" s="114">
+      <c r="AM34" s="112">
         <v>1093.95</v>
       </c>
-      <c r="AE34" s="114">
+      <c r="AN34" s="112">
         <v>330.5</v>
       </c>
-      <c r="AF34">
+      <c r="AO34" s="112">
         <f t="shared" si="0"/>
         <v>4.1515151515151514</v>
       </c>
-      <c r="AG34" s="163">
+      <c r="AP34" s="112">
         <f t="shared" si="1"/>
         <v>11.2988</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" s="107" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" s="108">
+      <c r="B35" s="105" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="106">
         <v>1</v>
       </c>
-      <c r="D35" s="108">
-        <v>0</v>
-      </c>
-      <c r="E35" s="109">
+      <c r="D35" s="106">
+        <v>0</v>
+      </c>
+      <c r="E35" s="107">
         <v>72.413793100000007</v>
       </c>
-      <c r="F35" s="110">
+      <c r="F35" s="108">
         <v>15.862068969999999</v>
       </c>
-      <c r="G35" s="109">
-        <v>87.69</v>
-      </c>
-      <c r="H35" s="111">
-        <v>55.681818200000002</v>
-      </c>
-      <c r="I35" s="110"/>
-      <c r="J35" s="112">
-        <v>78.48</v>
-      </c>
+      <c r="G35" s="108"/>
+      <c r="H35" s="108"/>
+      <c r="I35" s="108"/>
+      <c r="J35" s="108"/>
       <c r="K35" s="108"/>
       <c r="L35" s="108"/>
       <c r="M35" s="108"/>
       <c r="N35" s="108"/>
       <c r="O35" s="108"/>
-      <c r="P35" s="109"/>
+      <c r="P35" s="107">
+        <v>87.69</v>
+      </c>
       <c r="Q35" s="109">
+        <v>55.681818200000002</v>
+      </c>
+      <c r="R35" s="110">
+        <v>78.48</v>
+      </c>
+      <c r="S35" s="106"/>
+      <c r="T35" s="106"/>
+      <c r="U35" s="106"/>
+      <c r="V35" s="106"/>
+      <c r="W35" s="106"/>
+      <c r="X35" s="107"/>
+      <c r="Y35" s="107">
         <v>0.25914397</v>
       </c>
-      <c r="R35" s="109"/>
-      <c r="S35" s="110">
+      <c r="Z35" s="107"/>
+      <c r="AA35" s="108">
         <v>128.5</v>
       </c>
-      <c r="T35" s="110">
+      <c r="AB35" s="108">
         <v>33.299999999999997</v>
       </c>
-      <c r="U35" s="115"/>
-      <c r="V35" s="110">
+      <c r="AC35" s="113"/>
+      <c r="AD35" s="108">
         <v>610.20000000000005</v>
       </c>
-      <c r="W35" s="110">
+      <c r="AE35" s="108">
         <v>105</v>
       </c>
-      <c r="X35" s="116"/>
-      <c r="Y35" s="116">
+      <c r="AF35" s="109"/>
+      <c r="AG35" s="114"/>
+      <c r="AH35" s="114">
         <v>4.22</v>
       </c>
-      <c r="Z35" s="116">
+      <c r="AI35" s="114">
         <v>0.54300000000000004</v>
       </c>
-      <c r="AA35" s="116">
+      <c r="AJ35" s="114">
         <v>76</v>
       </c>
-      <c r="AB35" s="116">
+      <c r="AK35" s="114">
         <v>40.119999999999997</v>
       </c>
-      <c r="AC35" s="116">
+      <c r="AL35" s="114">
         <v>6.6025</v>
       </c>
-      <c r="AD35" s="116">
+      <c r="AM35" s="114">
         <v>1343.07</v>
       </c>
-      <c r="AE35" s="116">
+      <c r="AN35" s="114">
         <v>317.26</v>
       </c>
-      <c r="AF35">
+      <c r="AO35" s="114">
         <f t="shared" si="0"/>
         <v>7.890995260663507</v>
       </c>
-      <c r="AG35" s="163">
+      <c r="AP35" s="114">
         <f t="shared" si="1"/>
         <v>7.1455000000000002</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" s="117" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" s="118">
+      <c r="B36" s="115" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="116">
         <v>1</v>
       </c>
-      <c r="D36" s="118">
+      <c r="D36" s="116">
         <v>1</v>
       </c>
-      <c r="E36" s="119">
+      <c r="E36" s="117">
         <v>75</v>
       </c>
-      <c r="F36" s="119">
+      <c r="F36" s="117">
         <v>11.071428600000001</v>
       </c>
-      <c r="G36" s="119">
+      <c r="G36" s="117"/>
+      <c r="H36" s="117"/>
+      <c r="I36" s="117"/>
+      <c r="J36" s="117"/>
+      <c r="K36" s="117"/>
+      <c r="L36" s="117"/>
+      <c r="M36" s="117"/>
+      <c r="N36" s="117"/>
+      <c r="O36" s="117"/>
+      <c r="P36" s="117">
         <v>108.042636</v>
       </c>
-      <c r="H36" s="120">
+      <c r="Q36" s="118">
         <v>38.068181799999998</v>
       </c>
-      <c r="I36" s="119"/>
-      <c r="J36" s="121">
+      <c r="R36" s="119">
         <v>58.09</v>
       </c>
-      <c r="K36" s="118"/>
-      <c r="L36" s="118"/>
-      <c r="M36" s="118"/>
-      <c r="N36" s="118"/>
-      <c r="O36" s="118"/>
-      <c r="P36" s="119"/>
-      <c r="Q36" s="118"/>
-      <c r="R36" s="119"/>
-      <c r="S36" s="118"/>
-      <c r="T36" s="119"/>
-      <c r="U36" s="118"/>
-      <c r="V36" s="119"/>
-      <c r="W36" s="118"/>
-      <c r="X36" s="122"/>
-      <c r="Y36" s="122">
+      <c r="S36" s="116"/>
+      <c r="T36" s="116"/>
+      <c r="U36" s="116"/>
+      <c r="V36" s="116"/>
+      <c r="W36" s="116"/>
+      <c r="X36" s="117"/>
+      <c r="Y36" s="116"/>
+      <c r="Z36" s="117"/>
+      <c r="AA36" s="116"/>
+      <c r="AB36" s="117"/>
+      <c r="AC36" s="116"/>
+      <c r="AD36" s="117"/>
+      <c r="AE36" s="116"/>
+      <c r="AF36" s="170"/>
+      <c r="AG36" s="120"/>
+      <c r="AH36" s="120">
         <v>8.61</v>
       </c>
-      <c r="Z36" s="122">
+      <c r="AI36" s="120">
         <v>1.0141</v>
       </c>
-      <c r="AA36" s="122">
+      <c r="AJ36" s="120">
         <v>128</v>
       </c>
-      <c r="AB36" s="122">
+      <c r="AK36" s="120">
         <v>69.31</v>
       </c>
-      <c r="AC36" s="122">
+      <c r="AL36" s="120">
         <v>11.479200000000001</v>
       </c>
-      <c r="AD36" s="122">
+      <c r="AM36" s="120">
         <v>1313.44</v>
       </c>
-      <c r="AE36" s="122">
+      <c r="AN36" s="120">
         <v>151.55000000000001</v>
       </c>
-      <c r="AG36" s="163">
+      <c r="AO36" s="120"/>
+      <c r="AP36" s="120">
         <f t="shared" si="1"/>
         <v>12.493300000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" s="117" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="118">
+      <c r="B37" s="115" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="116">
         <v>1</v>
       </c>
-      <c r="D37" s="118">
+      <c r="D37" s="116">
         <v>1</v>
       </c>
-      <c r="E37" s="119">
+      <c r="E37" s="117">
         <v>97.142857100000001</v>
       </c>
-      <c r="F37" s="123">
+      <c r="F37" s="121">
         <v>20.285714299999999</v>
       </c>
-      <c r="G37" s="119">
+      <c r="G37" s="121"/>
+      <c r="H37" s="121"/>
+      <c r="I37" s="121"/>
+      <c r="J37" s="121"/>
+      <c r="K37" s="121"/>
+      <c r="L37" s="121"/>
+      <c r="M37" s="121"/>
+      <c r="N37" s="121"/>
+      <c r="O37" s="121"/>
+      <c r="P37" s="117">
         <v>84.302325600000003</v>
       </c>
-      <c r="H37" s="124">
+      <c r="Q37" s="122">
         <v>48.295454599999999</v>
       </c>
-      <c r="I37" s="123"/>
-      <c r="J37" s="125">
+      <c r="R37" s="123">
         <v>100.9</v>
       </c>
-      <c r="K37" s="118"/>
-      <c r="L37" s="118"/>
-      <c r="M37" s="118"/>
-      <c r="N37" s="118"/>
-      <c r="O37" s="118"/>
-      <c r="P37" s="119"/>
-      <c r="Q37" s="118"/>
-      <c r="R37" s="119"/>
-      <c r="S37" s="118"/>
-      <c r="T37" s="119"/>
-      <c r="U37" s="118"/>
-      <c r="V37" s="119"/>
-      <c r="W37" s="118"/>
-      <c r="X37" s="122"/>
-      <c r="Y37" s="122">
+      <c r="S37" s="116"/>
+      <c r="T37" s="116"/>
+      <c r="U37" s="116"/>
+      <c r="V37" s="116"/>
+      <c r="W37" s="116"/>
+      <c r="X37" s="117"/>
+      <c r="Y37" s="116"/>
+      <c r="Z37" s="117"/>
+      <c r="AA37" s="116"/>
+      <c r="AB37" s="117"/>
+      <c r="AC37" s="116"/>
+      <c r="AD37" s="117"/>
+      <c r="AE37" s="116"/>
+      <c r="AF37" s="170"/>
+      <c r="AG37" s="120"/>
+      <c r="AH37" s="120">
         <v>6.73</v>
       </c>
-      <c r="Z37" s="122">
+      <c r="AI37" s="120">
         <v>0.90800000000000003</v>
       </c>
-      <c r="AA37" s="122">
+      <c r="AJ37" s="120">
         <v>112</v>
       </c>
-      <c r="AB37" s="122">
+      <c r="AK37" s="120">
         <v>58.19</v>
       </c>
-      <c r="AC37" s="122">
+      <c r="AL37" s="120">
         <v>9.5004000000000008</v>
       </c>
-      <c r="AD37" s="122">
+      <c r="AM37" s="120">
         <v>1371.83</v>
       </c>
-      <c r="AE37" s="122">
+      <c r="AN37" s="120">
         <v>202.84</v>
       </c>
-      <c r="AG37" s="163">
+      <c r="AO37" s="120"/>
+      <c r="AP37" s="120">
         <f t="shared" si="1"/>
         <v>10.4084</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="B38" s="117" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="118">
+      <c r="B38" s="115" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="116">
         <v>1</v>
       </c>
-      <c r="D38" s="118">
+      <c r="D38" s="116">
         <v>1</v>
       </c>
-      <c r="E38" s="119">
+      <c r="E38" s="117">
         <v>90.476190500000001</v>
       </c>
-      <c r="F38" s="123">
+      <c r="F38" s="121">
         <v>31.6666667</v>
       </c>
-      <c r="G38" s="119">
+      <c r="G38" s="121"/>
+      <c r="H38" s="121"/>
+      <c r="I38" s="121"/>
+      <c r="J38" s="121"/>
+      <c r="K38" s="121"/>
+      <c r="L38" s="121"/>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121"/>
+      <c r="O38" s="121"/>
+      <c r="P38" s="117">
         <v>94.9612403</v>
       </c>
-      <c r="H38" s="124">
+      <c r="Q38" s="122">
         <v>41.4772727</v>
       </c>
-      <c r="I38" s="123"/>
-      <c r="J38" s="125">
+      <c r="R38" s="123">
         <v>83.57</v>
       </c>
-      <c r="K38" s="118"/>
-      <c r="L38" s="118"/>
-      <c r="M38" s="118"/>
-      <c r="N38" s="118"/>
-      <c r="O38" s="118"/>
-      <c r="P38" s="119"/>
-      <c r="Q38" s="118"/>
-      <c r="R38" s="119"/>
-      <c r="S38" s="118"/>
-      <c r="T38" s="119"/>
-      <c r="U38" s="118"/>
-      <c r="V38" s="119"/>
-      <c r="W38" s="118"/>
-      <c r="X38" s="122"/>
-      <c r="Y38" s="122">
+      <c r="S38" s="116"/>
+      <c r="T38" s="116"/>
+      <c r="U38" s="116"/>
+      <c r="V38" s="116"/>
+      <c r="W38" s="116"/>
+      <c r="X38" s="117"/>
+      <c r="Y38" s="116"/>
+      <c r="Z38" s="117"/>
+      <c r="AA38" s="116"/>
+      <c r="AB38" s="117"/>
+      <c r="AC38" s="116"/>
+      <c r="AD38" s="117"/>
+      <c r="AE38" s="116"/>
+      <c r="AF38" s="170"/>
+      <c r="AG38" s="120"/>
+      <c r="AH38" s="120">
         <v>2.4300000000000002</v>
       </c>
-      <c r="Z38" s="122">
+      <c r="AI38" s="120">
         <v>0.51919999999999999</v>
       </c>
-      <c r="AA38" s="122">
+      <c r="AJ38" s="120">
         <v>127</v>
       </c>
-      <c r="AB38" s="122">
+      <c r="AK38" s="120">
         <v>58.88</v>
       </c>
-      <c r="AC38" s="122">
+      <c r="AL38" s="120">
         <v>11.9574</v>
       </c>
-      <c r="AD38" s="122">
+      <c r="AM38" s="120">
         <v>1347.44</v>
       </c>
-      <c r="AE38" s="122">
+      <c r="AN38" s="120">
         <v>553.5</v>
       </c>
-      <c r="AG38" s="163">
+      <c r="AO38" s="120"/>
+      <c r="AP38" s="120">
         <f t="shared" si="1"/>
         <v>12.476599999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="B39" s="117" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="118">
+      <c r="B39" s="115" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="116">
         <v>1</v>
       </c>
-      <c r="D39" s="118">
+      <c r="D39" s="116">
         <v>1</v>
       </c>
-      <c r="E39" s="119">
+      <c r="E39" s="117">
         <v>48.387096769999999</v>
       </c>
-      <c r="F39" s="119">
+      <c r="F39" s="117">
         <v>7.4193548390000004</v>
       </c>
-      <c r="G39" s="119">
+      <c r="G39" s="117"/>
+      <c r="H39" s="117"/>
+      <c r="I39" s="117"/>
+      <c r="J39" s="117"/>
+      <c r="K39" s="117"/>
+      <c r="L39" s="117"/>
+      <c r="M39" s="117"/>
+      <c r="N39" s="117"/>
+      <c r="O39" s="117"/>
+      <c r="P39" s="117">
         <v>83.333333400000001</v>
       </c>
-      <c r="H39" s="124">
+      <c r="Q39" s="122">
         <v>51.704545500000002</v>
       </c>
-      <c r="I39" s="123"/>
-      <c r="J39" s="125">
+      <c r="R39" s="123">
         <v>20.38</v>
       </c>
-      <c r="K39" s="118"/>
-      <c r="L39" s="118"/>
-      <c r="M39" s="118"/>
-      <c r="N39" s="118"/>
-      <c r="O39" s="118"/>
-      <c r="P39" s="119"/>
-      <c r="Q39" s="118"/>
-      <c r="R39" s="119"/>
-      <c r="S39" s="118"/>
-      <c r="T39" s="119"/>
-      <c r="U39" s="118"/>
-      <c r="V39" s="119"/>
-      <c r="W39" s="118"/>
-      <c r="X39" s="122"/>
-      <c r="Y39" s="122">
+      <c r="S39" s="116"/>
+      <c r="T39" s="116"/>
+      <c r="U39" s="116"/>
+      <c r="V39" s="116"/>
+      <c r="W39" s="116"/>
+      <c r="X39" s="117"/>
+      <c r="Y39" s="116"/>
+      <c r="Z39" s="117"/>
+      <c r="AA39" s="116"/>
+      <c r="AB39" s="117"/>
+      <c r="AC39" s="116"/>
+      <c r="AD39" s="117"/>
+      <c r="AE39" s="116"/>
+      <c r="AF39" s="170"/>
+      <c r="AG39" s="120"/>
+      <c r="AH39" s="120">
         <v>2.21</v>
       </c>
-      <c r="Z39" s="122">
+      <c r="AI39" s="120">
         <v>0.59340000000000004</v>
       </c>
-      <c r="AA39" s="122">
+      <c r="AJ39" s="120">
         <v>110</v>
       </c>
-      <c r="AB39" s="122">
+      <c r="AK39" s="120">
         <v>54.48</v>
       </c>
-      <c r="AC39" s="122">
+      <c r="AL39" s="120">
         <v>9.8055000000000003</v>
       </c>
-      <c r="AD39" s="122">
+      <c r="AM39" s="120">
         <v>1129.82</v>
       </c>
-      <c r="AE39" s="122">
+      <c r="AN39" s="120">
         <v>510.23</v>
       </c>
-      <c r="AG39" s="163">
+      <c r="AO39" s="120"/>
+      <c r="AP39" s="120">
         <f t="shared" si="1"/>
         <v>10.398900000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="B40" s="126" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" s="127">
+      <c r="B40" s="124" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="125">
         <v>1</v>
       </c>
-      <c r="D40" s="127">
+      <c r="D40" s="125">
         <v>2</v>
       </c>
-      <c r="E40" s="128">
+      <c r="E40" s="126">
         <v>78.787878800000001</v>
       </c>
-      <c r="F40" s="128">
+      <c r="F40" s="126">
         <v>22.121212100000001</v>
       </c>
-      <c r="G40" s="128">
+      <c r="G40" s="126"/>
+      <c r="H40" s="126"/>
+      <c r="I40" s="126"/>
+      <c r="J40" s="126"/>
+      <c r="K40" s="126"/>
+      <c r="L40" s="126"/>
+      <c r="M40" s="126"/>
+      <c r="N40" s="126"/>
+      <c r="O40" s="126"/>
+      <c r="P40" s="126">
         <v>96.41</v>
       </c>
-      <c r="H40" s="129">
+      <c r="Q40" s="127">
         <v>59.090909099999998</v>
       </c>
-      <c r="I40" s="130"/>
-      <c r="J40" s="131">
+      <c r="R40" s="128">
         <v>55.04</v>
       </c>
-      <c r="K40" s="127"/>
-      <c r="L40" s="127"/>
-      <c r="M40" s="127"/>
-      <c r="N40" s="127"/>
-      <c r="O40" s="127"/>
-      <c r="P40" s="128">
+      <c r="S40" s="125"/>
+      <c r="T40" s="125"/>
+      <c r="U40" s="125"/>
+      <c r="V40" s="125"/>
+      <c r="W40" s="125"/>
+      <c r="X40" s="126">
         <v>0.19438444999999999</v>
       </c>
-      <c r="Q40" s="128">
+      <c r="Y40" s="126">
         <v>0.30237581000000002</v>
       </c>
-      <c r="R40" s="128">
+      <c r="Z40" s="126">
         <v>1.5555555599999999</v>
       </c>
-      <c r="S40" s="132">
+      <c r="AA40" s="129">
         <v>92.6</v>
       </c>
-      <c r="T40" s="132">
+      <c r="AB40" s="129">
         <v>28</v>
       </c>
-      <c r="U40" s="133">
+      <c r="AC40" s="130">
         <v>18</v>
       </c>
-      <c r="V40" s="132">
+      <c r="AD40" s="129">
         <v>632</v>
       </c>
-      <c r="W40" s="132">
+      <c r="AE40" s="129">
         <v>113</v>
       </c>
-      <c r="X40" s="134">
+      <c r="AF40" s="132"/>
+      <c r="AG40" s="131">
         <v>574</v>
       </c>
-      <c r="Y40" s="134">
+      <c r="AH40" s="131">
         <v>2.4</v>
       </c>
-      <c r="Z40" s="134">
+      <c r="AI40" s="131">
         <v>0.61670000000000003</v>
       </c>
-      <c r="AA40" s="134">
+      <c r="AJ40" s="131">
         <v>138</v>
       </c>
-      <c r="AB40" s="134">
+      <c r="AK40" s="131">
         <v>52.21</v>
       </c>
-      <c r="AC40" s="134">
+      <c r="AL40" s="131">
         <v>11.1843</v>
       </c>
-      <c r="AD40" s="134">
+      <c r="AM40" s="131">
         <v>1201.3</v>
       </c>
-      <c r="AE40" s="134">
+      <c r="AN40" s="131">
         <v>499.54</v>
       </c>
-      <c r="AF40">
+      <c r="AO40" s="131">
         <f t="shared" si="0"/>
         <v>11.666666666666668</v>
       </c>
-      <c r="AG40" s="163">
+      <c r="AP40" s="131">
         <f t="shared" si="1"/>
         <v>11.801</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="B41" s="126" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41" s="127">
+      <c r="B41" s="124" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="125">
         <v>1</v>
       </c>
-      <c r="D41" s="127">
+      <c r="D41" s="125">
         <v>2</v>
       </c>
-      <c r="E41" s="128">
+      <c r="E41" s="126">
         <v>80.4878049</v>
       </c>
-      <c r="F41" s="132">
+      <c r="F41" s="129">
         <v>22.926829300000001</v>
       </c>
-      <c r="G41" s="128">
+      <c r="G41" s="129"/>
+      <c r="H41" s="129"/>
+      <c r="I41" s="129"/>
+      <c r="J41" s="129"/>
+      <c r="K41" s="129"/>
+      <c r="L41" s="129"/>
+      <c r="M41" s="129"/>
+      <c r="N41" s="129"/>
+      <c r="O41" s="129"/>
+      <c r="P41" s="126">
         <v>97.87</v>
       </c>
-      <c r="H41" s="135">
+      <c r="Q41" s="132">
         <v>58.5227273</v>
       </c>
-      <c r="I41" s="127"/>
-      <c r="J41" s="136">
+      <c r="R41" s="133">
         <v>27.52</v>
       </c>
-      <c r="K41" s="127"/>
-      <c r="L41" s="127"/>
-      <c r="M41" s="127"/>
-      <c r="N41" s="127"/>
-      <c r="O41" s="127"/>
-      <c r="P41" s="128">
+      <c r="S41" s="125"/>
+      <c r="T41" s="125"/>
+      <c r="U41" s="125"/>
+      <c r="V41" s="125"/>
+      <c r="W41" s="125"/>
+      <c r="X41" s="126">
         <v>0.10805501000000001</v>
       </c>
-      <c r="Q41" s="128">
+      <c r="Y41" s="126">
         <v>0.18123771999999999</v>
       </c>
-      <c r="R41" s="128">
+      <c r="Z41" s="126">
         <v>1.6772727300000001</v>
       </c>
-      <c r="S41" s="132">
+      <c r="AA41" s="129">
         <v>203.6</v>
       </c>
-      <c r="T41" s="132">
+      <c r="AB41" s="129">
         <v>36.9</v>
       </c>
-      <c r="U41" s="133">
+      <c r="AC41" s="130">
         <v>22</v>
       </c>
-      <c r="V41" s="132">
+      <c r="AD41" s="129">
         <v>662.5</v>
       </c>
-      <c r="W41" s="132">
+      <c r="AE41" s="129">
         <v>993</v>
       </c>
-      <c r="X41" s="134">
+      <c r="AF41" s="132"/>
+      <c r="AG41" s="131">
         <v>817</v>
       </c>
-      <c r="Y41" s="134">
+      <c r="AH41" s="131">
         <v>2.12</v>
       </c>
-      <c r="Z41" s="134">
+      <c r="AI41" s="131">
         <v>0.60489999999999999</v>
       </c>
-      <c r="AA41" s="134">
+      <c r="AJ41" s="131">
         <v>134</v>
       </c>
-      <c r="AB41" s="134">
+      <c r="AK41" s="131">
         <v>63.87</v>
       </c>
-      <c r="AC41" s="134">
+      <c r="AL41" s="131">
         <v>12.145300000000001</v>
       </c>
-      <c r="AD41" s="134">
+      <c r="AM41" s="131">
         <v>1280.06</v>
       </c>
-      <c r="AE41" s="134">
+      <c r="AN41" s="131">
         <v>602.79999999999995</v>
       </c>
-      <c r="AF41">
+      <c r="AO41" s="131">
         <f t="shared" si="0"/>
         <v>17.40566037735849</v>
       </c>
-      <c r="AG41" s="163">
+      <c r="AP41" s="131">
         <f t="shared" si="1"/>
         <v>12.750200000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="B42" s="126" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="127">
+      <c r="B42" s="124" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="125">
         <v>1</v>
       </c>
-      <c r="D42" s="127">
+      <c r="D42" s="125">
         <v>2</v>
       </c>
-      <c r="E42" s="128">
+      <c r="E42" s="126">
         <v>78.571428600000004</v>
       </c>
-      <c r="F42" s="132">
+      <c r="F42" s="129">
         <v>17.428571399999999</v>
       </c>
-      <c r="G42" s="128">
+      <c r="G42" s="129"/>
+      <c r="H42" s="129"/>
+      <c r="I42" s="129"/>
+      <c r="J42" s="129"/>
+      <c r="K42" s="129"/>
+      <c r="L42" s="129"/>
+      <c r="M42" s="129"/>
+      <c r="N42" s="129"/>
+      <c r="O42" s="129"/>
+      <c r="P42" s="126">
         <v>77.52</v>
       </c>
-      <c r="H42" s="135">
+      <c r="Q42" s="132">
         <v>43.181818200000002</v>
       </c>
-      <c r="I42" s="127"/>
-      <c r="J42" s="136">
+      <c r="R42" s="133">
         <v>61.15</v>
       </c>
-      <c r="K42" s="127"/>
-      <c r="L42" s="127"/>
-      <c r="M42" s="127"/>
-      <c r="N42" s="127"/>
-      <c r="O42" s="127"/>
-      <c r="P42" s="128">
+      <c r="S42" s="125"/>
+      <c r="T42" s="125"/>
+      <c r="U42" s="125"/>
+      <c r="V42" s="125"/>
+      <c r="W42" s="125"/>
+      <c r="X42" s="126">
         <v>0.11928429</v>
       </c>
-      <c r="Q42" s="128">
+      <c r="Y42" s="126">
         <v>0.19615639000000001</v>
       </c>
-      <c r="R42" s="128">
+      <c r="Z42" s="126">
         <v>1.64444444</v>
       </c>
-      <c r="S42" s="132">
+      <c r="AA42" s="129">
         <v>150.9</v>
       </c>
-      <c r="T42" s="132">
+      <c r="AB42" s="129">
         <v>29.6</v>
       </c>
-      <c r="U42" s="133">
+      <c r="AC42" s="130">
         <v>18</v>
       </c>
-      <c r="V42" s="132">
+      <c r="AD42" s="129">
         <v>658.2</v>
       </c>
-      <c r="W42" s="132">
+      <c r="AE42" s="129">
         <v>110</v>
       </c>
-      <c r="X42" s="134">
+      <c r="AF42" s="132"/>
+      <c r="AG42" s="131">
         <v>751</v>
       </c>
-      <c r="Y42" s="134">
+      <c r="AH42" s="131">
         <v>2.8</v>
       </c>
-      <c r="Z42" s="134">
+      <c r="AI42" s="131">
         <v>0.76349999999999996</v>
       </c>
-      <c r="AA42" s="134">
+      <c r="AJ42" s="131">
         <v>129</v>
       </c>
-      <c r="AB42" s="134">
+      <c r="AK42" s="131">
         <v>62.27</v>
       </c>
-      <c r="AC42" s="134">
+      <c r="AL42" s="131">
         <v>11.507</v>
       </c>
-      <c r="AD42" s="134">
+      <c r="AM42" s="131">
         <v>1266.1500000000001</v>
       </c>
-      <c r="AE42" s="134">
+      <c r="AN42" s="131">
         <v>451.2</v>
       </c>
-      <c r="AF42">
+      <c r="AO42" s="131">
         <f t="shared" si="0"/>
         <v>10.571428571428573</v>
       </c>
-      <c r="AG42" s="163">
+      <c r="AP42" s="131">
         <f t="shared" si="1"/>
         <v>12.2705</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="B43" s="137" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" s="138">
+      <c r="B43" s="134" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="135">
         <v>1</v>
       </c>
-      <c r="D43" s="138">
+      <c r="D43" s="135">
         <v>2</v>
       </c>
-      <c r="E43" s="139">
+      <c r="E43" s="136">
         <v>68.571428569999995</v>
       </c>
-      <c r="F43" s="139">
+      <c r="F43" s="136">
         <v>17.38095238</v>
       </c>
-      <c r="G43" s="139">
+      <c r="G43" s="136"/>
+      <c r="H43" s="136"/>
+      <c r="I43" s="136"/>
+      <c r="J43" s="136"/>
+      <c r="K43" s="136"/>
+      <c r="L43" s="136"/>
+      <c r="M43" s="136"/>
+      <c r="N43" s="136"/>
+      <c r="O43" s="136"/>
+      <c r="P43" s="136">
         <v>84.79</v>
       </c>
-      <c r="H43" s="140">
+      <c r="Q43" s="137">
         <v>64.204545499999995</v>
       </c>
-      <c r="I43" s="138"/>
-      <c r="J43" s="141">
+      <c r="R43" s="138">
         <v>60.13</v>
       </c>
-      <c r="K43" s="138"/>
-      <c r="L43" s="138"/>
-      <c r="M43" s="138"/>
-      <c r="N43" s="138"/>
-      <c r="O43" s="138"/>
-      <c r="P43" s="138"/>
-      <c r="Q43" s="138"/>
-      <c r="R43" s="138"/>
-      <c r="S43" s="142"/>
-      <c r="T43" s="142"/>
-      <c r="U43" s="142"/>
-      <c r="V43" s="142"/>
-      <c r="W43" s="142"/>
-      <c r="X43" s="143"/>
-      <c r="Y43" s="143">
+      <c r="S43" s="135"/>
+      <c r="T43" s="135"/>
+      <c r="U43" s="135"/>
+      <c r="V43" s="135"/>
+      <c r="W43" s="135"/>
+      <c r="X43" s="135"/>
+      <c r="Y43" s="135"/>
+      <c r="Z43" s="135"/>
+      <c r="AA43" s="139"/>
+      <c r="AB43" s="139"/>
+      <c r="AC43" s="139"/>
+      <c r="AD43" s="139"/>
+      <c r="AE43" s="139"/>
+      <c r="AF43" s="171"/>
+      <c r="AG43" s="140"/>
+      <c r="AH43" s="140">
         <v>1.97</v>
       </c>
-      <c r="Z43" s="143">
+      <c r="AI43" s="140">
         <v>0.67500000000000004</v>
       </c>
-      <c r="AA43" s="143">
+      <c r="AJ43" s="140">
         <v>125</v>
       </c>
-      <c r="AB43" s="143">
+      <c r="AK43" s="140">
         <v>53.07</v>
       </c>
-      <c r="AC43" s="143">
+      <c r="AL43" s="140">
         <v>10.924200000000001</v>
       </c>
-      <c r="AD43" s="143">
+      <c r="AM43" s="140">
         <v>1274.79</v>
       </c>
-      <c r="AE43" s="143">
+      <c r="AN43" s="140">
         <v>646.1</v>
       </c>
-      <c r="AG43" s="163">
+      <c r="AO43" s="140"/>
+      <c r="AP43" s="140">
         <f t="shared" si="1"/>
         <v>11.599200000000002</v>
       </c>

--- a/BD Cobre.xlsx
+++ b/BD Cobre.xlsx
@@ -149,9 +149,6 @@
     <t>Entrada</t>
   </si>
   <si>
-    <t>MicelioExtra</t>
-  </si>
-  <si>
     <t>MicelioMM</t>
   </si>
   <si>
@@ -165,6 +162,9 @@
   </si>
   <si>
     <t>LargoRaizMM</t>
+  </si>
+  <si>
+    <t>MicelioExtraTincion</t>
   </si>
 </sst>
 </file>
@@ -212,7 +212,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -297,12 +297,6 @@
         <bgColor rgb="FFF9CB9C"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="28">
     <border>
@@ -1201,7 +1195,7 @@
     <xf numFmtId="0" fontId="3" fillId="13" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1524,19 +1518,19 @@
         <v>38</v>
       </c>
       <c r="J1" s="172" t="s">
+        <v>44</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>37</v>
@@ -1590,7 +1584,7 @@
         <v>33</v>
       </c>
       <c r="AF1" s="161" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG1" s="6" t="s">
         <v>20</v>

--- a/BD Cobre.xlsx
+++ b/BD Cobre.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-20490" yWindow="780" windowWidth="20460" windowHeight="10770" tabRatio="236"/>
+    <workbookView xWindow="-20490" yWindow="780" windowWidth="20460" windowHeight="10770" tabRatio="236" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tabla general" sheetId="1" r:id="rId1"/>
+    <sheet name="relativizado" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="144525"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="53">
   <si>
     <t>id</t>
   </si>
@@ -166,12 +167,36 @@
   <si>
     <t>MicelioExtraTincion</t>
   </si>
+  <si>
+    <t>in vitro</t>
+  </si>
+  <si>
+    <t>MM</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Micelio</t>
+  </si>
+  <si>
+    <t>Esporas</t>
+  </si>
+  <si>
+    <t>MicelioPla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EsporasPla </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,8 +236,28 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color rgb="FFB0B0B0"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -297,8 +342,20 @@
         <bgColor rgb="FFF9CB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F8F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="28">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -681,12 +738,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFD6DADC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFD6DADC"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFD6DADC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="173">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1197,6 +1274,24 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1471,7 +1566,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5184,4 +5279,668 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="173"/>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="173" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="173" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="173" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" s="178" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" s="178" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" s="178"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="174">
+        <v>1</v>
+      </c>
+      <c r="B2" s="175">
+        <v>10</v>
+      </c>
+      <c r="C2" s="176" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="176">
+        <v>1</v>
+      </c>
+      <c r="E2" s="176">
+        <v>0</v>
+      </c>
+      <c r="F2" s="176" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="175">
+        <v>2026.8</v>
+      </c>
+      <c r="H2" s="175">
+        <v>263</v>
+      </c>
+      <c r="I2">
+        <f>G2/18093.6</f>
+        <v>0.1120175089534421</v>
+      </c>
+      <c r="J2">
+        <f>H2/3660</f>
+        <v>7.1857923497267759E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="174">
+        <v>2</v>
+      </c>
+      <c r="B3" s="175">
+        <v>10</v>
+      </c>
+      <c r="C3" s="176" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="176">
+        <v>1</v>
+      </c>
+      <c r="E3" s="176">
+        <v>0</v>
+      </c>
+      <c r="F3" s="176" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="175">
+        <v>62.7</v>
+      </c>
+      <c r="H3" s="175">
+        <v>100</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I19" si="0">G3/18093.6</f>
+        <v>3.4653137020825048E-3</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J19" si="1">H3/3660</f>
+        <v>2.7322404371584699E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="174">
+        <v>3</v>
+      </c>
+      <c r="B4" s="175">
+        <v>11</v>
+      </c>
+      <c r="C4" s="176" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="176">
+        <v>1</v>
+      </c>
+      <c r="E4" s="176">
+        <v>0</v>
+      </c>
+      <c r="F4" s="176" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="175">
+        <v>596.5</v>
+      </c>
+      <c r="H4" s="175">
+        <v>154</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>3.2967458106733877E-2</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="1"/>
+        <v>4.2076502732240437E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="174">
+        <v>4</v>
+      </c>
+      <c r="B5" s="175">
+        <v>11</v>
+      </c>
+      <c r="C5" s="176" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="176">
+        <v>1</v>
+      </c>
+      <c r="E5" s="176">
+        <v>0</v>
+      </c>
+      <c r="F5" s="176" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="175">
+        <v>101</v>
+      </c>
+      <c r="H5" s="175">
+        <v>168</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>5.5820842728920728E-3</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="1"/>
+        <v>4.5901639344262293E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="174">
+        <v>5</v>
+      </c>
+      <c r="B6" s="175">
+        <v>12</v>
+      </c>
+      <c r="C6" s="176" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="176">
+        <v>1</v>
+      </c>
+      <c r="E6" s="176">
+        <v>0</v>
+      </c>
+      <c r="F6" s="176" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="175">
+        <v>1297.9000000000001</v>
+      </c>
+      <c r="H6" s="177" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>7.1732546314719023E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="174">
+        <v>6</v>
+      </c>
+      <c r="B7" s="175">
+        <v>12</v>
+      </c>
+      <c r="C7" s="176" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="176">
+        <v>1</v>
+      </c>
+      <c r="E7" s="176">
+        <v>0</v>
+      </c>
+      <c r="F7" s="176" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="177" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="175">
+        <v>154</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="1"/>
+        <v>4.2076502732240437E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="174">
+        <v>7</v>
+      </c>
+      <c r="B8" s="175">
+        <v>13</v>
+      </c>
+      <c r="C8" s="176" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="176">
+        <v>1</v>
+      </c>
+      <c r="E8" s="176">
+        <v>1</v>
+      </c>
+      <c r="F8" s="176" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="175">
+        <v>2486</v>
+      </c>
+      <c r="H8" s="175">
+        <v>93</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>0.13739664853870984</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="1"/>
+        <v>2.540983606557377E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="174">
+        <v>8</v>
+      </c>
+      <c r="B9" s="175">
+        <v>13</v>
+      </c>
+      <c r="C9" s="176" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="176">
+        <v>1</v>
+      </c>
+      <c r="E9" s="176">
+        <v>1</v>
+      </c>
+      <c r="F9" s="176" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="175">
+        <v>124.6</v>
+      </c>
+      <c r="H9" s="175">
+        <v>184</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>6.8864128752708139E-3</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="1"/>
+        <v>5.0273224043715849E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="174">
+        <v>9</v>
+      </c>
+      <c r="B10" s="175">
+        <v>14</v>
+      </c>
+      <c r="C10" s="176" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="176">
+        <v>1</v>
+      </c>
+      <c r="E10" s="176">
+        <v>1</v>
+      </c>
+      <c r="F10" s="176" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="175">
+        <v>414.3</v>
+      </c>
+      <c r="H10" s="175">
+        <v>81</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>2.2897599151081048E-2</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="1"/>
+        <v>2.2131147540983605E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="174">
+        <v>10</v>
+      </c>
+      <c r="B11" s="175">
+        <v>14</v>
+      </c>
+      <c r="C11" s="176" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="176">
+        <v>1</v>
+      </c>
+      <c r="E11" s="176">
+        <v>1</v>
+      </c>
+      <c r="F11" s="176" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="175">
+        <v>202</v>
+      </c>
+      <c r="H11" s="175">
+        <v>468</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>1.1164168545784146E-2</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="1"/>
+        <v>0.12786885245901639</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="174">
+        <v>11</v>
+      </c>
+      <c r="B12" s="175">
+        <v>15</v>
+      </c>
+      <c r="C12" s="176" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="176">
+        <v>1</v>
+      </c>
+      <c r="E12" s="176">
+        <v>1</v>
+      </c>
+      <c r="F12" s="176" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="175">
+        <v>713.9</v>
+      </c>
+      <c r="H12" s="175">
+        <v>94</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>3.9455940221956934E-2</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="1"/>
+        <v>2.5683060109289616E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="174">
+        <v>12</v>
+      </c>
+      <c r="B13" s="175">
+        <v>15</v>
+      </c>
+      <c r="C13" s="176" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="176">
+        <v>1</v>
+      </c>
+      <c r="E13" s="176">
+        <v>1</v>
+      </c>
+      <c r="F13" s="176" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="175">
+        <v>133.4</v>
+      </c>
+      <c r="H13" s="175">
+        <v>683</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="0"/>
+        <v>7.372772693106956E-3</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="1"/>
+        <v>0.1866120218579235</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="174">
+        <v>13</v>
+      </c>
+      <c r="B14" s="175">
+        <v>16</v>
+      </c>
+      <c r="C14" s="176" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="176">
+        <v>1</v>
+      </c>
+      <c r="E14" s="176">
+        <v>2</v>
+      </c>
+      <c r="F14" s="176" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="175">
+        <v>2533.4</v>
+      </c>
+      <c r="H14" s="175">
+        <v>220</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>0.14001635937569087</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="1"/>
+        <v>6.0109289617486336E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="174">
+        <v>14</v>
+      </c>
+      <c r="B15" s="175">
+        <v>16</v>
+      </c>
+      <c r="C15" s="176" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="176">
+        <v>1</v>
+      </c>
+      <c r="E15" s="176">
+        <v>2</v>
+      </c>
+      <c r="F15" s="176" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15" s="175">
+        <v>55.3</v>
+      </c>
+      <c r="H15" s="175">
+        <v>12</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>3.056329309811204E-3</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="1"/>
+        <v>3.2786885245901639E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="174">
+        <v>15</v>
+      </c>
+      <c r="B16" s="175">
+        <v>17</v>
+      </c>
+      <c r="C16" s="176" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="176">
+        <v>1</v>
+      </c>
+      <c r="E16" s="176">
+        <v>2</v>
+      </c>
+      <c r="F16" s="176" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="175">
+        <v>3105</v>
+      </c>
+      <c r="H16" s="175">
+        <v>376</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="0"/>
+        <v>0.17160764027059294</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="1"/>
+        <v>0.10273224043715846</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="174">
+        <v>16</v>
+      </c>
+      <c r="B17" s="175">
+        <v>17</v>
+      </c>
+      <c r="C17" s="176" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="176">
+        <v>1</v>
+      </c>
+      <c r="E17" s="176">
+        <v>2</v>
+      </c>
+      <c r="F17" s="176" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="175">
+        <v>61.9</v>
+      </c>
+      <c r="H17" s="175">
+        <v>6</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="0"/>
+        <v>3.42109917318831E-3</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="1"/>
+        <v>1.639344262295082E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="174">
+        <v>17</v>
+      </c>
+      <c r="B18" s="175">
+        <v>18</v>
+      </c>
+      <c r="C18" s="176" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="176">
+        <v>1</v>
+      </c>
+      <c r="E18" s="176">
+        <v>2</v>
+      </c>
+      <c r="F18" s="176" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="175">
+        <v>4086</v>
+      </c>
+      <c r="H18" s="175">
+        <v>596</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="0"/>
+        <v>0.22582570632709911</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="1"/>
+        <v>0.1628415300546448</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="174">
+        <v>18</v>
+      </c>
+      <c r="B19" s="175">
+        <v>18</v>
+      </c>
+      <c r="C19" s="176" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="176">
+        <v>1</v>
+      </c>
+      <c r="E19" s="176">
+        <v>2</v>
+      </c>
+      <c r="F19" s="176" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" s="175">
+        <v>92.9</v>
+      </c>
+      <c r="H19" s="175">
+        <v>8</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="0"/>
+        <v>5.1344121678383522E-3</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="1"/>
+        <v>2.185792349726776E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G20">
+        <f>SUM(G2:G19)</f>
+        <v>18093.599999999999</v>
+      </c>
+      <c r="H20">
+        <f>SUM(H2:H19)</f>
+        <v>3660</v>
+      </c>
+      <c r="I20">
+        <f>SUM(I2:I19)</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="J20">
+        <f>SUM(J2:J19)</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/BD Cobre.xlsx
+++ b/BD Cobre.xlsx
@@ -1,30 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lauta\Documents\GitHub\Cobre\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513F46D2-4979-435F-B348-DF66537B76B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20490" yWindow="780" windowWidth="20460" windowHeight="10770" tabRatio="236" activeTab="1"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" tabRatio="236" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabla general" sheetId="1" r:id="rId1"/>
     <sheet name="relativizado" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -195,7 +190,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -763,7 +758,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1272,9 +1267,6 @@
     <xf numFmtId="0" fontId="3" fillId="13" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1290,13 +1282,13 @@
     <xf numFmtId="0" fontId="9" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1566,25 +1558,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AP43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="10" max="11" width="14.5703125" customWidth="1"/>
-    <col min="12" max="14" width="9.85546875" customWidth="1"/>
-    <col min="15" max="15" width="15.85546875" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" customWidth="1"/>
+    <col min="10" max="11" width="14.5546875" customWidth="1"/>
+    <col min="12" max="14" width="9.88671875" customWidth="1"/>
+    <col min="15" max="15" width="15.88671875" customWidth="1"/>
+    <col min="32" max="32" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1612,7 +1604,7 @@
       <c r="I1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="172" t="s">
+      <c r="J1" s="2" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="2" t="s">
@@ -1712,7 +1704,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1783,7 +1775,7 @@
       </c>
       <c r="AG2" s="11"/>
     </row>
-    <row r="3" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1840,7 +1832,7 @@
       </c>
       <c r="AG3" s="15"/>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1895,7 +1887,7 @@
       <c r="AF4" s="163"/>
       <c r="AG4" s="15"/>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1968,7 +1960,7 @@
       </c>
       <c r="AG5" s="20"/>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -2041,7 +2033,7 @@
       </c>
       <c r="AG6" s="20"/>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -2114,7 +2106,7 @@
       </c>
       <c r="AG7" s="20"/>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -2187,7 +2179,7 @@
       </c>
       <c r="AG8" s="26"/>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -2260,7 +2252,7 @@
       </c>
       <c r="AG9" s="26"/>
     </row>
-    <row r="10" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -2333,7 +2325,7 @@
       </c>
       <c r="AG10" s="30"/>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2420,7 +2412,7 @@
       </c>
       <c r="AG11" s="35"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -2507,7 +2499,7 @@
       </c>
       <c r="AG12" s="40"/>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2560,7 +2552,7 @@
       <c r="AF13" s="143"/>
       <c r="AG13" s="40"/>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2647,7 +2639,7 @@
       </c>
       <c r="AG14" s="45"/>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2734,7 +2726,7 @@
       </c>
       <c r="AG15" s="45"/>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -2819,7 +2811,7 @@
       </c>
       <c r="AG16" s="45"/>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -2906,7 +2898,7 @@
       </c>
       <c r="AG17" s="51"/>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2993,7 +2985,7 @@
       </c>
       <c r="AG18" s="51"/>
     </row>
-    <row r="19" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -3080,7 +3072,7 @@
       </c>
       <c r="AG19" s="56"/>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -3181,7 +3173,7 @@
         <v>13.714399999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -3281,7 +3273,7 @@
         <v>13.092700000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -3382,7 +3374,7 @@
         <v>10.4689</v>
       </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -3471,7 +3463,7 @@
         <v>11.2867</v>
       </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -3551,7 +3543,7 @@
         <v>10.5482</v>
       </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -3630,7 +3622,7 @@
         <v>13.067300000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -3709,7 +3701,7 @@
         <v>8.2826000000000004</v>
       </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -3788,7 +3780,7 @@
         <v>5.9245000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -3888,7 +3880,7 @@
         <v>11.1501</v>
       </c>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -3988,7 +3980,7 @@
         <v>14.5954</v>
       </c>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -4088,7 +4080,7 @@
         <v>12.234100000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -4188,7 +4180,7 @@
         <v>7.4502999999999995</v>
       </c>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -4288,7 +4280,7 @@
         <v>12.1668</v>
       </c>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -4388,7 +4380,7 @@
         <v>9.8529</v>
       </c>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -4488,7 +4480,7 @@
         <v>11.2988</v>
       </c>
     </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -4580,7 +4572,7 @@
         <v>7.1455000000000002</v>
       </c>
     </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -4659,7 +4651,7 @@
         <v>12.493300000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -4738,7 +4730,7 @@
         <v>10.4084</v>
       </c>
     </row>
-    <row r="38" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -4817,7 +4809,7 @@
         <v>12.476599999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -4896,7 +4888,7 @@
         <v>10.398900000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -4996,7 +4988,7 @@
         <v>11.801</v>
       </c>
     </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -5096,7 +5088,7 @@
         <v>12.750200000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -5196,7 +5188,7 @@
         <v>12.2705</v>
       </c>
     </row>
-    <row r="43" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -5282,12 +5274,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="173"/>
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="172"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5300,46 +5292,46 @@
       <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="173" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="173" t="s">
+      <c r="F1" s="172" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="172" t="s">
         <v>49</v>
       </c>
-      <c r="H1" s="173" t="s">
+      <c r="H1" s="172" t="s">
         <v>50</v>
       </c>
-      <c r="I1" s="178" t="s">
+      <c r="I1" s="177" t="s">
         <v>51</v>
       </c>
-      <c r="J1" s="178" t="s">
+      <c r="J1" s="177" t="s">
         <v>52</v>
       </c>
-      <c r="K1" s="178"/>
-    </row>
-    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="174">
-        <v>1</v>
-      </c>
-      <c r="B2" s="175">
+      <c r="K1" s="177"/>
+    </row>
+    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="173">
+        <v>1</v>
+      </c>
+      <c r="B2" s="174">
         <v>10</v>
       </c>
-      <c r="C2" s="176" t="s">
+      <c r="C2" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="176">
-        <v>1</v>
-      </c>
-      <c r="E2" s="176">
-        <v>0</v>
-      </c>
-      <c r="F2" s="176" t="s">
+      <c r="D2" s="175">
+        <v>1</v>
+      </c>
+      <c r="E2" s="175">
+        <v>0</v>
+      </c>
+      <c r="F2" s="175" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="175">
+      <c r="G2" s="174">
         <v>2026.8</v>
       </c>
-      <c r="H2" s="175">
+      <c r="H2" s="174">
         <v>263</v>
       </c>
       <c r="I2">
@@ -5351,29 +5343,29 @@
         <v>7.1857923497267759E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="174">
+    <row r="3" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="173">
         <v>2</v>
       </c>
-      <c r="B3" s="175">
+      <c r="B3" s="174">
         <v>10</v>
       </c>
-      <c r="C3" s="176" t="s">
+      <c r="C3" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="176">
-        <v>1</v>
-      </c>
-      <c r="E3" s="176">
-        <v>0</v>
-      </c>
-      <c r="F3" s="176" t="s">
+      <c r="D3" s="175">
+        <v>1</v>
+      </c>
+      <c r="E3" s="175">
+        <v>0</v>
+      </c>
+      <c r="F3" s="175" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="175">
+      <c r="G3" s="174">
         <v>62.7</v>
       </c>
-      <c r="H3" s="175">
+      <c r="H3" s="174">
         <v>100</v>
       </c>
       <c r="I3">
@@ -5385,29 +5377,29 @@
         <v>2.7322404371584699E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="174">
+    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="173">
         <v>3</v>
       </c>
-      <c r="B4" s="175">
+      <c r="B4" s="174">
         <v>11</v>
       </c>
-      <c r="C4" s="176" t="s">
+      <c r="C4" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="176">
-        <v>1</v>
-      </c>
-      <c r="E4" s="176">
-        <v>0</v>
-      </c>
-      <c r="F4" s="176" t="s">
+      <c r="D4" s="175">
+        <v>1</v>
+      </c>
+      <c r="E4" s="175">
+        <v>0</v>
+      </c>
+      <c r="F4" s="175" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="175">
+      <c r="G4" s="174">
         <v>596.5</v>
       </c>
-      <c r="H4" s="175">
+      <c r="H4" s="174">
         <v>154</v>
       </c>
       <c r="I4">
@@ -5419,29 +5411,29 @@
         <v>4.2076502732240437E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="174">
+    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="173">
         <v>4</v>
       </c>
-      <c r="B5" s="175">
+      <c r="B5" s="174">
         <v>11</v>
       </c>
-      <c r="C5" s="176" t="s">
+      <c r="C5" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="176">
-        <v>1</v>
-      </c>
-      <c r="E5" s="176">
-        <v>0</v>
-      </c>
-      <c r="F5" s="176" t="s">
+      <c r="D5" s="175">
+        <v>1</v>
+      </c>
+      <c r="E5" s="175">
+        <v>0</v>
+      </c>
+      <c r="F5" s="175" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="175">
+      <c r="G5" s="174">
         <v>101</v>
       </c>
-      <c r="H5" s="175">
+      <c r="H5" s="174">
         <v>168</v>
       </c>
       <c r="I5">
@@ -5453,29 +5445,29 @@
         <v>4.5901639344262293E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="174">
+    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="173">
         <v>5</v>
       </c>
-      <c r="B6" s="175">
+      <c r="B6" s="174">
         <v>12</v>
       </c>
-      <c r="C6" s="176" t="s">
+      <c r="C6" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="176">
-        <v>1</v>
-      </c>
-      <c r="E6" s="176">
-        <v>0</v>
-      </c>
-      <c r="F6" s="176" t="s">
+      <c r="D6" s="175">
+        <v>1</v>
+      </c>
+      <c r="E6" s="175">
+        <v>0</v>
+      </c>
+      <c r="F6" s="175" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="175">
+      <c r="G6" s="174">
         <v>1297.9000000000001</v>
       </c>
-      <c r="H6" s="177" t="s">
+      <c r="H6" s="176" t="s">
         <v>48</v>
       </c>
       <c r="I6">
@@ -5483,29 +5475,29 @@
         <v>7.1732546314719023E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="174">
+    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="173">
         <v>6</v>
       </c>
-      <c r="B7" s="175">
+      <c r="B7" s="174">
         <v>12</v>
       </c>
-      <c r="C7" s="176" t="s">
+      <c r="C7" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="176">
-        <v>1</v>
-      </c>
-      <c r="E7" s="176">
-        <v>0</v>
-      </c>
-      <c r="F7" s="176" t="s">
+      <c r="D7" s="175">
+        <v>1</v>
+      </c>
+      <c r="E7" s="175">
+        <v>0</v>
+      </c>
+      <c r="F7" s="175" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="177" t="s">
+      <c r="G7" s="176" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="175">
+      <c r="H7" s="174">
         <v>154</v>
       </c>
       <c r="J7">
@@ -5513,29 +5505,29 @@
         <v>4.2076502732240437E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="174">
+    <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="173">
         <v>7</v>
       </c>
-      <c r="B8" s="175">
+      <c r="B8" s="174">
         <v>13</v>
       </c>
-      <c r="C8" s="176" t="s">
+      <c r="C8" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="176">
-        <v>1</v>
-      </c>
-      <c r="E8" s="176">
-        <v>1</v>
-      </c>
-      <c r="F8" s="176" t="s">
+      <c r="D8" s="175">
+        <v>1</v>
+      </c>
+      <c r="E8" s="175">
+        <v>1</v>
+      </c>
+      <c r="F8" s="175" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="175">
+      <c r="G8" s="174">
         <v>2486</v>
       </c>
-      <c r="H8" s="175">
+      <c r="H8" s="174">
         <v>93</v>
       </c>
       <c r="I8">
@@ -5547,29 +5539,29 @@
         <v>2.540983606557377E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="174">
+    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="173">
         <v>8</v>
       </c>
-      <c r="B9" s="175">
+      <c r="B9" s="174">
         <v>13</v>
       </c>
-      <c r="C9" s="176" t="s">
+      <c r="C9" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="176">
-        <v>1</v>
-      </c>
-      <c r="E9" s="176">
-        <v>1</v>
-      </c>
-      <c r="F9" s="176" t="s">
+      <c r="D9" s="175">
+        <v>1</v>
+      </c>
+      <c r="E9" s="175">
+        <v>1</v>
+      </c>
+      <c r="F9" s="175" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="175">
+      <c r="G9" s="174">
         <v>124.6</v>
       </c>
-      <c r="H9" s="175">
+      <c r="H9" s="174">
         <v>184</v>
       </c>
       <c r="I9">
@@ -5581,29 +5573,29 @@
         <v>5.0273224043715849E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="174">
+    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="173">
         <v>9</v>
       </c>
-      <c r="B10" s="175">
+      <c r="B10" s="174">
         <v>14</v>
       </c>
-      <c r="C10" s="176" t="s">
+      <c r="C10" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="176">
-        <v>1</v>
-      </c>
-      <c r="E10" s="176">
-        <v>1</v>
-      </c>
-      <c r="F10" s="176" t="s">
+      <c r="D10" s="175">
+        <v>1</v>
+      </c>
+      <c r="E10" s="175">
+        <v>1</v>
+      </c>
+      <c r="F10" s="175" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="175">
+      <c r="G10" s="174">
         <v>414.3</v>
       </c>
-      <c r="H10" s="175">
+      <c r="H10" s="174">
         <v>81</v>
       </c>
       <c r="I10">
@@ -5615,29 +5607,29 @@
         <v>2.2131147540983605E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="174">
+    <row r="11" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="173">
         <v>10</v>
       </c>
-      <c r="B11" s="175">
+      <c r="B11" s="174">
         <v>14</v>
       </c>
-      <c r="C11" s="176" t="s">
+      <c r="C11" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="176">
-        <v>1</v>
-      </c>
-      <c r="E11" s="176">
-        <v>1</v>
-      </c>
-      <c r="F11" s="176" t="s">
+      <c r="D11" s="175">
+        <v>1</v>
+      </c>
+      <c r="E11" s="175">
+        <v>1</v>
+      </c>
+      <c r="F11" s="175" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="175">
+      <c r="G11" s="174">
         <v>202</v>
       </c>
-      <c r="H11" s="175">
+      <c r="H11" s="174">
         <v>468</v>
       </c>
       <c r="I11">
@@ -5649,29 +5641,29 @@
         <v>0.12786885245901639</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="174">
+    <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="173">
         <v>11</v>
       </c>
-      <c r="B12" s="175">
+      <c r="B12" s="174">
         <v>15</v>
       </c>
-      <c r="C12" s="176" t="s">
+      <c r="C12" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="176">
-        <v>1</v>
-      </c>
-      <c r="E12" s="176">
-        <v>1</v>
-      </c>
-      <c r="F12" s="176" t="s">
+      <c r="D12" s="175">
+        <v>1</v>
+      </c>
+      <c r="E12" s="175">
+        <v>1</v>
+      </c>
+      <c r="F12" s="175" t="s">
         <v>46</v>
       </c>
-      <c r="G12" s="175">
+      <c r="G12" s="174">
         <v>713.9</v>
       </c>
-      <c r="H12" s="175">
+      <c r="H12" s="174">
         <v>94</v>
       </c>
       <c r="I12">
@@ -5683,29 +5675,29 @@
         <v>2.5683060109289616E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="174">
+    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="173">
         <v>12</v>
       </c>
-      <c r="B13" s="175">
+      <c r="B13" s="174">
         <v>15</v>
       </c>
-      <c r="C13" s="176" t="s">
+      <c r="C13" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="176">
-        <v>1</v>
-      </c>
-      <c r="E13" s="176">
-        <v>1</v>
-      </c>
-      <c r="F13" s="176" t="s">
+      <c r="D13" s="175">
+        <v>1</v>
+      </c>
+      <c r="E13" s="175">
+        <v>1</v>
+      </c>
+      <c r="F13" s="175" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="175">
+      <c r="G13" s="174">
         <v>133.4</v>
       </c>
-      <c r="H13" s="175">
+      <c r="H13" s="174">
         <v>683</v>
       </c>
       <c r="I13">
@@ -5717,29 +5709,29 @@
         <v>0.1866120218579235</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="174">
+    <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="173">
         <v>13</v>
       </c>
-      <c r="B14" s="175">
+      <c r="B14" s="174">
         <v>16</v>
       </c>
-      <c r="C14" s="176" t="s">
+      <c r="C14" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="176">
-        <v>1</v>
-      </c>
-      <c r="E14" s="176">
+      <c r="D14" s="175">
+        <v>1</v>
+      </c>
+      <c r="E14" s="175">
         <v>2</v>
       </c>
-      <c r="F14" s="176" t="s">
+      <c r="F14" s="175" t="s">
         <v>46</v>
       </c>
-      <c r="G14" s="175">
+      <c r="G14" s="174">
         <v>2533.4</v>
       </c>
-      <c r="H14" s="175">
+      <c r="H14" s="174">
         <v>220</v>
       </c>
       <c r="I14">
@@ -5751,29 +5743,29 @@
         <v>6.0109289617486336E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="174">
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="173">
         <v>14</v>
       </c>
-      <c r="B15" s="175">
+      <c r="B15" s="174">
         <v>16</v>
       </c>
-      <c r="C15" s="176" t="s">
+      <c r="C15" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="176">
-        <v>1</v>
-      </c>
-      <c r="E15" s="176">
+      <c r="D15" s="175">
+        <v>1</v>
+      </c>
+      <c r="E15" s="175">
         <v>2</v>
       </c>
-      <c r="F15" s="176" t="s">
+      <c r="F15" s="175" t="s">
         <v>47</v>
       </c>
-      <c r="G15" s="175">
+      <c r="G15" s="174">
         <v>55.3</v>
       </c>
-      <c r="H15" s="175">
+      <c r="H15" s="174">
         <v>12</v>
       </c>
       <c r="I15">
@@ -5785,29 +5777,29 @@
         <v>3.2786885245901639E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="174">
+    <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="173">
         <v>15</v>
       </c>
-      <c r="B16" s="175">
+      <c r="B16" s="174">
         <v>17</v>
       </c>
-      <c r="C16" s="176" t="s">
+      <c r="C16" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="176">
-        <v>1</v>
-      </c>
-      <c r="E16" s="176">
+      <c r="D16" s="175">
+        <v>1</v>
+      </c>
+      <c r="E16" s="175">
         <v>2</v>
       </c>
-      <c r="F16" s="176" t="s">
+      <c r="F16" s="175" t="s">
         <v>46</v>
       </c>
-      <c r="G16" s="175">
+      <c r="G16" s="174">
         <v>3105</v>
       </c>
-      <c r="H16" s="175">
+      <c r="H16" s="174">
         <v>376</v>
       </c>
       <c r="I16">
@@ -5819,29 +5811,29 @@
         <v>0.10273224043715846</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="174">
+    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="173">
         <v>16</v>
       </c>
-      <c r="B17" s="175">
+      <c r="B17" s="174">
         <v>17</v>
       </c>
-      <c r="C17" s="176" t="s">
+      <c r="C17" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="176">
-        <v>1</v>
-      </c>
-      <c r="E17" s="176">
+      <c r="D17" s="175">
+        <v>1</v>
+      </c>
+      <c r="E17" s="175">
         <v>2</v>
       </c>
-      <c r="F17" s="176" t="s">
+      <c r="F17" s="175" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="175">
+      <c r="G17" s="174">
         <v>61.9</v>
       </c>
-      <c r="H17" s="175">
+      <c r="H17" s="174">
         <v>6</v>
       </c>
       <c r="I17">
@@ -5853,29 +5845,29 @@
         <v>1.639344262295082E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="174">
+    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="173">
         <v>17</v>
       </c>
-      <c r="B18" s="175">
+      <c r="B18" s="174">
         <v>18</v>
       </c>
-      <c r="C18" s="176" t="s">
+      <c r="C18" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="176">
-        <v>1</v>
-      </c>
-      <c r="E18" s="176">
+      <c r="D18" s="175">
+        <v>1</v>
+      </c>
+      <c r="E18" s="175">
         <v>2</v>
       </c>
-      <c r="F18" s="176" t="s">
+      <c r="F18" s="175" t="s">
         <v>46</v>
       </c>
-      <c r="G18" s="175">
+      <c r="G18" s="174">
         <v>4086</v>
       </c>
-      <c r="H18" s="175">
+      <c r="H18" s="174">
         <v>596</v>
       </c>
       <c r="I18">
@@ -5887,29 +5879,29 @@
         <v>0.1628415300546448</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="174">
+    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="173">
         <v>18</v>
       </c>
-      <c r="B19" s="175">
+      <c r="B19" s="174">
         <v>18</v>
       </c>
-      <c r="C19" s="176" t="s">
+      <c r="C19" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="176">
-        <v>1</v>
-      </c>
-      <c r="E19" s="176">
+      <c r="D19" s="175">
+        <v>1</v>
+      </c>
+      <c r="E19" s="175">
         <v>2</v>
       </c>
-      <c r="F19" s="176" t="s">
+      <c r="F19" s="175" t="s">
         <v>47</v>
       </c>
-      <c r="G19" s="175">
+      <c r="G19" s="174">
         <v>92.9</v>
       </c>
-      <c r="H19" s="175">
+      <c r="H19" s="174">
         <v>8</v>
       </c>
       <c r="I19">
@@ -5921,7 +5913,7 @@
         <v>2.185792349726776E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G20">
         <f>SUM(G2:G19)</f>
         <v>18093.599999999999</v>

--- a/BD Cobre.xlsx
+++ b/BD Cobre.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lauta\Documents\GitHub\Cobre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513F46D2-4979-435F-B348-DF66537B76B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{129C65E5-4F51-48AA-8CE9-BB891B638DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" tabRatio="236" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="14400" windowHeight="9036" tabRatio="236" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabla general" sheetId="1" r:id="rId1"/>
     <sheet name="relativizado" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1567,16 +1568,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AP43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="10" max="11" width="14.5546875" customWidth="1"/>
-    <col min="12" max="14" width="9.88671875" customWidth="1"/>
-    <col min="15" max="15" width="15.88671875" customWidth="1"/>
-    <col min="32" max="32" width="14.5546875" customWidth="1"/>
+    <col min="10" max="11" width="14.54296875" customWidth="1"/>
+    <col min="12" max="14" width="9.90625" customWidth="1"/>
+    <col min="15" max="15" width="15.90625" customWidth="1"/>
+    <col min="32" max="32" width="14.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1704,7 +1705,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1775,7 +1776,7 @@
       </c>
       <c r="AG2" s="11"/>
     </row>
-    <row r="3" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1832,7 +1833,7 @@
       </c>
       <c r="AG3" s="15"/>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1887,7 +1888,7 @@
       <c r="AF4" s="163"/>
       <c r="AG4" s="15"/>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1960,7 +1961,7 @@
       </c>
       <c r="AG5" s="20"/>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -2033,7 +2034,7 @@
       </c>
       <c r="AG6" s="20"/>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -2106,7 +2107,7 @@
       </c>
       <c r="AG7" s="20"/>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -2179,7 +2180,7 @@
       </c>
       <c r="AG8" s="26"/>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -2252,7 +2253,7 @@
       </c>
       <c r="AG9" s="26"/>
     </row>
-    <row r="10" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -2325,7 +2326,7 @@
       </c>
       <c r="AG10" s="30"/>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2412,7 +2413,7 @@
       </c>
       <c r="AG11" s="35"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -2499,7 +2500,7 @@
       </c>
       <c r="AG12" s="40"/>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2552,7 +2553,7 @@
       <c r="AF13" s="143"/>
       <c r="AG13" s="40"/>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2639,7 +2640,7 @@
       </c>
       <c r="AG14" s="45"/>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2726,7 +2727,7 @@
       </c>
       <c r="AG15" s="45"/>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -2811,7 +2812,7 @@
       </c>
       <c r="AG16" s="45"/>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -2898,7 +2899,7 @@
       </c>
       <c r="AG17" s="51"/>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2985,7 +2986,7 @@
       </c>
       <c r="AG18" s="51"/>
     </row>
-    <row r="19" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -3072,7 +3073,7 @@
       </c>
       <c r="AG19" s="56"/>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -3173,7 +3174,7 @@
         <v>13.714399999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -3273,7 +3274,7 @@
         <v>13.092700000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -3374,7 +3375,7 @@
         <v>10.4689</v>
       </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -3463,7 +3464,7 @@
         <v>11.2867</v>
       </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -3543,7 +3544,7 @@
         <v>10.5482</v>
       </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -3622,7 +3623,7 @@
         <v>13.067300000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -3701,7 +3702,7 @@
         <v>8.2826000000000004</v>
       </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -3780,7 +3781,7 @@
         <v>5.9245000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -3880,7 +3881,7 @@
         <v>11.1501</v>
       </c>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -3980,7 +3981,7 @@
         <v>14.5954</v>
       </c>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -4080,7 +4081,7 @@
         <v>12.234100000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -4180,7 +4181,7 @@
         <v>7.4502999999999995</v>
       </c>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -4280,7 +4281,7 @@
         <v>12.1668</v>
       </c>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -4380,7 +4381,7 @@
         <v>9.8529</v>
       </c>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -4480,7 +4481,7 @@
         <v>11.2988</v>
       </c>
     </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -4572,7 +4573,7 @@
         <v>7.1455000000000002</v>
       </c>
     </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -4651,7 +4652,7 @@
         <v>12.493300000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -4730,7 +4731,7 @@
         <v>10.4084</v>
       </c>
     </row>
-    <row r="38" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -4809,7 +4810,7 @@
         <v>12.476599999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -4888,7 +4889,7 @@
         <v>10.398900000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -4988,7 +4989,7 @@
         <v>11.801</v>
       </c>
     </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -5088,7 +5089,7 @@
         <v>12.750200000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -5188,7 +5189,7 @@
         <v>12.2705</v>
       </c>
     </row>
-    <row r="43" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -5276,9 +5277,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="172"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -5309,7 +5310,7 @@
       </c>
       <c r="K1" s="177"/>
     </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="173">
         <v>1</v>
       </c>
@@ -5343,7 +5344,7 @@
         <v>7.1857923497267759E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="173">
         <v>2</v>
       </c>
@@ -5377,7 +5378,7 @@
         <v>2.7322404371584699E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="173">
         <v>3</v>
       </c>
@@ -5411,7 +5412,7 @@
         <v>4.2076502732240437E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="173">
         <v>4</v>
       </c>
@@ -5445,7 +5446,7 @@
         <v>4.5901639344262293E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="173">
         <v>5</v>
       </c>
@@ -5475,7 +5476,7 @@
         <v>7.1732546314719023E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="173">
         <v>6</v>
       </c>
@@ -5505,7 +5506,7 @@
         <v>4.2076502732240437E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="173">
         <v>7</v>
       </c>
@@ -5539,7 +5540,7 @@
         <v>2.540983606557377E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="173">
         <v>8</v>
       </c>
@@ -5573,7 +5574,7 @@
         <v>5.0273224043715849E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="173">
         <v>9</v>
       </c>
@@ -5607,7 +5608,7 @@
         <v>2.2131147540983605E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="173">
         <v>10</v>
       </c>
@@ -5641,7 +5642,7 @@
         <v>0.12786885245901639</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="173">
         <v>11</v>
       </c>
@@ -5675,7 +5676,7 @@
         <v>2.5683060109289616E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="173">
         <v>12</v>
       </c>
@@ -5709,7 +5710,7 @@
         <v>0.1866120218579235</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="173">
         <v>13</v>
       </c>
@@ -5743,7 +5744,7 @@
         <v>6.0109289617486336E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="173">
         <v>14</v>
       </c>
@@ -5777,7 +5778,7 @@
         <v>3.2786885245901639E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="173">
         <v>15</v>
       </c>
@@ -5811,7 +5812,7 @@
         <v>0.10273224043715846</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="173">
         <v>16</v>
       </c>
@@ -5845,7 +5846,7 @@
         <v>1.639344262295082E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="173">
         <v>17</v>
       </c>
@@ -5879,7 +5880,7 @@
         <v>0.1628415300546448</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="173">
         <v>18</v>
       </c>
@@ -5913,7 +5914,7 @@
         <v>2.185792349726776E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="G20">
         <f>SUM(G2:G19)</f>
         <v>18093.599999999999</v>
